--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1291,17 +1291,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>12/06/2026 08:17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1309,12 +1309,12 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
         </is>
       </c>
     </row>
@@ -1324,30 +1324,34 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:29</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:52</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1357,30 +1361,34 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 14:51</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:38</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1390,30 +1398,34 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 19:35</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>11/06/2026 12:01</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1423,17 +1435,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 16:35</t>
+          <t>11/06/2026 10:50</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1441,12 +1453,12 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
         </is>
       </c>
     </row>
@@ -1456,17 +1468,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026 19:37</t>
+          <t>11/06/2026 09:59</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1474,12 +1486,12 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -1489,17 +1501,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026 01:28</t>
+          <t>11/06/2026 09:29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1507,12 +1519,12 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -1522,17 +1534,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16/03/2026 11:15</t>
+          <t>10/06/2026 09:50</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1540,12 +1552,12 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
         </is>
       </c>
     </row>
@@ -1555,17 +1567,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10/03/2026 09:00</t>
+          <t>09/06/2026 17:11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1573,12 +1585,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1588,34 +1600,30 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
+          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 19:52</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội, TP.HCM</t>
-        </is>
-      </c>
+          <t>09/06/2026 16:59</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
         </is>
       </c>
     </row>
@@ -1625,30 +1633,30 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Quy Nhơn</t>
+          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:44</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>09/06/2026 13:44</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
         </is>
       </c>
     </row>
@@ -1658,30 +1666,30 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Đà Nẵng</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:37</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>09/06/2026 10:42</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
         </is>
       </c>
     </row>
@@ -1691,34 +1699,30 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
+          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:45</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:23</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
+          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1732,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Đà Lạt</t>
+          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:27</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1746,12 +1750,12 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -1761,17 +1765,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Thanh Hóa</t>
+          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>05/02/2026 09:57</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1779,12 +1783,12 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
+          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1798,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
+          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>04/02/2026 10:54</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1812,12 +1816,12 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -1827,17 +1831,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
+          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:48</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1845,12 +1849,12 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
+          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1860,17 +1864,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
+          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:47</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1878,12 +1882,12 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
+          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -1893,17 +1897,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
+          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 11:04</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1911,12 +1915,12 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -1926,34 +1930,30 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>26/01/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:19</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
         </is>
       </c>
     </row>
@@ -1963,34 +1963,5022 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 16:45</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:18</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
+          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>09/06/2026 09:18</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:55</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>06/06/2026 22:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>06/06/2026 07:22</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>05/06/2026 18:09</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>05/06/2026 13:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>05/06/2026 12:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>04/06/2026 14:02</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>04/06/2026 09:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>04/06/2026 09:11</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:29</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>03/06/2026 14:21</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 19:53</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 19:51</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 19:22</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 16:52</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 10:21</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 10:01</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 10:01</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 10:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 10:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 10:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 09:57</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 09:55</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 09:54</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>02/06/2026 09:41</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>01/06/2026 13:31</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>01/06/2026 00:38</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>01/06/2026 00:28</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>01/06/2026 00:19</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>01/06/2026 00:09</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>01/06/2026 00:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>31/05/2026 23:52</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>31/05/2026 23:43</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>31/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>31/05/2026 21:33</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>30/05/2026 20:49</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>30/05/2026 13:42</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026 20:31</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026 08:51</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026 08:34</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>29/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>28/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2026 11:02</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2026 09:38</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2026 09:32</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>27/05/2026 09:09</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>26/05/2026 16:11</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>26/05/2026 10:52</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>26/05/2026 10:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>26/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 19:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:18</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:17</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:14</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:13</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>25/05/2026 17:12</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 14:54</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 14:52</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 13:38</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:29</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:23</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>22/05/2026 09:20</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 16:08</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:46</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:34</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:26</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:21</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:07</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 15:01</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 14:33</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 11:00</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>21/05/2026 09:36</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 19:08</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 17:08</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 16:57</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 16:41</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 09:37</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 09:02</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 23:46</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 23:10</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 22:33</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 17:19</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:14</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 13:55</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 11:40</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>19/05/2026 09:04</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026 16:11</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026 15:17</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026 14:51</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:32</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>18/05/2026 09:07</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>16/05/2026 09:30</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>16/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 20:09</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 17:30</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:11</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:08</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:07</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:07</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:07</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 11:07</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:54</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:42</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:12</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:55</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>14/05/2026 19:35</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>14/05/2026 13:42</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 17:01</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 17:00</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 16:35</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 14:34</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:24</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 09:59</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 09:33</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 09:23</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>13/05/2026 09:12</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Tin tuc</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>12/05/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>06/05/2026 19:37</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>05/05/2026 10:31</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026 01:28</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>16/03/2026 11:15</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>10/03/2026 09:00</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>09/03/2026 19:52</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội, TP.HCM</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Open Day Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>03/03/2026 09:44</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Open Day Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>03/03/2026 09:37</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr"/>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>02/03/2026 09:45</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Open Day tại Đà Lạt</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>02/03/2026 09:27</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Open Day tại Thanh Hóa</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>05/02/2026 09:57</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>04/02/2026 10:54</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>02/02/2026 16:48</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>02/02/2026 16:47</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>02/02/2026 11:04</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>26/01/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 16:45</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
           <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 10:38</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>20/01/2026 19:51</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>28/12/2025 18:24</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 2/11, sự kiện “Homecoming 2025” của Trường Đại học FPT đã diễn ra đầy cảm xúc với sự góp mặt của 400 cựu sinh viên của gần 20 thế hệ, từ khoá đầu tiên từ khi thành lập trường tới nay. Không chỉ là nơi để mọi người cùng tề tựu, sự kiện đã [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/400-cuu-sinh-vien-tu-nhieu-the-he-fptu-hoi-ngo-tai-su-kien-homecoming-2025/</t>
         </is>
       </c>
     </row>

--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tong quan nguon" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tất cả hoạt động" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 hoạt động mới nhất" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tong quan nguon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tất cả hoạt động" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="20 hoạt động mới nhất" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -608,12 +608,12 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -641,12 +641,12 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -666,24 +666,20 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>30/06/2026 13:48</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -693,7 +689,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -703,7 +699,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -711,12 +707,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -726,7 +722,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -736,7 +732,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>26/06/2026 10:57</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -744,12 +740,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -759,7 +755,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -777,12 +773,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -792,7 +788,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -802,20 +798,24 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -835,24 +835,20 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>24/06/2026 07:01</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -862,7 +858,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -872,7 +868,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -880,12 +876,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -895,7 +891,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -913,12 +909,12 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -928,17 +924,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -946,12 +942,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -961,7 +957,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -971,20 +967,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1012,12 +1012,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1045,12 +1045,12 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1078,12 +1078,12 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>15/06/2026 09:13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1111,12 +1111,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
+          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 10:20</t>
+          <t>15/06/2026 08:52</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1144,12 +1144,12 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
+          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:46</t>
+          <t>14/06/2026 07:23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1177,12 +1177,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
+          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
+          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:22</t>
+          <t>14/06/2026 07:06</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1210,12 +1210,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
+          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
+          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 19:15</t>
+          <t>14/06/2026 05:48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1243,12 +1243,12 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
+          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
+          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 09:12</t>
+          <t>13/06/2026 10:20</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1276,12 +1276,12 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
+          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
+          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 08:17</t>
+          <t>13/06/2026 09:46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1309,12 +1309,12 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
+          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1334,24 +1334,20 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:52</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>13/06/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1357,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
+          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1371,24 +1367,20 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:38</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 19:15</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
+          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1390,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
+          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1408,24 +1400,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 12:01</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 09:12</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
+          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1423,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
+          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1445,7 +1433,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 10:50</t>
+          <t>12/06/2026 08:17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1453,12 +1441,12 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
+          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1456,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
+          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1478,20 +1466,24 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:59</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:52</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
+          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1493,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
+          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1511,20 +1503,24 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:29</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:38</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
+          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1530,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
+          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1544,20 +1540,24 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:50</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+          <t>11/06/2026 12:01</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
+          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
+          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 17:11</t>
+          <t>11/06/2026 10:50</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1585,12 +1585,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
+          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
+          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 16:59</t>
+          <t>11/06/2026 09:59</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1618,12 +1618,12 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
+          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
+          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 13:44</t>
+          <t>11/06/2026 09:29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1651,12 +1651,12 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
+          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
+          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 10:42</t>
+          <t>10/06/2026 09:50</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1684,12 +1684,12 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
+          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
+          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 17:11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1717,12 +1717,12 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
+          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
+          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 16:59</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1750,12 +1750,12 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
+          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
+          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 13:44</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1783,12 +1783,12 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 10:42</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1816,12 +1816,12 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
+          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
+          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1849,12 +1849,12 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
+          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
+          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1882,12 +1882,12 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
+          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1915,12 +1915,12 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
+          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
+          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:19</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1948,12 +1948,12 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
+          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1981,12 +1981,12 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
+          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
+          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
+          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2029,17 +2029,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2047,12 +2047,12 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
+          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2072,24 +2072,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 22:25</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:19</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
+          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2095,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
+          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2109,7 +2105,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 07:22</t>
+          <t>09/06/2026 09:18</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2117,12 +2113,12 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
+          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2128,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
+          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2142,7 +2138,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 18:09</t>
+          <t>09/06/2026 09:18</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2150,12 +2146,12 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
+          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
         </is>
       </c>
     </row>
@@ -2165,34 +2161,30 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 13:00</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>08/06/2026 14:55</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2194,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2212,24 +2204,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 12:25</t>
+          <t>06/06/2026 22:25</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Quy Nhơn</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
+          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2231,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
+          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2249,7 +2241,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 14:02</t>
+          <t>06/06/2026 07:22</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2257,12 +2249,12 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2264,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
+          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2282,7 +2274,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:30</t>
+          <t>05/06/2026 18:09</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2290,12 +2282,12 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
+          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2297,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
+          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2315,24 +2307,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:11</t>
+          <t>05/06/2026 13:00</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Quy Nhơn</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
+          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -2342,30 +2334,34 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:29</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>05/06/2026 12:25</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2371,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
+          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2385,24 +2381,20 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:21</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>04/06/2026 14:02</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
+          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2404,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
+          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2422,7 +2414,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:53</t>
+          <t>04/06/2026 09:30</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2430,12 +2422,12 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
+          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2437,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
+          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2455,20 +2447,24 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:51</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>04/06/2026 09:11</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
+          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2474,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
+          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:22</t>
+          <t>03/06/2026 14:29</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2496,12 +2492,12 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
+          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2507,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
+          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2521,20 +2517,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:55</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>03/06/2026 14:21</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
+          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
+          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:52</t>
+          <t>02/06/2026 19:53</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2562,12 +2562,12 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
+          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
+          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:21</t>
+          <t>02/06/2026 19:51</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -2595,12 +2595,12 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
+          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 19:22</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -2628,12 +2628,12 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
+          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
+          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 16:55</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -2661,12 +2661,12 @@
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
+          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
+          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 16:52</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -2694,12 +2694,12 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:21</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -2727,12 +2727,12 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
+          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
+          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -2760,12 +2760,12 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
+          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
+          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:57</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -2793,12 +2793,12 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
+          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
+          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:55</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -2826,12 +2826,12 @@
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
+          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
+          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:54</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2859,12 +2859,12 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
+          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
+          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:41</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2892,12 +2892,12 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
+          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -2907,17 +2907,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
+          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 13:31</t>
+          <t>02/06/2026 09:57</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2925,12 +2925,12 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
+          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:38</t>
+          <t>02/06/2026 09:55</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2958,12 +2958,12 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
+          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:28</t>
+          <t>02/06/2026 09:54</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -2991,12 +2991,12 @@
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
+          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:19</t>
+          <t>02/06/2026 09:41</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3024,12 +3024,12 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3039,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
+          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:09</t>
+          <t>01/06/2026 13:31</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -3057,12 +3057,12 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
+          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3082,24 +3082,20 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:01</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 00:38</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr"/>
       <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
+          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3105,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:52</t>
+          <t>01/06/2026 00:28</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -3127,12 +3123,12 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
+          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3138,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
+          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3152,7 +3148,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:43</t>
+          <t>01/06/2026 00:19</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -3160,12 +3156,12 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
+          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3171,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
+          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3185,24 +3181,20 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:33</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 00:09</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
       <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
+          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3204,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
+          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3222,20 +3214,24 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 21:33</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr"/>
+          <t>01/06/2026 00:01</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
+          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
         </is>
       </c>
     </row>
@@ -3245,34 +3241,30 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
+          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 20:49</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>31/05/2026 23:52</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
       <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
+          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
         </is>
       </c>
     </row>
@@ -3282,17 +3274,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
+          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 13:42</t>
+          <t>31/05/2026 23:43</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -3300,12 +3292,12 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
+          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3315,30 +3307,34 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
+          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 20:31</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr"/>
+          <t>31/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
+          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3344,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
+          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3358,7 +3354,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:51</t>
+          <t>31/05/2026 21:33</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3366,12 +3362,12 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
+          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
+          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
         </is>
       </c>
     </row>
@@ -3381,30 +3377,34 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
+          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:34</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>30/05/2026 20:49</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
+          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -3414,34 +3414,30 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
+          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:30</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>30/05/2026 13:42</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
+          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3447,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
+          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3461,7 +3457,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026 10:33</t>
+          <t>29/05/2026 20:31</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -3469,12 +3465,12 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
+          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3480,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
+          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3494,7 +3490,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 11:02</t>
+          <t>29/05/2026 08:51</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -3502,12 +3498,12 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
+          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3513,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3527,24 +3523,20 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:38</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>29/05/2026 08:34</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
+          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3546,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3564,24 +3556,24 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:32</t>
+          <t>29/05/2026 08:30</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Quy Nhơn</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
+          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3583,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
+          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3601,7 +3593,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:09</t>
+          <t>28/05/2026 10:33</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -3609,12 +3601,12 @@
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
+          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3616,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3634,24 +3626,20 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:11</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>27/05/2026 11:02</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
+          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3649,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
+          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3671,20 +3659,24 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:52</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
+          <t>27/05/2026 09:38</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
+          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
         </is>
       </c>
     </row>
@@ -3694,30 +3686,34 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
+          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:10</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>27/05/2026 09:32</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
+          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -3727,34 +3723,30 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 09:22</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>27/05/2026 09:09</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
+          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3756,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
+          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3774,20 +3766,24 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 19:40</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>26/05/2026 16:11</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
+          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3793,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
+          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3807,7 +3803,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:18</t>
+          <t>26/05/2026 10:52</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -3815,12 +3811,12 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
+          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -3830,34 +3826,30 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
+          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:17</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>26/05/2026 10:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
+          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3859,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
+          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3877,20 +3869,24 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
+          <t>26/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
+          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3896,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
+          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -3910,7 +3906,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
+          <t>25/05/2026 19:40</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -3918,12 +3914,12 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
+          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3929,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3943,7 +3939,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:14</t>
+          <t>25/05/2026 17:18</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -3951,12 +3947,12 @@
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
+          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3962,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
+          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3976,20 +3972,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:13</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+          <t>25/05/2026 17:17</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
+          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
+          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:12</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -4017,12 +4017,12 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
+          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
+          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:54</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -4050,12 +4050,12 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
+          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
+          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:52</t>
+          <t>25/05/2026 17:14</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -4083,12 +4083,12 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
+          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 13:38</t>
+          <t>25/05/2026 17:13</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -4116,12 +4116,12 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
+          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
+          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 10:33</t>
+          <t>25/05/2026 17:12</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -4149,12 +4149,12 @@
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
+          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:29</t>
+          <t>22/05/2026 14:54</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -4182,12 +4182,12 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:23</t>
+          <t>22/05/2026 14:52</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -4215,12 +4215,12 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
+          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
+          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:20</t>
+          <t>22/05/2026 13:38</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -4248,12 +4248,12 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
+          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 16:08</t>
+          <t>22/05/2026 10:33</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -4281,12 +4281,12 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
+          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:46</t>
+          <t>22/05/2026 09:29</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -4314,12 +4314,12 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:34</t>
+          <t>22/05/2026 09:23</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -4347,12 +4347,12 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
+          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:26</t>
+          <t>22/05/2026 09:20</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -4380,12 +4380,12 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
+          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4405,24 +4405,20 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:21</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>21/05/2026 16:08</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
       <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
+          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4428,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4442,7 +4438,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:07</t>
+          <t>21/05/2026 15:46</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -4450,12 +4446,12 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4461,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4475,7 +4471,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:01</t>
+          <t>21/05/2026 15:34</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -4483,12 +4479,12 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4494,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
+          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4508,7 +4504,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 14:33</t>
+          <t>21/05/2026 15:26</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -4516,12 +4512,12 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
+          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4527,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4541,20 +4537,24 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 11:00</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr"/>
+          <t>21/05/2026 15:21</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
+          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 09:36</t>
+          <t>21/05/2026 15:07</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -4582,12 +4582,12 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
         </is>
       </c>
     </row>
@@ -4597,17 +4597,17 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 19:08</t>
+          <t>21/05/2026 15:01</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
+          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 17:08</t>
+          <t>21/05/2026 14:33</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -4648,12 +4648,12 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
+          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
+          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4673,24 +4673,20 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:57</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>21/05/2026 11:00</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4696,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
+          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4710,7 +4706,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:41</t>
+          <t>21/05/2026 09:36</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -4718,12 +4714,12 @@
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
+          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
         </is>
       </c>
     </row>
@@ -4733,17 +4729,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
+          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:37</t>
+          <t>20/05/2026 19:08</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -4751,12 +4747,12 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4762,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
+          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4776,7 +4772,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:02</t>
+          <t>20/05/2026 17:08</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -4784,12 +4780,12 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4795,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
+          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4809,20 +4805,24 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:46</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
+          <t>20/05/2026 16:57</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
+          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
+          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:33</t>
+          <t>20/05/2026 16:41</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
+          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
+          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:10</t>
+          <t>20/05/2026 09:37</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -4883,12 +4883,12 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
+          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
+          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 22:33</t>
+          <t>20/05/2026 09:02</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -4916,12 +4916,12 @@
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
+          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
+          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4941,24 +4941,20 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 17:19</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:46</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
+          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4964,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
+          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -4978,24 +4974,20 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
         </is>
       </c>
     </row>
@@ -5005,7 +4997,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
+          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5015,24 +5007,20 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:10</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
       <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5030,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
+          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -5052,7 +5040,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
+          <t>19/05/2026 22:33</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -5060,12 +5048,12 @@
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5063,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5085,20 +5073,24 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:14</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
+          <t>19/05/2026 17:19</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
+          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5100,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
+          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5118,20 +5110,24 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
+          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5137,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
+          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5151,24 +5147,24 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
+          <t>19/05/2026 15:15</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>TP.HCM</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5174,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
+          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5188,7 +5184,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 13:55</t>
+          <t>19/05/2026 15:15</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -5196,12 +5192,12 @@
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5207,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
+          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5221,7 +5217,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 11:40</t>
+          <t>19/05/2026 15:14</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -5229,12 +5225,12 @@
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5240,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
+          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5254,7 +5250,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 09:04</t>
+          <t>19/05/2026 15:04</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -5262,12 +5258,12 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
+          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5273,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
+          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5287,20 +5283,24 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 16:11</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
+          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
+          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 15:17</t>
+          <t>19/05/2026 13:55</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -5328,12 +5328,12 @@
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
         </is>
       </c>
     </row>
@@ -5343,17 +5343,17 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 14:51</t>
+          <t>19/05/2026 11:40</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -5361,12 +5361,12 @@
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
+          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 10:32</t>
+          <t>19/05/2026 09:04</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -5394,12 +5394,12 @@
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
+          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
+          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 09:07</t>
+          <t>18/05/2026 16:11</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -5427,12 +5427,12 @@
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
+          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
+          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:30</t>
+          <t>18/05/2026 15:17</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr"/>
@@ -5460,12 +5460,12 @@
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
+          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
         </is>
       </c>
     </row>
@@ -5475,17 +5475,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
+          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:22</t>
+          <t>18/05/2026 14:51</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -5493,12 +5493,12 @@
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
+          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
+          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 20:09</t>
+          <t>18/05/2026 10:32</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -5526,12 +5526,12 @@
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
+          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
+          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -5551,24 +5551,20 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 17:30</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>18/05/2026 09:07</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
+          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5574,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
+          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5588,7 +5584,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:11</t>
+          <t>16/05/2026 09:30</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -5596,12 +5592,12 @@
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
+          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5607,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
+          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -5621,7 +5617,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:08</t>
+          <t>16/05/2026 09:22</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -5629,12 +5625,12 @@
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5640,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
+          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -5654,7 +5650,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 20:09</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -5662,12 +5658,12 @@
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5673,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
+          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -5687,20 +5683,24 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr"/>
+          <t>15/05/2026 17:30</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
+          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
+          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:11</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -5728,12 +5728,12 @@
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
+          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
+          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:08</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -5761,12 +5761,12 @@
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
+          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
+          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:54</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -5794,12 +5794,12 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
+          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
+          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:42</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -5827,12 +5827,12 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
+          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
+          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:12</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -5860,12 +5860,12 @@
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
+          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
+          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 08:55</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -5893,12 +5893,12 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
+          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
         </is>
       </c>
     </row>
@@ -5908,17 +5908,17 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 19:35</t>
+          <t>15/05/2026 09:54</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -5926,12 +5926,12 @@
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 13:42</t>
+          <t>15/05/2026 09:42</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -5959,12 +5959,12 @@
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
+          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
+          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:01</t>
+          <t>15/05/2026 09:12</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -5992,12 +5992,12 @@
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:00</t>
+          <t>15/05/2026 08:55</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -6025,12 +6025,12 @@
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 16:35</t>
+          <t>14/05/2026 19:35</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -6058,12 +6058,12 @@
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
+          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 14:34</t>
+          <t>14/05/2026 13:42</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -6091,12 +6091,12 @@
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
+          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
+          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 13:24</t>
+          <t>13/05/2026 17:01</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -6124,12 +6124,12 @@
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
+          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:59</t>
+          <t>13/05/2026 17:00</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -6157,12 +6157,12 @@
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
+          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6172,17 +6172,17 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
+          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:33</t>
+          <t>13/05/2026 16:35</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -6190,12 +6190,12 @@
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
+          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
+          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:23</t>
+          <t>13/05/2026 14:34</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -6223,12 +6223,12 @@
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
+          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
+          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:12</t>
+          <t>13/05/2026 13:24</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -6256,12 +6256,12 @@
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
+          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
+          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -6281,24 +6281,20 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026 11:29</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>13/05/2026 09:59</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
       <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
+          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6308,17 +6304,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026 19:37</t>
+          <t>13/05/2026 09:33</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -6326,12 +6322,12 @@
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6337,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026 10:31</t>
+          <t>13/05/2026 09:23</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -6359,12 +6355,12 @@
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6374,17 +6370,17 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026 01:28</t>
+          <t>13/05/2026 09:12</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -6392,12 +6388,12 @@
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6407,30 +6403,34 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>16/03/2026 11:15</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr"/>
+          <t>12/05/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>10/03/2026 09:00</t>
+          <t>06/05/2026 19:37</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -6458,12 +6458,12 @@
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
+          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -6483,24 +6483,20 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 19:52</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội, TP.HCM</t>
-        </is>
-      </c>
+          <t>05/05/2026 10:31</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
       <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -6510,30 +6506,30 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Quy Nhơn</t>
+          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:44</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>10/04/2026 01:28</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6539,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Đà Nẵng</t>
+          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -6553,20 +6549,20 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:37</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>16/03/2026 11:15</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -6576,34 +6572,30 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
+          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:45</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>10/03/2026 09:00</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
+          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -6613,30 +6605,34 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Đà Lạt</t>
+          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:27</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr"/>
+          <t>09/03/2026 19:52</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội, TP.HCM</t>
+        </is>
+      </c>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
+          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6642,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Thanh Hóa</t>
+          <t>FPTU Open Day Quy Nhơn</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -6656,20 +6652,20 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>05/02/2026 09:57</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr"/>
+          <t>03/03/2026 09:44</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
         </is>
       </c>
     </row>
@@ -6679,30 +6675,30 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
+          <t>FPTU Open Day Đà Nẵng</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>04/02/2026 10:54</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr"/>
+          <t>03/03/2026 09:37</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
         </is>
       </c>
     </row>
@@ -6712,30 +6708,34 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:48</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr"/>
+          <t>02/03/2026 09:45</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
         </is>
       </c>
     </row>
@@ -6745,17 +6745,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
+          <t>FPTU Open Day tại Đà Lạt</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:47</t>
+          <t>02/03/2026 09:27</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -6763,12 +6763,12 @@
       <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
+          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
         </is>
       </c>
     </row>
@@ -6778,17 +6778,17 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
+          <t>FPTU Open Day tại Thanh Hóa</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 11:04</t>
+          <t>05/02/2026 09:57</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -6796,12 +6796,12 @@
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -6821,24 +6821,20 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>26/01/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>04/02/2026 10:54</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -6848,34 +6844,30 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 16:45</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>02/02/2026 16:48</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -6885,34 +6877,30 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 10:38</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>02/02/2026 16:47</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6910,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -6932,7 +6920,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>20/01/2026 19:51</t>
+          <t>02/02/2026 11:04</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -6940,12 +6928,12 @@
       <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
         </is>
       </c>
     </row>
@@ -6955,28 +6943,172 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>28/12/2025 18:24</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr"/>
+          <t>26/01/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
+          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 16:45</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 10:38</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>20/01/2026 19:51</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>28/12/2025 18:24</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
           <t>Ngày 2/11, sự kiện “Homecoming 2025” của Trường Đại học FPT đã diễn ra đầy cảm xúc với sự góp mặt của 400 cựu sinh viên của gần 20 thế hệ, từ khoá đầu tiên từ khi thành lập trường tới nay. Không chỉ là nơi để mọi người cùng tề tựu, sự kiện đã [&amp;#8230;]</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>https://daihoc.fpt.edu.vn/event/400-cuu-sinh-vien-tu-nhieu-the-he-fptu-hoi-ngo-tai-su-kien-homecoming-2025/</t>
         </is>
@@ -7062,7 +7194,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7072,7 +7204,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -7080,12 +7212,12 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7227,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7105,7 +7237,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -7113,12 +7245,12 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7260,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7138,24 +7270,20 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>30/06/2026 13:48</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7293,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7175,7 +7303,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -7183,12 +7311,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7326,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7208,7 +7336,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>26/06/2026 10:57</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -7216,12 +7344,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7359,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7241,7 +7369,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -7249,12 +7377,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7392,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7274,20 +7402,24 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7429,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7307,24 +7439,20 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>24/06/2026 07:01</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7462,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7344,7 +7472,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -7352,12 +7480,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7495,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7377,7 +7505,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -7385,12 +7513,12 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -7400,17 +7528,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -7418,12 +7546,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7561,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7443,20 +7571,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7598,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7476,7 +7608,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -7484,12 +7616,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7631,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7509,7 +7641,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -7517,12 +7649,12 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -7532,17 +7664,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -7550,12 +7682,12 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7697,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7575,7 +7707,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>15/06/2026 09:13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -7583,12 +7715,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7730,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
+          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7608,7 +7740,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 10:20</t>
+          <t>15/06/2026 08:52</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -7616,12 +7748,12 @@
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7763,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
+          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7641,7 +7773,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:46</t>
+          <t>14/06/2026 07:23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -7649,12 +7781,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
+          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7796,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
+          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7674,7 +7806,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:22</t>
+          <t>14/06/2026 07:06</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -7682,12 +7814,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
+          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7829,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
+          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -7707,7 +7839,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 19:15</t>
+          <t>14/06/2026 05:48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -7715,12 +7847,12 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
+          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
         </is>
       </c>
     </row>

--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -608,12 +608,12 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -641,12 +641,12 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -707,12 +707,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -740,12 +740,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>30/06/2026 20:38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -773,12 +773,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -798,24 +798,20 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>30/06/2026 13:48</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -825,7 +821,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -835,20 +831,24 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -876,12 +876,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>26/06/2026 10:57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -909,12 +909,12 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -942,12 +942,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -967,24 +967,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
+          <t>24/06/2026 20:14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1012,12 +1012,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1045,12 +1045,12 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1078,12 +1078,12 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1111,12 +1111,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1136,20 +1136,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1169,7 +1173,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1177,12 +1181,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1210,12 +1214,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -1225,17 +1229,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1243,12 +1247,12 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1262,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
+          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1268,7 +1272,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 10:20</t>
+          <t>15/06/2026 09:13</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1276,12 +1280,12 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
+          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1295,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
+          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1301,7 +1305,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:46</t>
+          <t>15/06/2026 08:52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1309,12 +1313,12 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1328,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
+          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1334,7 +1338,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:22</t>
+          <t>14/06/2026 07:23</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1342,12 +1346,12 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
+          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1361,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
+          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1367,7 +1371,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 19:15</t>
+          <t>14/06/2026 07:06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1375,12 +1379,12 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
+          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1394,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
+          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1400,7 +1404,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 09:12</t>
+          <t>14/06/2026 05:48</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1408,12 +1412,12 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
+          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1427,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
+          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1433,7 +1437,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 08:17</t>
+          <t>13/06/2026 10:20</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1441,12 +1445,12 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
+          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1460,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
+          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1466,24 +1470,20 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:52</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>13/06/2026 09:46</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
+          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1503,24 +1503,20 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:38</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>13/06/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1526,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
+          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1540,24 +1536,20 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 12:01</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 19:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
+          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1559,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
+          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1577,7 +1569,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 10:50</t>
+          <t>12/06/2026 09:12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1585,12 +1577,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
+          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1592,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
+          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1610,7 +1602,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:59</t>
+          <t>12/06/2026 08:17</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1618,12 +1610,12 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
+          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1625,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
+          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1643,20 +1635,24 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:29</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:52</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
+          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1662,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
+          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1676,20 +1672,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:50</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:38</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
+          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
+          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1709,20 +1709,24 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 17:11</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+          <t>11/06/2026 12:01</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
+          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
+          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1742,7 +1746,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 16:59</t>
+          <t>11/06/2026 10:50</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1750,12 +1754,12 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
+          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1769,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
+          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1775,7 +1779,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 13:44</t>
+          <t>11/06/2026 09:59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -1783,12 +1787,12 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
+          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1802,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
+          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1808,7 +1812,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 10:42</t>
+          <t>11/06/2026 09:29</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -1816,12 +1820,12 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
+          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
+          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1841,7 +1845,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>10/06/2026 09:50</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1849,12 +1853,12 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
+          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1868,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
+          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1874,7 +1878,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 17:11</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1882,12 +1886,12 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
+          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1901,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
+          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1907,7 +1911,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 16:59</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1915,12 +1919,12 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1934,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
+          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1940,7 +1944,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 13:44</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1948,12 +1952,12 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
+          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1967,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1973,7 +1977,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 10:42</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1981,12 +1985,12 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
+          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2000,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
+          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2006,7 +2010,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2014,12 +2018,12 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
+          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2033,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
+          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2039,7 +2043,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2047,12 +2051,12 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2066,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
+          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2072,7 +2076,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:19</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2080,12 +2084,12 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
+          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2099,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
+          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2113,12 +2117,12 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2132,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
+          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2138,7 +2142,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2146,12 +2150,12 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
+          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -2161,17 +2165,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2179,12 +2183,12 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2198,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
+          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2204,24 +2208,20 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 22:25</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
+          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
+          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 07:22</t>
+          <t>09/06/2026 09:19</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2249,12 +2249,12 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
+          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
+          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 18:09</t>
+          <t>09/06/2026 09:18</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2282,12 +2282,12 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
+          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
+          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2307,24 +2307,20 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 13:00</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:18</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
+          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
         </is>
       </c>
     </row>
@@ -2334,34 +2330,30 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 12:25</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>08/06/2026 14:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2363,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2381,20 +2373,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 14:02</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
+          <t>06/06/2026 22:25</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
+          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2400,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
+          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2414,7 +2410,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:30</t>
+          <t>06/06/2026 07:22</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2422,12 +2418,12 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2433,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
+          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2447,24 +2443,20 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:11</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>05/06/2026 18:09</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
+          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
         </is>
       </c>
     </row>
@@ -2474,30 +2466,34 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:29</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+          <t>05/06/2026 13:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2503,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
+          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2517,24 +2513,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:21</t>
+          <t>05/06/2026 12:25</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Cần Thơ</t>
+          <t>Quy Nhơn</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
+          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2540,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
+          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2554,7 +2550,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:53</t>
+          <t>04/06/2026 14:02</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2562,12 +2558,12 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
+          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2573,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
+          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2587,7 +2583,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:51</t>
+          <t>04/06/2026 09:30</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -2595,12 +2591,12 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
+          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2606,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
+          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2620,20 +2616,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:22</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+          <t>04/06/2026 09:11</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
+          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2643,17 +2643,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
+          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:55</t>
+          <t>03/06/2026 14:29</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -2661,12 +2661,12 @@
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
+          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
+          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2686,20 +2686,24 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:52</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>03/06/2026 14:21</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
+          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2713,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
+          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:21</t>
+          <t>02/06/2026 19:53</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -2727,12 +2731,12 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
+          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2746,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
+          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2752,7 +2756,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 19:51</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -2760,12 +2764,12 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
+          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2785,7 +2789,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 19:22</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -2793,12 +2797,12 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
+          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2812,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
+          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2818,7 +2822,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 16:55</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -2826,12 +2830,12 @@
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2845,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
+          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2851,7 +2855,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 16:52</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2859,12 +2863,12 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
+          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2878,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2884,7 +2888,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:21</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2892,12 +2896,12 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
+          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2911,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
+          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2917,7 +2921,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:57</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2925,12 +2929,12 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
+          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2944,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
+          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2950,7 +2954,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:55</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2958,12 +2962,12 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
+          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2977,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
+          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2983,7 +2987,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:54</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -2991,12 +2995,12 @@
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
+          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3010,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
+          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3016,7 +3020,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:41</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3024,12 +3028,12 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
+          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3043,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
+          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 13:31</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -3057,12 +3061,12 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
+          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3076,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
+          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3082,7 +3086,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:38</t>
+          <t>02/06/2026 09:57</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -3090,12 +3094,12 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
+          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3109,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3115,7 +3119,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:28</t>
+          <t>02/06/2026 09:55</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -3123,12 +3127,12 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3142,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
+          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3148,7 +3152,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:19</t>
+          <t>02/06/2026 09:54</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -3156,12 +3160,12 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3175,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
+          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3181,7 +3185,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:09</t>
+          <t>02/06/2026 09:41</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -3189,12 +3193,12 @@
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -3204,34 +3208,30 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
+          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:01</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 13:31</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
+          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:52</t>
+          <t>01/06/2026 00:38</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3259,12 +3259,12 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
+          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:43</t>
+          <t>01/06/2026 00:28</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -3292,12 +3292,12 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
+          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
+          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3317,24 +3317,20 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:33</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 00:19</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
       <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
+          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3340,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
+          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3354,7 +3350,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 21:33</t>
+          <t>01/06/2026 00:09</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3362,12 +3358,12 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
+          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
         </is>
       </c>
     </row>
@@ -3377,34 +3373,34 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
+          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 20:49</t>
+          <t>01/06/2026 00:01</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>TP.HCM</t>
+          <t>Cần Thơ</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
+          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
         </is>
       </c>
     </row>
@@ -3414,17 +3410,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
+          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 13:42</t>
+          <t>31/05/2026 23:52</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -3432,12 +3428,12 @@
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
+          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3443,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
+          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 20:31</t>
+          <t>31/05/2026 23:43</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -3465,12 +3461,12 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
+          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3476,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
+          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3490,20 +3486,24 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:51</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
+          <t>31/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
+          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
+          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:34</t>
+          <t>31/05/2026 21:33</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -3531,12 +3531,12 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
+          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
+          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
         </is>
       </c>
     </row>
@@ -3546,34 +3546,34 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
+          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:30</t>
+          <t>30/05/2026 20:49</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Quy Nhơn</t>
+          <t>TP.HCM</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
+          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
+          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026 10:33</t>
+          <t>30/05/2026 13:42</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -3601,12 +3601,12 @@
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
+          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3616,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
+          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 11:02</t>
+          <t>29/05/2026 20:31</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -3634,12 +3634,12 @@
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
+          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
+          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3659,24 +3659,20 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:38</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>29/05/2026 08:51</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
+          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3682,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3696,24 +3692,20 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:32</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>29/05/2026 08:34</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
         </is>
       </c>
     </row>
@@ -3723,30 +3715,34 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
+          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:09</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr"/>
+          <t>29/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
+          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -3756,34 +3752,30 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:11</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>28/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
+          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3785,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
+          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3803,7 +3795,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:52</t>
+          <t>27/05/2026 11:02</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -3811,12 +3803,12 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
+          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
         </is>
       </c>
     </row>
@@ -3826,30 +3818,34 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
+          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr"/>
+          <t>27/05/2026 09:38</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
+          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3855,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3869,7 +3865,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 09:22</t>
+          <t>27/05/2026 09:32</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3881,12 +3877,12 @@
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
+          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3892,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
+          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 19:40</t>
+          <t>27/05/2026 09:09</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -3914,12 +3910,12 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
+          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3925,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
+          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3939,20 +3935,24 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:18</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
+          <t>26/05/2026 16:11</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
+          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
+          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3972,24 +3972,20 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:17</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>26/05/2026 10:52</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
+          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -3999,17 +3995,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
+          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
+          <t>26/05/2026 10:10</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -4017,12 +4013,12 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
+          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4028,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
+          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4042,20 +4038,24 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>26/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
+          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
+          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:14</t>
+          <t>25/05/2026 19:40</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -4083,12 +4083,12 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
+          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:13</t>
+          <t>25/05/2026 17:18</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -4116,12 +4116,12 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
+          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
+          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4141,20 +4141,24 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:12</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
+          <t>25/05/2026 17:17</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
+          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4168,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
+          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4174,7 +4178,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:54</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -4182,12 +4186,12 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
+          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4201,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
+          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4207,7 +4211,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:52</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -4215,12 +4219,12 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
+          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4234,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
+          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4240,7 +4244,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 13:38</t>
+          <t>25/05/2026 17:14</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -4248,12 +4252,12 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4267,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
+          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4273,7 +4277,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 10:33</t>
+          <t>25/05/2026 17:13</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -4281,12 +4285,12 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
+          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4300,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
+          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4306,7 +4310,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:29</t>
+          <t>25/05/2026 17:12</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -4314,12 +4318,12 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4333,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4339,7 +4343,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:23</t>
+          <t>22/05/2026 14:54</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -4347,12 +4351,12 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4366,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
+          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4372,7 +4376,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:20</t>
+          <t>22/05/2026 14:52</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -4380,12 +4384,12 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
+          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4399,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
+          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4405,7 +4409,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 16:08</t>
+          <t>22/05/2026 13:38</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -4413,12 +4417,12 @@
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4432,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4438,7 +4442,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:46</t>
+          <t>22/05/2026 10:33</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -4446,12 +4450,12 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
+          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4471,7 +4475,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:34</t>
+          <t>22/05/2026 09:29</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -4479,12 +4483,12 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4498,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4504,7 +4508,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:26</t>
+          <t>22/05/2026 09:23</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -4512,12 +4516,12 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4531,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
+          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4537,24 +4541,20 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:21</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>22/05/2026 09:20</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
       <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
+          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:07</t>
+          <t>21/05/2026 16:08</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -4582,12 +4582,12 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
+          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:01</t>
+          <t>21/05/2026 15:46</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 14:33</t>
+          <t>21/05/2026 15:34</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -4648,12 +4648,12 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 11:00</t>
+          <t>21/05/2026 15:26</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -4681,12 +4681,12 @@
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
+          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4706,20 +4706,24 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 09:36</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
+          <t>21/05/2026 15:21</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
+          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4729,17 +4733,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 19:08</t>
+          <t>21/05/2026 15:07</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -4747,12 +4751,12 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4766,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4772,7 +4776,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 17:08</t>
+          <t>21/05/2026 15:01</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -4780,12 +4784,12 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4799,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
+          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4805,24 +4809,20 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:57</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>21/05/2026 14:33</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
+          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
+          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:41</t>
+          <t>21/05/2026 11:00</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
+          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:37</t>
+          <t>21/05/2026 09:36</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -4883,12 +4883,12 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
+          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
         </is>
       </c>
     </row>
@@ -4898,17 +4898,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
+          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:02</t>
+          <t>20/05/2026 19:08</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -4916,12 +4916,12 @@
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
+          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:46</t>
+          <t>20/05/2026 17:08</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -4949,12 +4949,12 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
+          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -4974,20 +4974,24 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:33</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr"/>
+          <t>20/05/2026 16:57</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
+          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -4997,7 +5001,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
+          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5007,7 +5011,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:10</t>
+          <t>20/05/2026 16:41</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -5015,12 +5019,12 @@
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
+          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5034,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
+          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -5040,7 +5044,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 22:33</t>
+          <t>20/05/2026 09:37</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -5048,12 +5052,12 @@
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
+          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5067,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
+          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5073,24 +5077,20 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 17:19</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>20/05/2026 09:02</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
+          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
+          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5110,24 +5110,20 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:46</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
+          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5133,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
+          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5147,24 +5143,20 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5166,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
+          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5184,7 +5176,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
+          <t>19/05/2026 23:10</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -5192,12 +5184,12 @@
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5199,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
+          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5217,7 +5209,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:14</t>
+          <t>19/05/2026 22:33</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -5225,12 +5217,12 @@
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5232,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5250,20 +5242,24 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr"/>
+          <t>19/05/2026 17:19</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
+          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5269,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
+          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5283,24 +5279,24 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
+          <t>19/05/2026 15:15</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>TP.HCM</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
+          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5306,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
+          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5320,20 +5316,24 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 13:55</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
+          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 11:40</t>
+          <t>19/05/2026 15:15</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -5361,12 +5361,12 @@
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
+          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 09:04</t>
+          <t>19/05/2026 15:14</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr"/>
@@ -5394,12 +5394,12 @@
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
+          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 16:11</t>
+          <t>19/05/2026 15:04</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr"/>
@@ -5427,12 +5427,12 @@
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
+          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
+          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -5452,20 +5452,24 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 15:17</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
+          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
         </is>
       </c>
     </row>
@@ -5475,17 +5479,17 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 14:51</t>
+          <t>19/05/2026 13:55</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -5493,12 +5497,12 @@
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5512,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
+          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -5518,7 +5522,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 10:32</t>
+          <t>19/05/2026 11:40</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -5526,12 +5530,12 @@
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
+          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5545,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
+          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -5551,7 +5555,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 09:07</t>
+          <t>19/05/2026 09:04</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -5559,12 +5563,12 @@
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
+          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5578,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
+          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5584,7 +5588,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:30</t>
+          <t>18/05/2026 16:11</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -5592,12 +5596,12 @@
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
+          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5611,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
+          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -5617,7 +5621,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:22</t>
+          <t>18/05/2026 15:17</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -5625,12 +5629,12 @@
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
+          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
+          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
         </is>
       </c>
     </row>
@@ -5640,17 +5644,17 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
+          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 20:09</t>
+          <t>18/05/2026 14:51</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -5658,12 +5662,12 @@
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
+          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5677,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
+          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -5683,24 +5687,20 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 17:30</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>18/05/2026 10:32</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
+          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
+          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:11</t>
+          <t>18/05/2026 09:07</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -5728,12 +5728,12 @@
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
+          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
+          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:08</t>
+          <t>16/05/2026 09:30</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -5761,12 +5761,12 @@
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
+          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
+          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>16/05/2026 09:22</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -5794,12 +5794,12 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
+          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 20:09</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -5827,12 +5827,12 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
+          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -5852,20 +5852,24 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr"/>
+          <t>15/05/2026 17:30</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
+          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5879,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
+          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -5885,7 +5889,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:11</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -5893,12 +5897,12 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
+          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5912,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
+          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -5918,7 +5922,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:54</t>
+          <t>15/05/2026 11:08</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -5926,12 +5930,12 @@
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
+          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5945,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
+          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -5951,7 +5955,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:42</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -5959,12 +5963,12 @@
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
+          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5978,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
+          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5984,7 +5988,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:12</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -5992,12 +5996,12 @@
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
+          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6011,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
+          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6017,7 +6021,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 08:55</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -6025,12 +6029,12 @@
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
+          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
         </is>
       </c>
     </row>
@@ -6040,17 +6044,17 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 19:35</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -6058,12 +6062,12 @@
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
         </is>
       </c>
     </row>
@@ -6073,7 +6077,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6083,7 +6087,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 13:42</t>
+          <t>15/05/2026 09:54</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -6091,12 +6095,12 @@
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
+          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6110,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
+          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -6116,7 +6120,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:01</t>
+          <t>15/05/2026 09:42</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -6124,12 +6128,12 @@
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6143,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6149,7 +6153,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:00</t>
+          <t>15/05/2026 09:12</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -6157,12 +6161,12 @@
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
+          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6172,17 +6176,17 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 16:35</t>
+          <t>15/05/2026 08:55</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -6190,12 +6194,12 @@
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6205,17 +6209,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
+          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 14:34</t>
+          <t>14/05/2026 19:35</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -6223,12 +6227,12 @@
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
+          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6248,7 +6252,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 13:24</t>
+          <t>14/05/2026 13:42</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -6256,12 +6260,12 @@
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
+          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6275,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
+          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -6281,7 +6285,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:59</t>
+          <t>13/05/2026 17:01</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -6289,12 +6293,12 @@
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6308,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
+          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -6314,7 +6318,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:33</t>
+          <t>13/05/2026 17:00</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -6322,12 +6326,12 @@
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
+          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6337,17 +6341,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
+          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:23</t>
+          <t>13/05/2026 16:35</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -6355,12 +6359,12 @@
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
+          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6374,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
+          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -6380,7 +6384,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:12</t>
+          <t>13/05/2026 14:34</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -6388,12 +6392,12 @@
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
+          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6407,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
+          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -6413,24 +6417,20 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026 11:29</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>13/05/2026 13:24</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
+          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
         </is>
       </c>
     </row>
@@ -6440,17 +6440,17 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026 19:37</t>
+          <t>13/05/2026 09:59</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -6458,12 +6458,12 @@
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6473,17 +6473,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026 10:31</t>
+          <t>13/05/2026 09:33</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -6491,12 +6491,12 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6506,17 +6506,17 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026 01:28</t>
+          <t>13/05/2026 09:23</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -6524,12 +6524,12 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6539,17 +6539,17 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>16/03/2026 11:15</t>
+          <t>13/05/2026 09:12</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -6557,12 +6557,12 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6572,30 +6572,34 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>10/03/2026 09:00</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr"/>
+          <t>12/05/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6609,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
+          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -6615,24 +6619,20 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 19:52</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội, TP.HCM</t>
-        </is>
-      </c>
+          <t>06/05/2026 19:37</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6642,30 +6642,30 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Quy Nhơn</t>
+          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:44</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>05/05/2026 10:31</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -6675,30 +6675,30 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Đà Nẵng</t>
+          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:37</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>10/04/2026 01:28</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
+          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -6718,24 +6718,20 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:45</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>16/03/2026 11:15</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
+          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -6745,17 +6741,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Đà Lạt</t>
+          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:27</t>
+          <t>10/03/2026 09:00</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -6763,12 +6759,12 @@
       <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
+          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -6778,30 +6774,34 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Thanh Hóa</t>
+          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>05/02/2026 09:57</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr"/>
+          <t>09/03/2026 19:52</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội, TP.HCM</t>
+        </is>
+      </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
+          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
         </is>
       </c>
     </row>
@@ -6811,30 +6811,30 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
+          <t>FPTU Open Day Quy Nhơn</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>04/02/2026 10:54</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr"/>
+          <t>03/03/2026 09:44</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
         </is>
       </c>
     </row>
@@ -6844,30 +6844,30 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
+          <t>FPTU Open Day Đà Nẵng</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:48</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr"/>
+          <t>03/03/2026 09:37</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
         </is>
       </c>
     </row>
@@ -6877,30 +6877,34 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:47</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr"/>
+          <t>02/03/2026 09:45</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
         </is>
       </c>
     </row>
@@ -6910,17 +6914,17 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
+          <t>FPTU Open Day tại Đà Lạt</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 11:04</t>
+          <t>02/03/2026 09:27</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr"/>
@@ -6928,12 +6932,12 @@
       <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
         </is>
       </c>
     </row>
@@ -6943,34 +6947,30 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+          <t>FPTU Open Day tại Thanh Hóa</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>26/01/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>05/02/2026 09:57</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
         </is>
       </c>
     </row>
@@ -6980,34 +6980,30 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 16:45</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>04/02/2026 10:54</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -7017,34 +7013,30 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 10:38</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>02/02/2026 16:48</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7046,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -7064,7 +7056,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>20/01/2026 19:51</t>
+          <t>02/02/2026 16:47</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -7072,12 +7064,12 @@
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7087,17 +7079,17 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>28/12/2025 18:24</t>
+          <t>02/02/2026 11:04</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -7105,10 +7097,187 @@
       <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
+          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>26/01/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 16:45</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 10:38</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>20/01/2026 19:51</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>28/12/2025 18:24</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
           <t>Ngày 2/11, sự kiện “Homecoming 2025” của Trường Đại học FPT đã diễn ra đầy cảm xúc với sự góp mặt của 400 cựu sinh viên của gần 20 thế hệ, từ khoá đầu tiên từ khi thành lập trường tới nay. Không chỉ là nơi để mọi người cùng tề tựu, sự kiện đã [&amp;#8230;]</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>https://daihoc.fpt.edu.vn/event/400-cuu-sinh-vien-tu-nhieu-the-he-fptu-hoi-ngo-tai-su-kien-homecoming-2025/</t>
         </is>
@@ -7194,7 +7363,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7204,7 +7373,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -7212,12 +7381,12 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7396,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7237,7 +7406,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -7245,12 +7414,12 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7429,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7270,7 +7439,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -7278,12 +7447,12 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7462,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7303,7 +7472,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -7311,12 +7480,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7495,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7336,7 +7505,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -7344,12 +7513,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7528,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7369,7 +7538,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>30/06/2026 20:38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -7377,12 +7546,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7392,7 +7561,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7402,24 +7571,20 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>30/06/2026 13:48</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7594,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7439,20 +7604,24 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7631,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7472,7 +7641,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -7480,12 +7649,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7664,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7505,7 +7674,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>26/06/2026 10:57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -7513,12 +7682,12 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7697,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7538,7 +7707,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -7546,12 +7715,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7730,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7571,24 +7740,24 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
+          <t>24/06/2026 20:14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7767,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7608,7 +7777,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -7616,12 +7785,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7800,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7641,7 +7810,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -7649,12 +7818,12 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -7664,17 +7833,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -7682,12 +7851,12 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7866,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7707,7 +7876,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -7715,12 +7884,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7899,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -7740,20 +7909,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7936,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7773,7 +7946,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -7781,12 +7954,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7969,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7806,7 +7979,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -7814,12 +7987,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -7829,17 +8002,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -7847,12 +8020,12 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>

--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/07/2026 14:00</t>
+          <t>03/07/2026 09:57</t>
         </is>
       </c>
     </row>
@@ -487,11 +487,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
+          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 14:00</t>
+          <t>03/07/2026 09:57</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -608,12 +608,12 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
+          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 11:34</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -641,12 +641,12 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -707,12 +707,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -740,12 +740,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 20:38</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -773,12 +773,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -806,12 +806,12 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -831,24 +831,20 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 16:38</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>30/06/2026 20:38</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -858,7 +854,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -868,7 +864,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
+          <t>30/06/2026 13:48</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -876,12 +872,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -891,7 +887,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -901,20 +897,24 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -942,12 +942,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -967,24 +967,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>26/06/2026 10:57</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -994,7 +990,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1004,7 +1000,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1012,12 +1008,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1023,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,20 +1033,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1078,12 +1078,12 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1111,12 +1111,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1126,34 +1126,30 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>23/06/2026 11:20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1159,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1173,7 +1169,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1181,12 +1177,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1206,7 +1202,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1214,12 +1210,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -1229,30 +1225,34 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1280,12 +1280,12 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1313,12 +1313,12 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -1328,17 +1328,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>15/06/2026 09:13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1379,12 +1379,12 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>15/06/2026 08:52</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1412,12 +1412,12 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
+          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 10:20</t>
+          <t>14/06/2026 07:23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1445,12 +1445,12 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
+          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
+          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:46</t>
+          <t>14/06/2026 07:06</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1478,12 +1478,12 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
+          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
+          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:22</t>
+          <t>14/06/2026 05:48</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1511,12 +1511,12 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
+          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
+          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 19:15</t>
+          <t>13/06/2026 10:20</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1544,12 +1544,12 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
+          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
+          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 09:12</t>
+          <t>13/06/2026 09:46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
+          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 08:17</t>
+          <t>13/06/2026 09:22</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1610,12 +1610,12 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
+          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1635,24 +1635,20 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:52</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 19:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
+          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1658,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
+          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1672,24 +1668,20 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:38</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 09:12</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
+          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1691,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
+          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1709,24 +1701,20 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 12:01</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 08:17</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
+          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1724,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
+          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1746,20 +1734,24 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 10:50</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:52</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
+          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1761,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
+          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1779,20 +1771,24 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:59</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:38</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
+          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1798,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
+          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1812,20 +1808,24 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:29</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+          <t>11/06/2026 12:01</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
+          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
+          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:50</t>
+          <t>11/06/2026 10:50</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -1853,12 +1853,12 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
+          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
+          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 17:11</t>
+          <t>11/06/2026 09:59</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1886,12 +1886,12 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
+          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
+          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 16:59</t>
+          <t>11/06/2026 09:29</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1919,12 +1919,12 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
+          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
+          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 13:44</t>
+          <t>10/06/2026 09:50</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1952,12 +1952,12 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
+          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
+          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 10:42</t>
+          <t>09/06/2026 17:11</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1985,12 +1985,12 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
+          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
+          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 16:59</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2018,12 +2018,12 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
+          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
+          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 13:44</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2051,12 +2051,12 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
+          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 10:42</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2084,12 +2084,12 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
+          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
+          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
+          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2150,12 +2150,12 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
+          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2183,12 +2183,12 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
+          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
+          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -2216,12 +2216,12 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
+          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:19</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2249,12 +2249,12 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
+          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
+          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2282,12 +2282,12 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
+          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
+          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2315,12 +2315,12 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
+          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2330,17 +2330,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>09/06/2026 09:19</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2348,12 +2348,12 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
+          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2373,24 +2373,20 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 22:25</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:18</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
+          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2396,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
+          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2410,7 +2406,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 07:22</t>
+          <t>09/06/2026 09:18</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2418,12 +2414,12 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
+          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
         </is>
       </c>
     </row>
@@ -2433,17 +2429,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 18:09</t>
+          <t>08/06/2026 14:55</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2451,12 +2447,12 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2462,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2476,24 +2472,24 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 13:00</t>
+          <t>06/06/2026 22:25</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Quy Nhơn</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
+          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2499,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
+          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2513,24 +2509,20 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 12:25</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>06/06/2026 07:22</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2532,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
+          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2550,7 +2542,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 14:02</t>
+          <t>05/06/2026 18:09</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2558,12 +2550,12 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
+          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2565,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
+          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2583,20 +2575,24 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:30</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>05/06/2026 13:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
+          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2602,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
+          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2616,24 +2612,24 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:11</t>
+          <t>05/06/2026 12:25</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Quy Nhơn</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
+          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
         </is>
       </c>
     </row>
@@ -2643,17 +2639,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:29</t>
+          <t>04/06/2026 14:02</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -2661,12 +2657,12 @@
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2672,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
+          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2686,24 +2682,20 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:21</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>04/06/2026 09:30</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
+          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2705,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
+          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2723,20 +2715,24 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:53</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+          <t>04/06/2026 09:11</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
+          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2746,17 +2742,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
+          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:51</t>
+          <t>03/06/2026 14:29</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -2764,12 +2760,12 @@
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
+          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2775,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
+          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2789,20 +2785,24 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:22</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+          <t>03/06/2026 14:21</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
+          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
+          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:55</t>
+          <t>02/06/2026 19:53</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -2830,12 +2830,12 @@
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
+          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
+          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:52</t>
+          <t>02/06/2026 19:51</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2863,12 +2863,12 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
+          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:21</t>
+          <t>02/06/2026 19:22</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2896,12 +2896,12 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
+          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
+          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 16:55</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2929,12 +2929,12 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
+          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
+          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 16:52</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
+          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:21</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -2995,12 +2995,12 @@
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
+          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3028,12 +3028,12 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
+          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
+          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -3061,12 +3061,12 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
+          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
+          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:57</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -3094,12 +3094,12 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
+          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
+          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:55</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -3127,12 +3127,12 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
+          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
+          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:54</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -3160,12 +3160,12 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
+          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
+          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:41</t>
+          <t>02/06/2026 09:57</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -3193,12 +3193,12 @@
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
+          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 13:31</t>
+          <t>02/06/2026 09:55</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -3226,12 +3226,12 @@
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
+          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:38</t>
+          <t>02/06/2026 09:54</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3259,12 +3259,12 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
+          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:28</t>
+          <t>02/06/2026 09:41</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -3292,12 +3292,12 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
+          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:19</t>
+          <t>01/06/2026 13:31</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -3325,12 +3325,12 @@
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
+          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:09</t>
+          <t>01/06/2026 00:38</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3358,12 +3358,12 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
+          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3383,24 +3383,20 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:01</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 00:28</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
       <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
+          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3406,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
+          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3420,7 +3416,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:52</t>
+          <t>01/06/2026 00:19</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -3428,12 +3424,12 @@
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
+          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3439,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
+          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3453,7 +3449,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:43</t>
+          <t>01/06/2026 00:09</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -3461,12 +3457,12 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
+          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3472,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
+          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3486,7 +3482,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:33</t>
+          <t>01/06/2026 00:01</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3498,12 +3494,12 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
+          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3509,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
+          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3523,7 +3519,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 21:33</t>
+          <t>31/05/2026 23:52</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -3531,12 +3527,12 @@
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
+          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
         </is>
       </c>
     </row>
@@ -3546,34 +3542,30 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
+          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 20:49</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>31/05/2026 23:43</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
+          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3583,30 +3575,34 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
+          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 13:42</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
+          <t>31/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
+          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
         </is>
       </c>
     </row>
@@ -3616,17 +3612,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
+          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 20:31</t>
+          <t>31/05/2026 21:33</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -3634,12 +3630,12 @@
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
+          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
+          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
         </is>
       </c>
     </row>
@@ -3649,30 +3645,34 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
+          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:51</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr"/>
+          <t>30/05/2026 20:49</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
+          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -3682,17 +3682,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
+          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:34</t>
+          <t>30/05/2026 13:42</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -3700,12 +3700,12 @@
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
+          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
         </is>
       </c>
     </row>
@@ -3715,34 +3715,30 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
+          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:30</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>29/05/2026 20:31</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
       <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
+          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
         </is>
       </c>
     </row>
@@ -3752,17 +3748,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
+          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026 10:33</t>
+          <t>29/05/2026 08:51</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -3770,12 +3766,12 @@
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
+          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3795,7 +3791,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 11:02</t>
+          <t>29/05/2026 08:34</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -3803,12 +3799,12 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
+          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3814,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
+          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3828,24 +3824,24 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:38</t>
+          <t>29/05/2026 08:30</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Quy Nhơn</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
+          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -3855,34 +3851,30 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:32</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>28/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
+          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
         </is>
       </c>
     </row>
@@ -3892,17 +3884,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
+          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:09</t>
+          <t>27/05/2026 11:02</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -3910,12 +3902,12 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
+          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3917,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3935,7 +3927,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:11</t>
+          <t>27/05/2026 09:38</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3947,12 +3939,12 @@
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
+          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3954,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
+          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3972,20 +3964,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:52</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+          <t>27/05/2026 09:32</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
+          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3991,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
+          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4005,7 +4001,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:10</t>
+          <t>27/05/2026 09:09</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -4013,12 +4009,12 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
+          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4024,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4038,7 +4034,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 09:22</t>
+          <t>26/05/2026 16:11</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -4050,12 +4046,12 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
+          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4065,7 +4061,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
+          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4075,7 +4071,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 19:40</t>
+          <t>26/05/2026 10:52</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -4083,12 +4079,12 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
+          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4094,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
+          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:18</t>
+          <t>26/05/2026 10:10</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -4116,12 +4112,12 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
+          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4127,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
+          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4141,24 +4137,24 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:17</t>
+          <t>26/05/2026 09:22</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Cần Thơ</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
+          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4164,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
+          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4178,7 +4174,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
+          <t>25/05/2026 19:40</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -4186,12 +4182,12 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
+          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4197,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4211,7 +4207,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
+          <t>25/05/2026 17:18</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -4219,12 +4215,12 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
+          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4230,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
+          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4244,20 +4240,24 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:14</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>25/05/2026 17:17</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
+          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
+          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:13</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -4285,12 +4285,12 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
+          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
+          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:12</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -4318,12 +4318,12 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
+          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
+          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:54</t>
+          <t>25/05/2026 17:14</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -4351,12 +4351,12 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
+          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:52</t>
+          <t>25/05/2026 17:13</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -4384,12 +4384,12 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
+          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
+          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 13:38</t>
+          <t>25/05/2026 17:12</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -4417,12 +4417,12 @@
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
+          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 10:33</t>
+          <t>22/05/2026 14:54</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -4450,12 +4450,12 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
+          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:29</t>
+          <t>22/05/2026 14:52</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -4483,12 +4483,12 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
+          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:23</t>
+          <t>22/05/2026 13:38</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -4516,12 +4516,12 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
+          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:20</t>
+          <t>22/05/2026 10:33</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -4549,12 +4549,12 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
+          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 16:08</t>
+          <t>22/05/2026 09:29</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -4582,12 +4582,12 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:46</t>
+          <t>22/05/2026 09:23</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:34</t>
+          <t>22/05/2026 09:20</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -4648,12 +4648,12 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
+          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:26</t>
+          <t>21/05/2026 16:08</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -4681,12 +4681,12 @@
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
+          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4706,24 +4706,20 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:21</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>21/05/2026 15:46</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4729,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4743,7 +4739,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:07</t>
+          <t>21/05/2026 15:34</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -4751,12 +4747,12 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4762,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
+          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4776,7 +4772,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:01</t>
+          <t>21/05/2026 15:26</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -4784,12 +4780,12 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
+          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4795,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
+          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4809,20 +4805,24 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 14:33</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr"/>
+          <t>21/05/2026 15:21</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
+          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 11:00</t>
+          <t>21/05/2026 15:07</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr"/>
@@ -4850,12 +4850,12 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 09:36</t>
+          <t>21/05/2026 15:01</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -4883,12 +4883,12 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
         </is>
       </c>
     </row>
@@ -4898,17 +4898,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 19:08</t>
+          <t>21/05/2026 14:33</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -4916,12 +4916,12 @@
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
+          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 17:08</t>
+          <t>21/05/2026 11:00</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -4949,12 +4949,12 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
+          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -4974,24 +4974,20 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:57</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>21/05/2026 09:36</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
+          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
         </is>
       </c>
     </row>
@@ -5001,17 +4997,17 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
+          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:41</t>
+          <t>20/05/2026 19:08</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -5019,12 +5015,12 @@
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5030,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
+          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -5044,7 +5040,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:37</t>
+          <t>20/05/2026 17:08</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -5052,12 +5048,12 @@
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5063,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
+          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5077,20 +5073,24 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:02</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
+          <t>20/05/2026 16:57</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
+          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
+          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:46</t>
+          <t>20/05/2026 16:41</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
@@ -5118,12 +5118,12 @@
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
+          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
+          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:33</t>
+          <t>20/05/2026 09:37</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -5151,12 +5151,12 @@
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
+          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
+          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:10</t>
+          <t>20/05/2026 09:02</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -5184,12 +5184,12 @@
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
+          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
+          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 22:33</t>
+          <t>19/05/2026 23:46</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -5217,12 +5217,12 @@
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
+          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
+          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5242,24 +5242,20 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 17:19</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5265,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
+          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5279,24 +5275,20 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:10</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
       <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5298,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
+          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5316,24 +5308,20 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>19/05/2026 22:33</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5331,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -5353,20 +5341,24 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr"/>
+          <t>19/05/2026 17:19</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
+          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5368,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
+          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5386,20 +5378,24 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:14</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
+          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5405,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
+          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -5419,20 +5415,24 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
+          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -5452,24 +5452,20 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5475,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
+          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -5489,7 +5485,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 13:55</t>
+          <t>19/05/2026 15:14</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -5497,12 +5493,12 @@
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5508,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
+          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -5522,7 +5518,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 11:40</t>
+          <t>19/05/2026 15:04</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -5530,12 +5526,12 @@
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
+          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5541,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
+          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -5555,20 +5551,24 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 09:04</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
+          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
+          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 16:11</t>
+          <t>19/05/2026 13:55</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
@@ -5596,12 +5596,12 @@
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
+          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
+          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 15:17</t>
+          <t>19/05/2026 11:40</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -5629,12 +5629,12 @@
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
+          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
         </is>
       </c>
     </row>
@@ -5644,17 +5644,17 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 14:51</t>
+          <t>19/05/2026 09:04</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -5662,12 +5662,12 @@
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
+          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 10:32</t>
+          <t>18/05/2026 16:11</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -5695,12 +5695,12 @@
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
+          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
+          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 09:07</t>
+          <t>18/05/2026 15:17</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -5728,12 +5728,12 @@
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
+          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
+          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
         </is>
       </c>
     </row>
@@ -5743,17 +5743,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
+          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:30</t>
+          <t>18/05/2026 14:51</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -5761,12 +5761,12 @@
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
+          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
+          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:22</t>
+          <t>18/05/2026 10:32</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -5794,12 +5794,12 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
+          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
+          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 20:09</t>
+          <t>18/05/2026 09:07</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -5827,12 +5827,12 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
+          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
+          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -5852,24 +5852,20 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 17:30</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>16/05/2026 09:30</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
+          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5875,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
+          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -5889,7 +5885,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:11</t>
+          <t>16/05/2026 09:22</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -5897,12 +5893,12 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5908,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
+          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -5922,7 +5918,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:08</t>
+          <t>15/05/2026 20:09</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -5930,12 +5926,12 @@
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5941,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
+          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -5955,20 +5951,24 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr"/>
+          <t>15/05/2026 17:30</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
+          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
+          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:11</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
@@ -5996,12 +5996,12 @@
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
+          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
+          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:08</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -6029,12 +6029,12 @@
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
+          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
+          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
+          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
+          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:54</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -6095,12 +6095,12 @@
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
+          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
+          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:42</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -6128,12 +6128,12 @@
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
+          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
+          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:12</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
@@ -6161,12 +6161,12 @@
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
+          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
+          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 08:55</t>
+          <t>15/05/2026 09:54</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -6194,12 +6194,12 @@
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
+          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
         </is>
       </c>
     </row>
@@ -6209,17 +6209,17 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 19:35</t>
+          <t>15/05/2026 09:42</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -6227,12 +6227,12 @@
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 13:42</t>
+          <t>15/05/2026 09:12</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -6260,12 +6260,12 @@
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
+          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
+          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:01</t>
+          <t>15/05/2026 08:55</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -6293,12 +6293,12 @@
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6308,17 +6308,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:00</t>
+          <t>14/05/2026 19:35</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -6326,12 +6326,12 @@
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 16:35</t>
+          <t>14/05/2026 13:42</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -6359,12 +6359,12 @@
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
+          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 14:34</t>
+          <t>13/05/2026 17:01</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -6392,12 +6392,12 @@
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
+          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 13:24</t>
+          <t>13/05/2026 17:00</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -6425,12 +6425,12 @@
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
+          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6440,17 +6440,17 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
+          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:59</t>
+          <t>13/05/2026 16:35</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -6458,12 +6458,12 @@
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
+          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
+          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:33</t>
+          <t>13/05/2026 14:34</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -6491,12 +6491,12 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
+          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
+          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:23</t>
+          <t>13/05/2026 13:24</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -6524,12 +6524,12 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
+          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
+          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:12</t>
+          <t>13/05/2026 09:59</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -6557,12 +6557,12 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
+          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
+          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -6582,24 +6582,20 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026 11:29</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>13/05/2026 09:33</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
+          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6609,17 +6605,17 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026 19:37</t>
+          <t>13/05/2026 09:23</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -6627,12 +6623,12 @@
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6642,17 +6638,17 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026 10:31</t>
+          <t>13/05/2026 09:12</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -6660,12 +6656,12 @@
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6675,30 +6671,34 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026 01:28</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr"/>
+          <t>12/05/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
         </is>
       </c>
     </row>
@@ -6708,17 +6708,17 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>16/03/2026 11:15</t>
+          <t>06/05/2026 19:37</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr"/>
@@ -6726,12 +6726,12 @@
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>10/03/2026 09:00</t>
+          <t>05/05/2026 10:31</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -6759,12 +6759,12 @@
       <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
+          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -6784,24 +6784,20 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 19:52</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội, TP.HCM</t>
-        </is>
-      </c>
+          <t>10/04/2026 01:28</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6807,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Quy Nhơn</t>
+          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -6821,20 +6817,20 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:44</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>16/03/2026 11:15</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -6844,30 +6840,30 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Đà Nẵng</t>
+          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:37</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>10/03/2026 09:00</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -6877,34 +6873,34 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
+          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:45</t>
+          <t>09/03/2026 19:52</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Hà Nội, TP.HCM</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
+          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6910,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Đà Lạt</t>
+          <t>FPTU Open Day Quy Nhơn</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -6924,20 +6920,20 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:27</t>
-        </is>
-      </c>
-      <c r="E190" s="2" t="inlineStr"/>
+          <t>03/03/2026 09:44</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6943,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Thanh Hóa</t>
+          <t>FPTU Open Day Đà Nẵng</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -6957,20 +6953,20 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>05/02/2026 09:57</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr"/>
+          <t>03/03/2026 09:37</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr">
-        <is>
-          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
         </is>
       </c>
     </row>
@@ -6980,30 +6976,34 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>04/02/2026 10:54</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr"/>
+          <t>02/03/2026 09:45</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
         </is>
       </c>
     </row>
@@ -7013,17 +7013,17 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
+          <t>FPTU Open Day tại Đà Lạt</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:48</t>
+          <t>02/03/2026 09:27</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr"/>
@@ -7031,12 +7031,12 @@
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
+          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
         </is>
       </c>
     </row>
@@ -7046,17 +7046,17 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
+          <t>FPTU Open Day tại Thanh Hóa</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:47</t>
+          <t>05/02/2026 09:57</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -7064,12 +7064,12 @@
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
+          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
+          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 11:04</t>
+          <t>04/02/2026 10:54</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -7097,12 +7097,12 @@
       <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -7122,24 +7122,20 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>26/01/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>02/02/2026 16:48</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -7149,34 +7145,30 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 16:45</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>02/02/2026 16:47</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7186,34 +7178,30 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 10:38</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>02/02/2026 11:04</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7211,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -7233,20 +7221,24 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>20/01/2026 19:51</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr"/>
+          <t>26/01/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7248,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -7266,18 +7258,125 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>28/12/2025 18:24</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr"/>
+          <t>21/01/2026 16:45</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
+          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>21/01/2026 10:38</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Tuyen sinh</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>20/01/2026 19:51</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>28/12/2025 18:24</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
           <t>Ngày 2/11, sự kiện “Homecoming 2025” của Trường Đại học FPT đã diễn ra đầy cảm xúc với sự góp mặt của 400 cựu sinh viên của gần 20 thế hệ, từ khoá đầu tiên từ khi thành lập trường tới nay. Không chỉ là nơi để mọi người cùng tề tựu, sự kiện đã [&amp;#8230;]</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>https://daihoc.fpt.edu.vn/event/400-cuu-sinh-vien-tu-nhieu-the-he-fptu-hoi-ngo-tai-su-kien-homecoming-2025/</t>
         </is>
@@ -7363,7 +7462,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
+          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7373,7 +7472,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 14:00</t>
+          <t>03/07/2026 09:57</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr"/>
@@ -7381,12 +7480,12 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
+          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7495,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7406,7 +7505,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 11:34</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -7414,12 +7513,12 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7528,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7439,7 +7538,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -7447,12 +7546,12 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7561,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7472,7 +7571,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -7480,12 +7579,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7594,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7505,7 +7604,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -7513,12 +7612,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7627,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7538,7 +7637,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 20:38</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -7546,12 +7645,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7660,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7571,7 +7670,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -7579,12 +7678,12 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7693,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7604,24 +7703,20 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 16:38</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>30/06/2026 20:38</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7726,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7641,7 +7736,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
+          <t>30/06/2026 13:48</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -7649,12 +7744,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7759,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7674,20 +7769,24 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7796,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7707,7 +7806,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -7715,12 +7814,12 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7829,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7740,24 +7839,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>26/06/2026 10:57</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7862,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7777,7 +7872,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -7785,12 +7880,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7895,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7810,20 +7905,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -7833,7 +7932,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7843,7 +7942,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -7851,12 +7950,12 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7965,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7876,7 +7975,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -7884,12 +7983,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -7899,34 +7998,30 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>23/06/2026 11:20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -7936,7 +8031,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -7946,7 +8041,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -7954,12 +8049,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -7969,7 +8064,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -7979,7 +8074,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -7987,12 +8082,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -8002,30 +8097,34 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>

--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03/07/2026 09:57</t>
+          <t>03/07/2026 16:37</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I203"/>
+  <dimension ref="A1:I204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
+          <t>Cất nóc Tổ hợp Giáo dục Bình Dương, hình thành trung tâm giáo dục công nghệ quy mô lớn tại phía Nam</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,20 +600,24 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 09:57</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>03/07/2026 16:37</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
+          <t>Ngày 3/7/2026, Lễ cất nóc Tổ hợp Giáo dục FPT Bình Dương đã diễn ra tại phường Tân Đông Hiệp, TP.HCM (trước là phường Thái Hòa, TP. Tân Uyên, Bình Dương cũ), đánh dấu bước hoàn thiện quan trọng của một trong những dự án giáo dục có quy mô lớn nhất khu vực Đông [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/cat-noc-to-hop-giao-duc-binh-duong-hinh-thanh-trung-tam-giao-duc-cong-nghe-quy-mo-lon-tai-phia-nam/</t>
         </is>
       </c>
     </row>
@@ -623,7 +627,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
+          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -633,7 +637,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 14:00</t>
+          <t>03/07/2026 09:57</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -641,12 +645,12 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
+          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
         </is>
       </c>
     </row>
@@ -656,7 +660,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -666,7 +670,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -674,12 +678,12 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -689,7 +693,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
+          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -699,7 +703,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 11:34</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -707,12 +711,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
+          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
         </is>
       </c>
     </row>
@@ -722,7 +726,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -732,7 +736,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -740,12 +744,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -755,7 +759,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -773,12 +777,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -788,7 +792,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -798,7 +802,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -806,12 +810,12 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -821,7 +825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -831,7 +835,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 20:38</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -839,12 +843,12 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -854,7 +858,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -864,7 +868,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>30/06/2026 20:38</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -872,12 +876,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -887,7 +891,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -897,24 +901,20 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 16:38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>30/06/2026 13:48</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -934,20 +934,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -957,7 +961,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -967,7 +971,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -975,12 +979,12 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -990,7 +994,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1000,7 +1004,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>26/06/2026 10:57</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1008,12 +1012,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1027,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,24 +1037,20 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>25/06/2026 15:45</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1070,20 +1070,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1097,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1103,7 +1107,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1111,12 +1115,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1135,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1149,7 +1153,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1159,17 +1163,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1177,12 +1181,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1202,7 +1206,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1210,12 +1214,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1229,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1235,24 +1239,20 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>23/06/2026 07:08</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1272,20 +1272,24 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1299,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1305,7 +1309,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1313,12 +1317,12 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -1328,17 +1332,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1346,12 +1350,12 @@
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1365,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1379,12 +1383,12 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1398,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1404,7 +1408,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
+          <t>15/06/2026 09:13</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1412,12 +1416,12 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>15/06/2026 08:52</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1445,12 +1449,12 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1464,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1470,7 +1474,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>14/06/2026 07:23</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1478,12 +1482,12 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1497,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1503,7 +1507,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>14/06/2026 07:06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1511,12 +1515,12 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1530,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
+          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1536,7 +1540,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 10:20</t>
+          <t>14/06/2026 05:48</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1544,12 +1548,12 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
+          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1563,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
+          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:46</t>
+          <t>13/06/2026 10:20</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1577,12 +1581,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
+          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1596,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
+          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1602,7 +1606,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:22</t>
+          <t>13/06/2026 09:46</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1610,12 +1614,12 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1629,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
+          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1635,7 +1639,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 19:15</t>
+          <t>13/06/2026 09:22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1643,12 +1647,12 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1662,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
+          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 09:12</t>
+          <t>12/06/2026 19:15</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1676,12 +1680,12 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
+          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1695,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
+          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1701,7 +1705,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 08:17</t>
+          <t>12/06/2026 09:12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1709,12 +1713,12 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
+          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
+          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1734,24 +1738,20 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:52</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 08:17</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
+          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
+          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:38</t>
+          <t>11/06/2026 17:52</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1783,12 +1783,12 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
+          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
+          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 12:01</t>
+          <t>11/06/2026 17:38</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1820,12 +1820,12 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
+          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
+          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1845,20 +1845,24 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 10:50</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+          <t>11/06/2026 12:01</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
+          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1872,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
+          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1878,7 +1882,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:59</t>
+          <t>11/06/2026 10:50</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -1886,12 +1890,12 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
+          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1905,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
+          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:29</t>
+          <t>11/06/2026 09:59</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -1919,12 +1923,12 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
+          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
+          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1944,7 +1948,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:50</t>
+          <t>11/06/2026 09:29</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1952,12 +1956,12 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
+          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1971,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
+          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1977,7 +1981,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 17:11</t>
+          <t>10/06/2026 09:50</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1985,12 +1989,12 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
+          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2004,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
+          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2010,7 +2014,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 16:59</t>
+          <t>09/06/2026 17:11</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2018,12 +2022,12 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
+          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2037,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
+          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2043,7 +2047,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 13:44</t>
+          <t>09/06/2026 16:59</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2051,12 +2055,12 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
+          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2070,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
+          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2076,7 +2080,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 10:42</t>
+          <t>09/06/2026 13:44</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2084,12 +2088,12 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
+          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2103,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2109,7 +2113,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 10:42</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2117,12 +2121,12 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
+          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2136,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
+          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2150,12 +2154,12 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
+          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2169,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
+          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2183,12 +2187,12 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2202,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
+          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2216,12 +2220,12 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
+          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2235,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
+          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2241,7 +2245,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -2249,12 +2253,12 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2268,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
+          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2282,12 +2286,12 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
+          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2301,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
+          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2315,12 +2319,12 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
+          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2334,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
+          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2340,7 +2344,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:19</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -2348,12 +2352,12 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
+          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2367,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
+          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2373,7 +2377,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:19</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2381,12 +2385,12 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
+          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2400,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
+          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2414,12 +2418,12 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
+          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2433,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>09/06/2026 09:18</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2447,12 +2451,12 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
         </is>
       </c>
     </row>
@@ -2462,34 +2466,30 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 22:25</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>08/06/2026 14:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2509,20 +2509,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 07:22</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
+          <t>06/06/2026 22:25</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
+          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2536,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
+          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2542,7 +2546,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 18:09</t>
+          <t>06/06/2026 07:22</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2550,12 +2554,12 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
+          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2575,24 +2579,20 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 13:00</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>05/06/2026 18:09</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
+          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
+          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 12:25</t>
+          <t>05/06/2026 13:00</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
+          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
+          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2649,20 +2649,24 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 14:02</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
+          <t>05/06/2026 12:25</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
+          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
+          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
+          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2682,7 +2686,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:30</t>
+          <t>04/06/2026 14:02</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -2690,12 +2694,12 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
+          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2709,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
+          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2715,24 +2719,20 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:11</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>04/06/2026 09:30</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
+          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
         </is>
       </c>
     </row>
@@ -2742,30 +2742,34 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:29</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>04/06/2026 09:11</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2775,34 +2779,30 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
+          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:21</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>03/06/2026 14:29</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
+          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
+          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2822,20 +2822,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:53</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>03/06/2026 14:21</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
+          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2849,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
+          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -2855,7 +2859,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:51</t>
+          <t>02/06/2026 19:53</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2863,12 +2867,12 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
+          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2882,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
+          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2888,7 +2892,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:22</t>
+          <t>02/06/2026 19:51</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -2896,12 +2900,12 @@
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2915,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
+          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2921,7 +2925,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:55</t>
+          <t>02/06/2026 19:22</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2929,12 +2933,12 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
+          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2948,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
+          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2954,7 +2958,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:52</t>
+          <t>02/06/2026 16:55</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2962,12 +2966,12 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
+          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2981,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
+          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2987,7 +2991,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:21</t>
+          <t>02/06/2026 16:52</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -2995,12 +2999,12 @@
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
+          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3014,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3020,7 +3024,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 10:21</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3028,12 +3032,12 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
+          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3047,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
+          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3061,12 +3065,12 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
+          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
+          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3086,7 +3090,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -3094,12 +3098,12 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3113,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
+          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3127,12 +3131,12 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
+          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3146,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
+          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3160,12 +3164,12 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
+          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3179,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
+          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3185,7 +3189,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:57</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -3193,12 +3197,12 @@
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
+          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3212,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
+          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3218,7 +3222,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:55</t>
+          <t>02/06/2026 09:57</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -3226,12 +3230,12 @@
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
+          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3245,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3251,7 +3255,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:54</t>
+          <t>02/06/2026 09:55</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3259,12 +3263,12 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3278,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
+          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3284,7 +3288,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:41</t>
+          <t>02/06/2026 09:54</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -3292,12 +3296,12 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -3307,17 +3311,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
+          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 13:31</t>
+          <t>02/06/2026 09:41</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -3325,12 +3329,12 @@
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -3340,17 +3344,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
+          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:38</t>
+          <t>01/06/2026 13:31</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3358,12 +3362,12 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
+          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3377,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3383,7 +3387,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:28</t>
+          <t>01/06/2026 00:38</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -3391,12 +3395,12 @@
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
+          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -3416,7 +3420,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:19</t>
+          <t>01/06/2026 00:28</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -3424,12 +3428,12 @@
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
+          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
         </is>
       </c>
     </row>
@@ -3439,7 +3443,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
+          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3449,7 +3453,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:09</t>
+          <t>01/06/2026 00:19</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -3457,12 +3461,12 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
+          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3476,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
+          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3482,24 +3486,20 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:01</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 00:09</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
+          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
+          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3519,20 +3519,24 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:52</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
+          <t>01/06/2026 00:01</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
+          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3546,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
+          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3552,7 +3556,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:43</t>
+          <t>31/05/2026 23:52</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -3560,12 +3564,12 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
+          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3579,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
+          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3585,24 +3589,20 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:33</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>31/05/2026 23:43</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
+          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
+          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3622,20 +3622,24 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 21:33</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr"/>
+          <t>31/05/2026 23:33</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
+          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
         </is>
       </c>
     </row>
@@ -3645,34 +3649,30 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
+          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 20:49</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>31/05/2026 21:33</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
       <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
+          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
+          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -3692,20 +3692,24 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 13:42</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr"/>
+          <t>30/05/2026 20:49</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
+          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3719,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
+          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -3725,7 +3729,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 20:31</t>
+          <t>30/05/2026 13:42</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -3733,12 +3737,12 @@
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
+          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
         </is>
       </c>
     </row>
@@ -3748,17 +3752,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
+          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:51</t>
+          <t>29/05/2026 20:31</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -3766,12 +3770,12 @@
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
+          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3785,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
+          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -3791,7 +3795,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:34</t>
+          <t>29/05/2026 08:51</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -3799,12 +3803,12 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
+          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3818,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -3824,24 +3828,20 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:30</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>29/05/2026 08:34</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
         </is>
       </c>
     </row>
@@ -3851,30 +3851,34 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
+          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026 10:33</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr"/>
+          <t>29/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
+          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -3884,17 +3888,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
+          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 11:02</t>
+          <t>28/05/2026 10:33</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -3902,12 +3906,12 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
+          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3921,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
+          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3927,24 +3931,20 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:38</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>27/05/2026 11:02</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
+          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:32</t>
+          <t>27/05/2026 09:38</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
+          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
         </is>
       </c>
     </row>
@@ -3991,30 +3991,34 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
+          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:09</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr"/>
+          <t>27/05/2026 09:32</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
+          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4024,34 +4028,30 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:11</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>27/05/2026 09:09</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
+          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
+          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4071,20 +4071,24 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:52</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr"/>
+          <t>26/05/2026 16:11</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
+          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4094,17 +4098,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
+          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:10</t>
+          <t>26/05/2026 10:52</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -4112,12 +4116,12 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
+          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4127,34 +4131,30 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 09:22</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>26/05/2026 10:10</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
+          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
+          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4174,20 +4174,24 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 19:40</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
+          <t>26/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
+          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4201,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
+          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -4207,7 +4211,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:18</t>
+          <t>25/05/2026 19:40</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -4215,12 +4219,12 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
+          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4234,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4240,24 +4244,20 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:17</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>25/05/2026 17:18</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
+          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
+          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4277,20 +4277,24 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>25/05/2026 17:17</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
+          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4304,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
+          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4318,12 +4322,12 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
+          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4337,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
+          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4343,7 +4347,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:14</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -4351,12 +4355,12 @@
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
+          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4370,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
+          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:13</t>
+          <t>25/05/2026 17:14</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -4384,12 +4388,12 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4403,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
+          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4409,7 +4413,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:12</t>
+          <t>25/05/2026 17:13</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -4417,12 +4421,12 @@
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
+          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4436,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
+          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4442,7 +4446,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:54</t>
+          <t>25/05/2026 17:12</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -4450,12 +4454,12 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
+          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4475,7 +4479,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:52</t>
+          <t>22/05/2026 14:54</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -4483,12 +4487,12 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4502,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
+          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4508,7 +4512,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 13:38</t>
+          <t>22/05/2026 14:52</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -4516,12 +4520,12 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
+          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
+          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4541,7 +4545,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 10:33</t>
+          <t>22/05/2026 13:38</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -4549,12 +4553,12 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4568,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
+          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4574,7 +4578,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:29</t>
+          <t>22/05/2026 10:33</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -4582,12 +4586,12 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
+          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4601,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4607,7 +4611,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:23</t>
+          <t>22/05/2026 09:29</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -4615,12 +4619,12 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4634,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4640,7 +4644,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:20</t>
+          <t>22/05/2026 09:23</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -4648,12 +4652,12 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4667,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
+          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4673,7 +4677,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 16:08</t>
+          <t>22/05/2026 09:20</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -4681,12 +4685,12 @@
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4700,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4706,7 +4710,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:46</t>
+          <t>21/05/2026 16:08</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -4714,12 +4718,12 @@
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
+          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:34</t>
+          <t>21/05/2026 15:46</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -4747,12 +4751,12 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4766,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4772,7 +4776,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:26</t>
+          <t>21/05/2026 15:34</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -4780,12 +4784,12 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4799,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
+          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4805,24 +4809,20 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:21</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>21/05/2026 15:26</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
+          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
+          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4842,20 +4842,24 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:07</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr"/>
+          <t>21/05/2026 15:21</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
+          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4869,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
+          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4875,7 +4879,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:01</t>
+          <t>21/05/2026 15:07</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -4883,12 +4887,12 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4902,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -4908,7 +4912,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 14:33</t>
+          <t>21/05/2026 15:01</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr"/>
@@ -4916,12 +4920,12 @@
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4935,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4941,7 +4945,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 11:00</t>
+          <t>21/05/2026 14:33</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -4949,12 +4953,12 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
         </is>
       </c>
     </row>
@@ -4964,7 +4968,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
+          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -4974,7 +4978,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 09:36</t>
+          <t>21/05/2026 11:00</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -4982,12 +4986,12 @@
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4997,17 +5001,17 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 19:08</t>
+          <t>21/05/2026 09:36</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -5015,12 +5019,12 @@
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
         </is>
       </c>
     </row>
@@ -5030,17 +5034,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
+          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 17:08</t>
+          <t>20/05/2026 19:08</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -5048,12 +5052,12 @@
       <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5067,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
+          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5073,24 +5077,20 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:57</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>20/05/2026 17:08</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
+          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -5110,20 +5110,24 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:41</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr"/>
+          <t>20/05/2026 16:57</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
+          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5137,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
+          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5143,7 +5147,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:37</t>
+          <t>20/05/2026 16:41</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -5151,12 +5155,12 @@
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
+          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5170,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
+          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5176,7 +5180,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:02</t>
+          <t>20/05/2026 09:37</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr"/>
@@ -5184,12 +5188,12 @@
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
+          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5203,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
+          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5209,7 +5213,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:46</t>
+          <t>20/05/2026 09:02</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -5217,12 +5221,12 @@
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
+          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5236,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
+          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5242,7 +5246,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:33</t>
+          <t>19/05/2026 23:46</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -5250,12 +5254,12 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
+          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -5265,7 +5269,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
+          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5275,7 +5279,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:10</t>
+          <t>19/05/2026 23:33</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -5283,12 +5287,12 @@
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
+          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5308,7 +5312,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 22:33</t>
+          <t>19/05/2026 23:10</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -5316,12 +5320,12 @@
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5335,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
+          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -5341,24 +5345,20 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 17:19</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>19/05/2026 22:33</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5378,24 +5378,24 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
+          <t>19/05/2026 17:19</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Đà Nẵng</t>
+          <t>TP.HCM</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
+          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
+          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -5420,19 +5420,19 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
+          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
+          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -5455,17 +5455,21 @@
           <t>19/05/2026 15:15</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5479,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
+          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -5485,7 +5489,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:14</t>
+          <t>19/05/2026 15:15</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr"/>
@@ -5493,12 +5497,12 @@
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5512,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
+          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -5518,7 +5522,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
+          <t>19/05/2026 15:14</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
@@ -5526,12 +5530,12 @@
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5545,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
+          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -5554,21 +5558,17 @@
           <t>19/05/2026 15:04</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+      <c r="E149" s="2" t="inlineStr"/>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
+          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
+          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5588,20 +5588,24 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 13:55</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
+          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5615,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
+          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -5621,7 +5625,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 11:40</t>
+          <t>19/05/2026 13:55</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -5629,12 +5633,12 @@
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5648,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
+          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -5654,7 +5658,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 09:04</t>
+          <t>19/05/2026 11:40</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr"/>
@@ -5662,12 +5666,12 @@
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
+          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5681,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
+          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -5687,7 +5691,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 16:11</t>
+          <t>19/05/2026 09:04</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -5695,12 +5699,12 @@
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
+          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5714,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
+          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -5720,7 +5724,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 15:17</t>
+          <t>18/05/2026 16:11</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -5728,12 +5732,12 @@
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
+          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
         </is>
       </c>
     </row>
@@ -5743,17 +5747,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 14:51</t>
+          <t>18/05/2026 15:17</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -5761,12 +5765,12 @@
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
         </is>
       </c>
     </row>
@@ -5776,17 +5780,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
+          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 10:32</t>
+          <t>18/05/2026 14:51</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -5794,12 +5798,12 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
+          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5813,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
+          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -5819,7 +5823,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 09:07</t>
+          <t>18/05/2026 10:32</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -5827,12 +5831,12 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
+          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -5842,7 +5846,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
+          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -5852,7 +5856,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:30</t>
+          <t>18/05/2026 09:07</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -5860,12 +5864,12 @@
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
+          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
         </is>
       </c>
     </row>
@@ -5875,7 +5879,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
+          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -5885,7 +5889,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:22</t>
+          <t>16/05/2026 09:30</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -5893,12 +5897,12 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
+          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5912,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
+          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -5918,7 +5922,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 20:09</t>
+          <t>16/05/2026 09:22</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -5926,12 +5930,12 @@
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5945,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
+          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -5951,24 +5955,20 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 17:30</t>
-        </is>
-      </c>
-      <c r="E161" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>15/05/2026 20:09</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
+          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5988,20 +5988,24 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:11</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr"/>
+          <t>15/05/2026 17:30</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
+          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6015,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
+          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6021,7 +6025,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:08</t>
+          <t>15/05/2026 11:11</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -6029,12 +6033,12 @@
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
+          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6048,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
+          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -6054,7 +6058,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:08</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
@@ -6062,12 +6066,12 @@
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
+          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -6077,7 +6081,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
+          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6095,12 +6099,12 @@
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
+          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6114,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
+          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -6128,12 +6132,12 @@
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
+          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6147,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
+          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6161,12 +6165,12 @@
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
+          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6180,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
+          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -6186,7 +6190,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:54</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr"/>
@@ -6194,12 +6198,12 @@
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
+          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
         </is>
       </c>
     </row>
@@ -6209,7 +6213,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
+          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -6219,7 +6223,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:42</t>
+          <t>15/05/2026 09:54</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -6227,12 +6231,12 @@
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
+          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6246,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
+          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6252,7 +6256,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:12</t>
+          <t>15/05/2026 09:42</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -6260,12 +6264,12 @@
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
+          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6279,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
+          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -6285,7 +6289,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 08:55</t>
+          <t>15/05/2026 09:12</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -6293,12 +6297,12 @@
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
+          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6308,17 +6312,17 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 19:35</t>
+          <t>15/05/2026 08:55</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -6326,12 +6330,12 @@
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6345,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 13:42</t>
+          <t>14/05/2026 19:35</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -6359,12 +6363,12 @@
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6378,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
+          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -6384,7 +6388,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:01</t>
+          <t>14/05/2026 13:42</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -6392,12 +6396,12 @@
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6411,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -6417,7 +6421,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:00</t>
+          <t>13/05/2026 17:01</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -6425,12 +6429,12 @@
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
         </is>
       </c>
     </row>
@@ -6440,17 +6444,17 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 16:35</t>
+          <t>13/05/2026 17:00</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -6458,12 +6462,12 @@
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6473,17 +6477,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
+          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 14:34</t>
+          <t>13/05/2026 16:35</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -6491,12 +6495,12 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
+          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6510,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
+          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -6516,7 +6520,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 13:24</t>
+          <t>13/05/2026 14:34</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -6524,12 +6528,12 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
+          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6543,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
+          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -6549,7 +6553,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:59</t>
+          <t>13/05/2026 13:24</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -6557,12 +6561,12 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
+          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6576,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
+          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -6582,7 +6586,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:33</t>
+          <t>13/05/2026 09:59</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -6590,12 +6594,12 @@
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
+          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6609,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
+          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -6615,7 +6619,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:23</t>
+          <t>13/05/2026 09:33</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -6623,12 +6627,12 @@
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
+          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6642,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
+          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -6648,7 +6652,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:12</t>
+          <t>13/05/2026 09:23</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -6656,12 +6660,12 @@
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
+          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6675,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
+          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -6681,24 +6685,20 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026 11:29</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>13/05/2026 09:12</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
+          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6708,30 +6708,34 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026 19:37</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr"/>
+          <t>12/05/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6745,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -6751,7 +6755,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026 10:31</t>
+          <t>06/05/2026 19:37</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -6759,12 +6763,12 @@
       <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6778,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -6784,7 +6788,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026 01:28</t>
+          <t>05/05/2026 10:31</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr"/>
@@ -6792,12 +6796,12 @@
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -6807,17 +6811,17 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>16/03/2026 11:15</t>
+          <t>10/04/2026 01:28</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -6825,12 +6829,12 @@
       <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -6840,17 +6844,17 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>10/03/2026 09:00</t>
+          <t>16/03/2026 11:15</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -6858,12 +6862,12 @@
       <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
+          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6877,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
+          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -6883,24 +6887,20 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>09/03/2026 19:52</t>
-        </is>
-      </c>
-      <c r="E189" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội, TP.HCM</t>
-        </is>
-      </c>
+          <t>10/03/2026 09:00</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+          <t>Năm 2026, Trường Đại học FPT triển khai chính sách hỗ trợ 30% học phí toàn khóa dành cho học sinh thuộc Khu vực 1 (KV1). Chính sách này nhằm giảm bớt rào cản tài chính và tạo điều kiện để học sinh tại các vùng dân tộc thiểu số, miền núi, biên giới và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-giam-30-hoc-phi-cho-hoc-sinh-khu-vuc-1-mo-rong-co-hoi-tiep-can-giao-duc-dai-hoc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -6910,30 +6910,34 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Quy Nhơn</t>
+          <t>“Giải mã” sức hút tại gian tư vấn FPTU: Học sinh Gen Z đang tìm kiếm điều gì?</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:44</t>
+          <t>09/03/2026 19:52</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Quy Nhơn</t>
+          <t>Hà Nội, TP.HCM</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Tại Ngày hội tư vấn tuyển sinh &amp;#8211; hướng nghiệp 2026 do Báo Tuổi Trẻ tổ chức ngày 8/3/2026 tại Hà Nội và TP.HCM, gian tư vấn của Trường Đại học FPT thu hút đông đảo học sinh và phụ huynh đến tìm hiểu thông tin. Không chỉ dừng lại ở việc cung cấp thông [&amp;#8230;]</t>
+        </is>
+      </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/giai-ma-suc-hut-tai-gian-tu-van-fptu-hoc-sinh-gen-z-dang-tim-kiem-dieu-gi/</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6947,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day Đà Nẵng</t>
+          <t>FPTU Open Day Quy Nhơn</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -6953,12 +6957,12 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>03/03/2026 09:37</t>
+          <t>03/03/2026 09:44</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Đà Nẵng</t>
+          <t>Quy Nhơn</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
@@ -6966,7 +6970,7 @@
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-quy-nhon-2/</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6980,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
+          <t>FPTU Open Day Đà Nẵng</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -6986,24 +6990,20 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:45</t>
+          <t>03/03/2026 09:37</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>Đà Nẵng</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
-        </is>
-      </c>
+      <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-da-nang/</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Đà Lạt</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025: NIÊN Ý KHAI XUÂN</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -7023,20 +7023,24 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>02/03/2026 09:27</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr"/>
+          <t>02/03/2026 09:45</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
+          <t>LỄ TÔN VINH HỌC KỲ FALL 2025 – NIÊN Ý KHAI XUÂN Lễ Tôn vinh học kỳ Fall 2025 &amp;#8211; Niên Ý Khai Xuân là sự kiện đặc biệt nhằm ghi nhận những thành tích xuất sắc của cá nhân và tập thể sinh viên Trường Đại học FPT cơ sở Hà Nội trong học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
+          <t>https://daihoc.fpt.edu.vn/event/le-ton-vinh-hoc-ky-fall-2025-nien-y-khai-xuan/</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7050,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Thanh Hóa</t>
+          <t>FPTU Open Day tại Đà Lạt</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -7056,7 +7060,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>05/02/2026 09:57</t>
+          <t>02/03/2026 09:27</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr"/>
@@ -7064,12 +7068,12 @@
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
+          <t>FPTU Experience Day 2026 tại Lâm Đồng: Một ngày trải nghiệm – nhiều bước ngoặt tương lai Không khí tại Đà Lạt hôm nay bùng nổ hơn bao giờ hết khi hàng ngàn học sinh chính thức “nhập vai” sinh viên Đại học FPT trong khuôn khổ Experience Day 2026. Từ lớp học thử, giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-da-lat/</t>
         </is>
       </c>
     </row>
@@ -7079,17 +7083,17 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
+          <t>FPTU Open Day tại Thanh Hóa</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>04/02/2026 10:54</t>
+          <t>05/02/2026 09:57</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr"/>
@@ -7097,12 +7101,12 @@
       <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
+          <t>FPTU Open Day sẽ có mặt tại Thanh Hóa vào chiều Chủ nhật, ngày 01/03/2026 tại Trường Tiểu học, THCS và THPT FPT Thanh Hóa, mang đến một không gian gặp gỡ – lắng nghe – trải nghiệm – định hướng dành cho học sinh THPT ngay tại địa phương. Sự kiện được tổ chức [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-openday-thanh-hoa/</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7116,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
+          <t>Trước ngưỡng cửa đại học, người trẻ tìm kiếm mô hình đào tạo sẵn sàng cho việc làm tương lai</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -7122,7 +7126,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:48</t>
+          <t>04/02/2026 10:54</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
@@ -7130,12 +7134,12 @@
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
+          <t>Kỷ nguyên AI, thị trường lao động thay đổi nhanh hơn chu kỳ đào tạo đại học, sinh viên ra trường không chỉ cần kiến thức chuyên môn. Quan trọng hơn là tư duy công nghệ để thích ứng, năng lực tự tạo giá trị và khả năng làm việc toàn cầu &amp;#8211; những yêu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truoc-nguong-cua-dai-hoc-nguoi-tre-tim-kiem-mo-hinh-dao-tao-san-sang-cho-viec-lam-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7149,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
+          <t>Hướng dẫn giới thiệu ứng viên chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -7155,7 +7159,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 16:47</t>
+          <t>02/02/2026 16:48</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr"/>
@@ -7163,12 +7167,12 @@
       <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
+          <t>Giới thiệu ứng viên Học bổng dành cho thầy cô giáo, Ban Giám hiệu các trường THPT và các tổ chức giáo dục nhằm giới thiệu và đề cử những ứng viên đáp ứng đầy đủ tiêu chí của chương trình học bổng, là các học sinh có thành tích học tập xuất sắc hoặc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-gioi-thieu-ung-vien-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7182,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
+          <t>Hướng dẫn nộp hồ sơ đăng ký chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Nguyễn Văn Đạo 2026</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -7188,7 +7192,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>02/02/2026 11:04</t>
+          <t>02/02/2026 16:47</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr"/>
@@ -7196,12 +7200,12 @@
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
+          <t>Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam là chương trình học bổng dành cho học sinh lớp 12 có thành tích học tập xuất sắc, năng lực nổi bật và khát vọng bứt phá trong kỷ nguyên số. Với 1.030 suất học bổng, tổng giá trị hơn 200 tỷ đồng, chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/huong-dan-nop-ho-so-dang-ky-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7215,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký Chương trình học bổng Tìm kiếm Nhân tài Kỷ nguyên số</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -7221,24 +7225,20 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>26/01/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>02/02/2026 11:04</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
+          <t>Ngày 2/2/2026, Trường Đại học FPT chính thức mở cổng đăng ký Chương trình Tìm kiếm Nhân tài Kỷ nguyên số &amp;#8211; Học bổng Nguyễn Văn Đạo cho học sinh lớp 12 trên toàn quốc tại địa chỉ website: TẠI ĐÂY. Thời hạn nhận hồ sơ đến hết ngày 15/5/2026. Một điểm đáng chú ý [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-chuong-trinh-hoc-bong-tim-kiem-nhan-tai-ky-nguyen-so/</t>
         </is>
       </c>
     </row>
@@ -7248,34 +7248,34 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
+          <t>Học sinh THPT “đổ bộ” Trường Đại học FPT trong ngày hội Open Day tại TP.HCM: Trải nghiệm công nghệ và định hướng tương lai</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 16:45</t>
+          <t>26/01/2026 15:04</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Cần Thơ</t>
+          <t>TP.HCM</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
+          <t>Ngày 24/01/2026, Trường Đại học FPT (FPTU) cơ sở TP.HCM đã tổ chức sự kiện Open Day, thu hút đông đảo học sinh THPT và phụ huynh đến tham quan, tìm hiểu và trực tiếp trải nghiệm môi trường học tập. Sự kiện không chỉ mang đến góc nhìn toàn diện về chương trình đào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/hoc-sinh-thpt-do-bo-truong-dai-hoc-fpt-trong-ngay-hoi-open-day-tai-tp-hcm-trai-nghiem-cong-nghe-va-dinh-huong-tuong-lai/</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
+          <t>FPTU Big Open Day Cần Thơ Campus 22/03/2026</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>21/01/2026 10:38</t>
+          <t>21/01/2026 16:45</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
+          <t>2k8 ơi, hãy nhanh tay đăng ký tham gia hành trình trải nghiệm tại FPTU Open Day - campus Cần Thơ lúc 8h, ngày 22/03/2026 nhé!</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-campus-22-03-2026/</t>
         </is>
       </c>
     </row>
@@ -7322,30 +7322,34 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
+          <t>FPTU Big Open Day Cần Thơ Campus 18/01/2026</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>20/01/2026 19:51</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr"/>
+          <t>21/01/2026 10:38</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+          <t>HƠN 3500 HỌC SINH THPT MIỀN TÂY HÁO HỨC TRẢI NGHIỆM TẠI FPTU BIG OPEN DAY Ngày 18/01/2026, Trường Đại học FPT campus Cần Thơ đã tổ chức thành công Ngày hội trải nghiệm FPTU Big Open Day, chào đón hơn 3500 học sinh THPT khu vực Đồng bằng Sông Cửu Long.    Đây là [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-big-open-day-can-tho-1801/</t>
         </is>
       </c>
     </row>
@@ -7355,17 +7359,17 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+          <t>Trường Đại học FPT công bố dự kiến phương thức tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>28/12/2025 18:24</t>
+          <t>20/01/2026 19:51</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr"/>
@@ -7373,10 +7377,43 @@
       <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr">
         <is>
+          <t>Trường Đại học FPT dự kiến tuyển sinh hệ đại học chính quy năm 2026 theo phương thức kết hợp kết quả kỳ thi tốt nghiệp THPT với kết quả học tập THPT, nhằm đánh giá toàn diện năng lực học tập của thí sinh và mở rộng cơ hội tiếp cận môi trường đào [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-du-kien-phuong-thuc-tuyen-sinh-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>400 cựu sinh viên từ nhiều thế hệ FPTU hội ngộ tại sự kiện Homecoming 2025</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Su kien</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>28/12/2025 18:24</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
           <t>Ngày 2/11, sự kiện “Homecoming 2025” của Trường Đại học FPT đã diễn ra đầy cảm xúc với sự góp mặt của 400 cựu sinh viên của gần 20 thế hệ, từ khoá đầu tiên từ khi thành lập trường tới nay. Không chỉ là nơi để mọi người cùng tề tựu, sự kiện đã [&amp;#8230;]</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>https://daihoc.fpt.edu.vn/event/400-cuu-sinh-vien-tu-nhieu-the-he-fptu-hoi-ngo-tai-su-kien-homecoming-2025/</t>
         </is>
@@ -7462,7 +7499,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
+          <t>Cất nóc Tổ hợp Giáo dục Bình Dương, hình thành trung tâm giáo dục công nghệ quy mô lớn tại phía Nam</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7472,20 +7509,24 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>03/07/2026 09:57</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
+          <t>03/07/2026 16:37</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
+          <t>Ngày 3/7/2026, Lễ cất nóc Tổ hợp Giáo dục FPT Bình Dương đã diễn ra tại phường Tân Đông Hiệp, TP.HCM (trước là phường Thái Hòa, TP. Tân Uyên, Bình Dương cũ), đánh dấu bước hoàn thiện quan trọng của một trong những dự án giáo dục có quy mô lớn nhất khu vực Đông [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/cat-noc-to-hop-giao-duc-binh-duong-hinh-thanh-trung-tam-giao-duc-cong-nghe-quy-mo-lon-tai-phia-nam/</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7536,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
+          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7505,7 +7546,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 14:00</t>
+          <t>03/07/2026 09:57</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
@@ -7513,12 +7554,12 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
+          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7569,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7538,7 +7579,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr"/>
@@ -7546,12 +7587,12 @@
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7602,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
+          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -7571,7 +7612,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 11:34</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -7579,12 +7620,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
+          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7635,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7604,7 +7645,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -7612,12 +7653,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7668,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -7645,12 +7686,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7660,7 +7701,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7670,7 +7711,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -7678,12 +7719,12 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7734,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -7703,7 +7744,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 20:38</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -7711,12 +7752,12 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7767,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -7736,7 +7777,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>30/06/2026 20:38</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -7744,12 +7785,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7800,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -7769,24 +7810,20 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 16:38</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>30/06/2026 13:48</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7833,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -7806,20 +7843,24 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7870,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -7839,7 +7880,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -7847,12 +7888,12 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7903,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7872,7 +7913,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>26/06/2026 10:57</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -7880,12 +7921,12 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -7895,7 +7936,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7905,24 +7946,20 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>25/06/2026 15:45</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7969,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -7942,20 +7979,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -7965,7 +8006,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -7975,7 +8016,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -7983,12 +8024,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8044,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -8021,7 +8062,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -8031,17 +8072,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -8049,12 +8090,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8105,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8074,7 +8115,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>23/06/2026 07:40</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -8082,12 +8123,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8138,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -8107,24 +8148,20 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>23/06/2026 07:08</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>

--- a/Trang web FPT/fpt_news_tong_hop.xlsx
+++ b/Trang web FPT/fpt_news_tong_hop.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03/07/2026 16:37</t>
+          <t>06/07/2026 10:10</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cất nóc Tổ hợp Giáo dục Bình Dương, hình thành trung tâm giáo dục công nghệ quy mô lớn tại phía Nam</t>
+          <t>3 Cóc vàng khối ngành Ngôn ngữ FPTU và hành trình vượt giới hạn bản thân</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,24 +600,20 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 16:37</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>06/07/2026 10:10</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Ngày 3/7/2026, Lễ cất nóc Tổ hợp Giáo dục FPT Bình Dương đã diễn ra tại phường Tân Đông Hiệp, TP.HCM (trước là phường Thái Hòa, TP. Tân Uyên, Bình Dương cũ), đánh dấu bước hoàn thiện quan trọng của một trong những dự án giáo dục có quy mô lớn nhất khu vực Đông [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu thành tích học tập ấn tượng, ba Cóc vàng khối ngành Ngôn ngữ học kỳ Spring 2026 của Trường Đại học FPT (FPTU) còn ghi dấu ấn bằng tinh thần học hỏi không ngừng, sự năng động trong hoạt động ngoại khóa và khát vọng phát triển bản thân. Mỗi người [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-hot/cat-noc-to-hop-giao-duc-binh-duong-hinh-thanh-trung-tam-giao-duc-cong-nghe-quy-mo-lon-tai-phia-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/3-coc-vang-khoi-nganh-ngon-ngu-fptu-va-hanh-trinh-vuot-gioi-han-ban-than/</t>
         </is>
       </c>
     </row>
@@ -627,7 +623,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
+          <t>HỘI THẢO PHỤ HUYNH: AI VÀ TƯƠNG LAI NGHỀ NGHIỆP – ĐỒNG HÀNH CÙNG CON TRƯỚC NGƯỠNG CỬA ĐẠI HỌC</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -637,7 +633,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>03/07/2026 09:57</t>
+          <t>06/07/2026 09:25</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -645,12 +641,12 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
+          <t>Tham gia Hội thảo Phụ huynh của Trường Đại học FPT để cập nhật xu hướng AI, định hướng nghề nghiệp, lựa chọn ngành học và đồng hành cùng con trước ngưỡng cửa đại học. Trong bối cảnh trí tuệ nhân tạo (AI) đang tạo ra những thay đổi sâu rộng đối với giáo dục [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/hoi-thao-phu-huynh-ai-va-tuong-lai-nghe-nghiep-dong-hanh-cung-con-truoc-nguong-cua-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -660,7 +656,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
+          <t>Cất nóc Tổ hợp Giáo dục Bình Dương, hình thành trung tâm giáo dục công nghệ quy mô lớn tại phía Nam</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -670,20 +666,24 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 14:00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>03/07/2026 16:37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
+          <t>Ngày 3/7/2026, Lễ cất nóc Tổ hợp Giáo dục FPT Bình Dương đã diễn ra tại phường Tân Đông Hiệp, TP.HCM (trước là phường Thái Hòa, TP. Tân Uyên, Bình Dương cũ), đánh dấu bước hoàn thiện quan trọng của một trong những dự án giáo dục có quy mô lớn nhất khu vực Đông [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/cat-noc-to-hop-giao-duc-binh-duong-hinh-thanh-trung-tam-giao-duc-cong-nghe-quy-mo-lon-tai-phia-nam/</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
+          <t>Từ cử nhân Digital Marketing của FPTU đến “Marketer giáo dục” giành liên tiếp 3 học bổng thạc sĩ</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 13:53</t>
+          <t>03/07/2026 09:57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -711,12 +711,12 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
+          <t>Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing vừa liên tiếp chinh phục 2 học bổng toàn phần, 1 học bổng bán phần chương trình thạc sĩ của các trường danh tiếng hàng đầu Trung Quốc. Cơ duyên đến với các chương trình học bổng của đất nước tỷ dân xuất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/tu-cu-nhan-digital-marketing-cua-fptu-den-marketer-giao-duc-gianh-lien-tiep-3-hoc-bong-thac-si/</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
+          <t>Hướng dẫn đăng ký nguyện vọng vào Trường Đại học FPT 2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 11:34</t>
+          <t>01/07/2026 14:00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -744,12 +744,12 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
+          <t>Nắm vững các bước đăng ký nguyện vọng đại học là cực kỳ quan trọng để trở thành “tân binh” của Trường Đại học FPT. Năm 2026, toàn bộ quá trình đăng ký tiếp tục thực hiện trực tuyến trên Hệ thống hỗ trợ tuyển sinh chung của Bộ GD&amp;#38;ĐT. Từ 2/7 đến 17h ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/huong-dan-dang-ky-nguyen-vong-vao-truong-dai-hoc-fpt-2026/</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Mẫu đơn phúc khảo điểm thi THPT 2026 và cách viết chuẩn</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 13:53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -777,12 +777,12 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
+          <t>Sau khi Bộ GD&amp;#38;ĐT chính thức công bố điểm thi tốt nghiệp THPT năm 2026 vào sáng 01/07/2026, nếu nhận thấy kết quả nhận được chưa phản ánh đúng năng lực làm bài thực tế, thí sinh hoàn toàn có quyền làm đơn đề nghị phúc khảo. Mẫu đơn phúc khảo điểm thi THPT 2026 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/don-phuc-khao-diem-thi-thpt/</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
+          <t>Trường Đại học FPT ra mắt Hệ thống Kiểm tra điều kiện xét tuyển năm 2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 08:00</t>
+          <t>01/07/2026 11:34</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -810,12 +810,12 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
+          <t>Nhằm hỗ trợ thí sinh 2K8 chủ động kiểm tra điều kiện xét tuyển và xây dựng chiến lược đăng ký nguyện vọng hiệu quả, Trường Đại học FPT chính thức triển khai Hệ thống Kiểm tra điều kiện xét tuyển năm 2026 tại địa chỉ: https://daihoc.fpt.edu.vn/kiem-tra-dieu-kien-xet-tuyen-fptu/  Mùa tuyển sinh đại học năm 2026 đang [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/truong-dai-hoc-fpt-ra-mat-he-thong-kiem-tra-dieu-kien-xet-tuyen-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
+          <t>Điểm chuẩn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>01/07/2026 07:00</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -843,12 +843,12 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh năm 2026 đang đến gần, mang theo những kỳ vọng và cả áp lực vô hình lên đôi vai của các sĩ tử lớp 12. Trong đó, Điểm chuẩn xét tuyển Trường Đại học FPT luôn là từ khóa nhận được sự quan tâm đặc biệt. Với phương thức tuyển sinh linh hoạt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-chuan-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
+          <t>Điểm sàn xét tuyển Trường Đại học FPT mới, chi tiết</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 20:38</t>
+          <t>01/07/2026 08:00</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -876,12 +876,12 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả các ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/diem-san-xet-tuyen-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
+          <t>Trường Đại học FPT công bố điểm sàn xét tuyển hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30/06/2026 13:48</t>
+          <t>01/07/2026 07:00</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -909,12 +909,12 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa công bố điểm sàn xét tuyển (ngưỡng bảo đảm chất lượng đầu vào) hệ đại học chính quy năm 2026 là 18 điểm. Riêng chương trình Cử nhân tài năng ngành Khoa học máy tính điểm sàn xét tuyển là 21 điểm. Chính sách này áp dụng cho tất cả [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-cong-bo-diem-san-xet-tuyen-he-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
+          <t>Sinh viên Trường Đại học FPT đạt giải Ba tại Hội thi Khoa học sinh viên toàn quốc – Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -934,24 +934,20 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29/06/2026 16:38</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>30/06/2026 20:38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
+          <t>Với đề tài nghiên cứu về sự sẵn sàng nghề nghiệp của sinh viên trong nền kinh tế số, nhóm sinh viên Trường Đại học FPT đã xuất sắc giành Giải Ba tại Hội thi Khoa học sinh viên toàn quốc &amp;#8211; Olympic Kinh tế lượng và Ứng dụng lần thứ XI năm 2026. Hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-hot/sinh-vien-truong-dai-hoc-fpt-dat-giai-ba-tai-hoi-thi-khoa-hoc-sinh-vien-toan-quoc-olympic-kinh-te-luong-va-ung-dung-lan-thu-xi-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -961,7 +957,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
+          <t>Từ việc làm sớm đến trải nghiệm toàn cầu: Vì sao nhiều sinh viên đặt Trường Đại học FPT ở nguyện vọng ưu tiên?</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -971,7 +967,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27/06/2026 13:29</t>
+          <t>30/06/2026 13:48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -979,12 +975,12 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
+          <t>&amp;#8220;Chọn trường nào?&amp;#8221; có lẽ là câu hỏi khiến nhiều học sinh 2K8 đau đầu nhất những ngày này. Nhìn lại quyết định năm 18 tuổi, nhiều sinh viên Trường Đại học FPT kể rằng họ đến với ngôi trường này vì những lý do rất khác nhau. Nhưng sau bốn năm, tất cả lại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-viec-lam-som-den-trai-nghiem-toan-cau-vi-sao-nhieu-sinh-vien-dat-truong-dai-hoc-fpt-o-nguyen-vong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -994,7 +990,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
+          <t>FPTU TechXCamp 2026: Hành trình trở thành phiên bản tốt hơn của mỗi người trẻ</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1004,20 +1000,24 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026 10:57</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>29/06/2026 16:38</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
+          <t>Ngày 23-28/6, Trường Đại học FPT đã tổ chức chương trình trải nghiệm FPTU TechXCamp 2026 tại Quy Nhơn thu hút gần 100 học sinh THPT đến từ nhiều tỉnh, thành khu vực miền Trung &amp;#8211; Tây Nguyên. Ngày hội gồm chuỗi hoạt động kết hợp công nghệ, khởi nghiệp, kỹ năng mềm và giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-techxcamp-2026-hanh-trinh-tro-thanh-phien-ban-tot-hon-cua-moi-nguoi-tre/</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
+          <t>Chọn nguyện vọng “trúng phóc”: Bí kíp từ những anh chị khóa trên dành cho 2K8</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026 15:45</t>
+          <t>27/06/2026 13:29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1045,12 +1045,12 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
+          <t>Từ những sinh viên từng hoang mang như bao sĩ tử khác, nhiều bạn trẻ đã tìm được môi trường giúp mình nghiên cứu khoa học, khởi nghiệp, vươn ra quốc tế hay theo đuổi đam mê. Với các sĩ tử 2K8, đây có thể là những kinh nghiệm đáng tham khảo trước khi đặt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/chon-nguyen-vong-trung-phoc-bi-kip-tu-nhung-anh-chi-khoa-tren-danh-cho-2k8/</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
+          <t>Tiến sĩ Lê Trường Tùng: Trường đại học cần đóng góp thiết thực cho phát triển bền vững của xã hội</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1070,24 +1070,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 20:14</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>26/06/2026 10:57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
+          <t>Theo Tiến sĩ Lê Trường Tùng, giáo dục đại học cần gắn đào tạo với trải nghiệm thực tiễn và trách nhiệm xã hội, qua đó đóng góp cho sự phát triển bền vững và hình thành ý thức cho người học. Ngày 24/6/2026, Tổ chức xếp hạng giáo dục đại học Times Higher Education [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tien-si-le-truong-tung-truong-dai-hoc-can-dong-gop-thiet-thuc-cho-phat-trien-ben-vung-cua-xa-hoi/</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
+          <t>Học khởi nghiệp ở trường đại học: Không phải ai cũng thành founder, nhưng ai cũng cần tư duy làm chủ</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1107,7 +1103,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026 07:01</t>
+          <t>25/06/2026 15:45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1115,12 +1111,12 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
+          <t>Từng giành 110 triệu đồng từ một cuộc thi khởi nghiệp khi còn là sinh viên Trường ĐH FPT, Nguyễn Thanh Tùng trở thành founder MindX, gọi vốn 15 triệu USD. Từ những đốm lửa startup đầu tiên, FPTU đưa tinh thần khởi nghiệp vào đào tạo, giúp sinh viên không chỉ học cách lập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/hoc-khoi-nghiep-o-truong-dai-hoc-khong-phai-ai-cung-thanh-founder-nhung-ai-cung-can-tu-duy-lam-chu/</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1126,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Hội trại thủ lĩnh FPTU Summer Jamboree 2026: Khi người trẻ bước vào hành trình “gắn kết” để trưởng thành</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1140,20 +1136,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>24/06/2026 20:14</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Diễn ra từ ngày 25 &amp;#8211; 28/6/2026 tại Trường Đại học FPT (cơ sở Đà Nẵng), trại hè thủ lĩnh FPTU Summer Jamboree 2026 quy tụ gần 3000 trại sinh trong nước và quốc tế, cùng kết nối, nâng cao sự thấu cảm trước những thách thức của thời đại số. Tiếp nối thành công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/hoi-trai-thu-linh-fptu-summer-jamboree-2026-khi-nguoi-tre-buoc-vao-hanh-trinh-gan-ket-de-truong-thanh/</t>
         </is>
       </c>
     </row>
@@ -1163,17 +1163,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
+          <t>Trường Đại học FPT vào top 300 đại học Phát triển bền vững hàng đầu thế giới, top 100 toàn cầu về Giáo dục chất lượng</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 11:20</t>
+          <t>24/06/2026 07:01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1181,12 +1181,12 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
+          <t>Trường Đại học FPT (FPTU) chính thức được Times Higher Education (THE) xếp vào nhóm 201–300 trường đại học có tác động phát triển bền vững hàng đầu thế giới trong bảng xếp hạng THE Impact Ratings 2026. Đây là lần đầu tiên FPTU đạt được nhóm xếp hạng này, đồng thời tiếp tục khẳng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-vao-top-300-dai-hoc-phat-trien-ben-vung-hang-dau-the-gioi-top-100-toan-cau-ve-giao-duc-chat-luong/</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:40</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1214,12 +1214,12 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
+          <t>Những “mảnh ghép” nhân tài tiếp tục lộ diện tại vòng phỏng vấn Đợt 2 Học bổng Nguyễn Văn Đạo</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026 07:08</t>
+          <t>23/06/2026 11:20</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1247,12 +1247,12 @@
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
+          <t>Không chỉ là một vòng đánh giá năng lực, 3 ngày phỏng vấn đợt 2 Chương trình Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Nguyễn Văn Đạo đã trở thành không gian để gần 1.200 Gen Z tự tin thể hiện bản lĩnh, tư duy khác biệt và khát vọng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/nhung-manh-ghep-nhan-tai-tiep-tuc-lo-dien-tai-vong-phong-van-dot-2-hoc-bong-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
+          <t>Tổng hợp cách bấm máy tính thi THPT Quốc Gia [Dễ hiểu]</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1272,24 +1272,20 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 20:35</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>23/06/2026 07:40</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
+          <t>Học sinh đang ôn thi THPT Quốc Gia và muốn tối ưu hóa thời gian giải đề Toán? Hay các bạn đang vật lộn với những phương trình, bất đẳng thức phức tạp mà máy tính chưa “hiểu ý”? Đừng lo lắng! Trong bài viết này, Trường Đại học FPT sẽ mang đến cho các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-bam-may-tinh-thi-thpt-quoc-gia/</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1295,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
+          <t>Tổng hợp các công thức giải nhanh trắc nghiệm hóa học</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1309,7 +1305,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:46</t>
+          <t>23/06/2026 07:08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1317,12 +1313,12 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
+          <t>Trong cấu trúc đề thi tốt nghiệp THPT Quốc gia, môn Hóa học với phần lớn câu hỏi trắc nghiệm đòi hỏi thí sinh không chỉ nắm chắc bản chất bài toán mà còn phải tối ưu hóa tốc độ xử lý đề. Việc áp dụng thành thạo các công thức giải nhanh trắc nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cac-cong-thuc-giai-nhanh-trac-nghiem-hoa-hoc/</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1328,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
+          <t>Check in sống ảo và trải nghiệm loạt hoạt động hấp dẫn tại Sen’s Week 2 của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1342,20 +1338,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026 16:29</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>22/06/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
+          <t>Không chỉ sở hữu một trong những hồ sen đẹp bậc nhất trong khuôn viên trường đại học, Trường Đại học FPT còn biến nơi đây thành không gian trải nghiệm văn hóa độc đáo với Tuần lễ Sen. Mỗi mùa sen nở, campus Hòa Lạc lại trở thành điểm hẹn check-in được giới trẻ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/check-in-song-ao-va-trai-nghiem-loat-hoat-dong-hap-dan-tai-sens-week-2-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1365,17 +1365,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
+          <t>FU Street Workout: Cộng đồng Calisthenics cho sinh viên FPTU dám vượt giới hạn</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026 16:11</t>
+          <t>22/06/2026 16:46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1383,12 +1383,12 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
+          <t>Khi lối sống khỏe, năng động và kỷ luật ngày càng trở thành xu hướng của giới trẻ, FU Street Workout là điểm đến dành cho những sinh viên muốn rèn luyện thể chất và bứt phá giới hạn bản thân. Thành lập năm 2016, FU Street Workout là câu lạc bộ Calisthenics trực thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fu-street-workout-cong-dong-calisthenics-cho-sinh-vien-fptu-dam-vuot-gioi-han/</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
+          <t>Thông báo về kết quả xét bổ nhiệm chức danh Phó giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 09:13</t>
+          <t>22/06/2026 16:29</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1416,12 +1416,12 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31/08/2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh giáo sư, phó giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh giáo sư, phó giáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-ket-qua-xet-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
+          <t>Mega Livestream “Sẵn sàng cho sự nghiệp toàn cầu”: Hành trình từ giảng đường bước ra thế giới cùng Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026 08:52</t>
+          <t>18/06/2026 16:11</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1449,12 +1449,12 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
+          <t>Trong bối cảnh cơ hội học tập, làm việc và phát triển ngày càng mở rộng ra môi trường quốc tế, việc lựa chọn một môi trường đại học phù hợp không chỉ dừng lại ở ngành học hay tấm bằng. Với thế hệ học sinh hôm nay, đại học còn là nơi bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-san-sang-cho-su-nghiep-toan-cau-hanh-trinh-tu-giang-duong-buoc-ra-the-gioi-cung-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
+          <t>Nên học ngôn ngữ nào? Top 7 gợi ý không nên bỏ qua</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:23</t>
+          <t>15/06/2026 09:13</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1482,12 +1482,12 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
+          <t>Thế giới ngày càng trở nên phẳng, và sử dụng thành thạo một ngoại ngữ trở thành một lợi thế cạnh tranh không thể thiếu. Nhưng với sự đa dạng của các ngôn ngữ, người học đang băn khoăn không biết nên học ngôn ngữ nào? Trong bài viết này, Trường Đại học FPT sẽ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nen-hoc-ngon-ngu-nao/</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
+          <t>Rớt nguyện vọng 1 thì phải làm sao? Cẩm nang định hướng cho sĩ tử</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 07:06</t>
+          <t>15/06/2026 08:52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1515,12 +1515,12 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi đến toàn thể thí sinh. Bên cạnh niềm vui sướng vỡ òa của những sĩ tử may mắn đỗ nguyện vọng mong ước, vẫn có không ít những giọt nước mắt buồn bã, lo âu từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/rot-nguyen-vong-1-thi-phai-lam-sao/</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
+          <t>Làm thế nào để tra cứu điểm thi tốt nghiệp THPT 2026?</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026 05:48</t>
+          <t>14/06/2026 07:23</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -1548,12 +1548,12 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
+          <t>Các sĩ tử đang hồi hộp chờ đợi kết quả của bước ngoặt lớn sau những năm tháng ngồi trên ghế nhà trường? Hãy gạt bỏ những lo âu, bồn chồn và truy cập ngay bài viết dưới đây của Trường Đại học FPT để nắm lòng các phương án tra cứu điểm thi tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/tra-cuu-diem-thi-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
+          <t>Sau khi thi tốt nghiệp THPT nên làm gì? 5 gợi ý vàng giúp sĩ tử bứt phá</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 10:20</t>
+          <t>14/06/2026 07:06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -1581,12 +1581,12 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
+          <t>Vượt qua kỳ thi tốt nghiệp THPT là một cột mốc vô cùng quan trọng, mở ra cánh cửa bước vào một thế giới rộng lớn với muôn vàn ngã rẽ và cơ hội phát triển. Đứng trước ngưỡng cửa quyết định ấy, không ít học sinh rơi vào trạng thái băn khoăn, lo lắng: [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/sau-khi-thi-tot-nghiep-thpt-nen-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
+          <t>Chi tiết cách đăng ký nguyện vọng trực tuyến dành cho sĩ tử 2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:46</t>
+          <t>14/06/2026 05:48</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -1614,12 +1614,12 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
+          <t>Đăng ký nguyện vọng trực tuyến là bước ngoặt quyết định giúp thí sinh chính thức chạm tay vào cánh cửa đại học, cao đẳng. Năm 2026, Bộ GD&amp;#38;ĐT quy định thời gian đăng ký và điều chỉnh nguyện vọng chính thức diễn ra từ ngày 02/07 đến 17h ngày 14/07/2026 trên Hệ thống Tuyển [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cach-dang-ky-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
+          <t>Tất tần tật về top 8 các ngành liên quan đến nghệ thuật</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026 09:22</t>
+          <t>13/06/2026 10:20</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -1647,12 +1647,12 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
+          <t>Trước khi đưa ra quyết định, mỗi cá nhân cần thấu hiểu rõ sở trường, phong cách cá nhân cũng như mục tiêu nghề nghiệp dài hạn của chính mình. Việc trang bị đầy đủ thông tin về thị trường lao động và yêu cầu chuyên môn sẽ giúp người học tránh được những sai [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-nganh-lien-quan-den-nghe-thuat/</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
+          <t>Nếu trượt hết các nguyện vọng thì phải làm thế nào 2026?</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 19:15</t>
+          <t>13/06/2026 09:46</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -1680,12 +1680,12 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT Quốc gia vừa chính thức khép lại, bảng điểm cũng đã được công bố rộng rãi. Bên cạnh những niềm vui đỗ đạt, không ít bạn trẻ phải đối mặt với nỗi thất vọng tràn trề khi không may trượt hết các nguyện vọng đại học đã đăng ký đợt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/neu-truot-het-cac-nguyen-vong/</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
+          <t>Hướng dẫn sử dụng công cụ tính điểm tốt nghiệp THPT online 2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 09:12</t>
+          <t>13/06/2026 09:22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -1713,12 +1713,12 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp trung học phổ thông năm 2026 luôn là cột mốc đặc biệt quan trọng đối với các sĩ tử trên cả nước. Sau khi hoàn thành các bài thi, việc tự dự đoán và tính toán điểm số là nhu cầu vô cùng chính xác để chuẩn bị cho lộ trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cong-cu-tinh-diem-tot-nghiep-thpt/</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
+          <t>Nhân viên văn phòng học ngành gì? TOP 10 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026 08:17</t>
+          <t>12/06/2026 19:15</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -1746,12 +1746,12 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
+          <t>Thắc mắc nhân viên văn phòng học ngành gì luôn là trăn trở của nhiều sĩ tử khi đứng trước ngưỡng cửa lựa chọn nghề nghiệp. Thực tế, khái niệm &amp;#8220;văn phòng&amp;#8221; bao hàm rất nhiều vị trí chuyên biệt từ quản lý, nhân sự cho đến kỹ thuật và hỗ trợ kinh doanh. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nhan-vien-van-phong-hoc-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
+          <t>Khối xã hội gồm những ngành gì? 7 gợi ý cho sĩ tử</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1771,24 +1771,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:52</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 09:12</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
+          <t>Việc xác định khối xã hội gồm những ngành gì là bước đi quan trọng giúp học sinh khai phá thế mạnh về ngôn ngữ, tư duy nhân văn và kỹ năng giao tiếp. Trong bối cảnh hội nhập quốc tế, các ngành học này không chỉ dừng lại ở lý thuyết mà còn mở [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khoi-xa-hoi-gom-nhung-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1794,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
+          <t>Con gái nên học nghề gì? 15+ nghề ổn định, lương cao</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1808,24 +1804,20 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 17:38</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>12/06/2026 08:17</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
+          <t>Việc lựa chọn nghề nghiệp chưa bao giờ là một quyết định dễ dàng, đặc biệt là đối với phái đẹp trong bối cảnh thị trường lao động đang không ngừng chuyển dịch. Không còn bị giới hạn trong những quan niệm truyền thống, phụ nữ ngày nay đang khẳng định bản lĩnh ở mọi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/con-gai-nen-hoc-nghe-gi/</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1827,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
+          <t>TOP các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1845,7 +1837,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 12:01</t>
+          <t>11/06/2026 17:52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1857,12 +1849,12 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
+          <t>Các trường đào tạo ngành Ngôn ngữ Anh ở Cần Thơ đang trở thành điểm đến lý tưởng cho những sinh viên muốn chinh phục ngôn ngữ quốc tế trong năm 2026. Đây được xem là nền tảng giúp người học tiếp cận tri thức, mở rộng cơ hội nghề nghiệp và hội nhập sâu rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/cac-truong-dao-tao-ngon-ngu-anh-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1864,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
+          <t>Điểm chuẩn Trường Đại học FPT Campus Cần Thơ 2025 kèm thông tin tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1882,20 +1874,24 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 10:50</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>11/06/2026 17:38</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
+          <t>Điểm chuẩn Trường Đại học FPT campus Cần Thơ 2025 là tiền đề vững chắc để Nhà trường tiếp tục triển khai các phương thức tuyển sinh cho năm 2026. Đối với các thí sinh đang có dự định trở thành sinh viên Trường Đại học FPT, việc nắm rõ kết quả trúng tuyển năm vừa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/diem-chuan-dai-hoc-fpt-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1901,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
+          <t>TOP 5 trường đào tạo ngành Truyền thông đa phương tiện tại Cần Thơ 2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1915,20 +1911,24 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:59</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>11/06/2026 12:01</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
+          <t>Ngành truyền thông đa phương tiện Cần Thơ đang trở thành tâm điểm thu hút sự chú ý của đông đảo học sinh và phụ huynh trong kỳ tuyển sinh năm 2026. Với sự bùng nổ của kỷ nguyên số và kinh tế sáng tạo, lĩnh vực này mang lại cơ hội nghề nghiệp rộng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-can-tho/</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
+          <t>Đề thi Ngữ văn THPT 2026 có khó không? Cập nhật ngay đáp án tham khảo</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026 09:29</t>
+          <t>11/06/2026 10:50</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -1956,12 +1956,12 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
+          <t>Sáng ngày 11/6, hơn 1,2 triệu sĩ tử trên cả nước đã hoàn thành môn thi đầu tiên &amp;#8211; môn Ngữ văn của kỳ thi tốt nghiệp THPT năm 2026. Đây là năm đầu tiên kỳ thi được tổ chức hoàn toàn theo Chương trình Giáo dục phổ thông (GDPT) 2018 với định dạng đề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/de-thi-dap-an-ngu-van-thpt/</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
+          <t>Thỏa thuận hợp tác giữa Trường Đại học FPT và “ông lớn” ngành bán lẻ WinCommerce mở rộng cơ hội việc làm cho sinh viên</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026 09:50</t>
+          <t>11/06/2026 09:59</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -1989,12 +1989,12 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
+          <t>Ngày 09/06/2026, Trường Đại học FPT (FPTU) và Công ty Cổ phần Dịch vụ Thương mại Tổng hợp WinCommerce (WinCommerce) chính thức ký kết Biên bản ghi nhớ (MOU), mở ra cơ hội học tập, trải nghiệm thực tế và công việc cho sinh viên nhà trường. Sự kiện có sự tham dự của bà [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/thoa-thuan-hop-tac-giua-truong-dai-hoc-fpt-va-ong-lon-nganh-ban-le-wincommerce-mo-rong-co-hoi-viec-lam-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
+          <t>[Cập nhật] Đáp án đề thi tốt nghiệp THPT tất cả môn, mã đề</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 17:11</t>
+          <t>11/06/2026 09:29</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2022,12 +2022,12 @@
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
+          <t>Để thí sinh dễ dàng tra cứu đáp án đề thi tốt nghiệp THPT nhanh chóng, chính xác, trong bài viết này, FPTU sẽ tổng hợp đầy đủ đáp án các môn thi ở từng mã đề. Cùng tìm hiểu bạn nhé! 1. Đáp án chính thức đề thi THPT môn Toán 1.1. Đáp án [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tot-nghiep-thpt/dap-an-de-thi-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
+          <t>35.000 chỗ trống, lương hấp dẫn, cạnh tranh thấp: Ngành chip bán dẫn đang chờ thế hệ kỹ sư tiếp theo</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 16:59</t>
+          <t>10/06/2026 09:50</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2055,12 +2055,12 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
+          <t>Khi ngành bán dẫn trở thành nền tảng của AI và kinh tế số, Việt Nam cần thêm hàng chục nghìn kỹ sư trong chưa đầy một thập kỷ tới. Chương trình đào tạo chuẩn quốc tế, cơ hội làm việc trong hệ sinh thái doanh nghiệp bán dẫn đang vận hành thực tế, sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/35-000-cho-trong-luong-hap-dan-canh-tranh-thap-nganh-chip-ban-dan-dang-cho-the-he-ky-su-tiep-theo/</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
+          <t>Không biết chọn ngành gì phải làm sao? 3 bước “gỡ rối” cho sĩ tử</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 13:44</t>
+          <t>09/06/2026 17:11</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2088,12 +2088,12 @@
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
+          <t>Một trong những yếu tố then chốt để có sự nghiệp bền vững chính là xác định được bản thân thực sự yêu thích và phù hợp với lĩnh vực nào. Tuy nhiên, thực tế có rất nhiều sĩ tử đang rơi vào tình trạng không biết chọn ngành gì do chưa thấu hiểu rõ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/khong-biet-chon-nganh-gi/</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
+          <t>Top 5 cách chọn ngành nghề phù hợp với bản thân</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 10:42</t>
+          <t>09/06/2026 16:59</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2121,12 +2121,12 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
+          <t>Trong hành trình trưởng thành, mỗi cá nhân đều trải qua những mốc thời gian quan trọng cần đưa ra quyết định lớn, đặc biệt là việc chọn ngành nghề phù hợp. Thế nhưng, giữa vô vàn hướng đi của xã hội hiện đại, hầu hết học sinh và sinh viên thường rơi vào trạng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chon-nganh-nghe-phu-hop/</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
+          <t>Sinh viên FPTU giành Giải Nhất tại “Olympic ICT toàn cầu” Huawei ICT Competition 2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 13:44</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2154,12 +2154,12 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
+          <t>Từ lời hứa “quay lại để làm tốt hơn” sau mùa giải năm trước, Dương Văn Hiệp &amp;#8211; sinh viên K18 chuyên ngành Trí tuệ nhân tạo &amp;#8211; đã cùng đội tuyển VN.FPTIT giành Giải Nhất nội dung Computing Track tại vòng chung kết toàn cầu diễn ra tại Thâm Quyến (Trung Quốc). Công nghệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-gianh-giai-nhat-tai-olympic-ict-toan-cau-huawei-ict-competition-2026/</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:23</t>
+          <t>09/06/2026 10:42</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -2187,12 +2187,12 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
+          <t>Hơn 1.200 sinh viên và chuyên gia tham gia FPTU Career Summit 2026, thảo luận tác động của AI, xu hướng việc làm và kỹ năng cần thiết cho tương lai. Sự kiện diễn ra ngày 6/6, do trường Đại học FPT tổ chức nhằm tạo không gian kết nối, chia sẻ và định hướng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-to-chuc-hoi-nghi-ve-tuong-lai-viec-lam/</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
+          <t>M01 là tổ hợp môn gì? Những điều cần biết về khối M01 trong tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Trong các kỳ tuyển sinh đại học, cao đẳng, bên cạnh những khối thi truyền thống như A00, B00 hay D01, khối M luôn là lựa chọn hàng đầu của những thí sinh yêu thích ngành Sư phạm. Vậy M01 là tổ hợp môn gì? Cách tính điểm và cơ hội nghề nghiệp ra sao? [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/m01-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
+          <t>Đối tượng ưu tiên tuyển sinh Đại học 2026: Ai được cộng điểm cao nhất?</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, bên cạnh điểm khu vực, việc xác định đúng đối tượng ưu tiên là yếu tố quyết định giúp thí sinh gia tăng cơ hội trúng tuyển vào các trường top đầu. Vậy năm 2026, có những nhóm đối tượng ưu tiên nào và mức điểm cộng được quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/doi-tuong-uu-tien/</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
+          <t>Điểm ưu tiên khu vực 2 là bao nhiêu? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -2286,12 +2286,12 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
+          <t>Trong mỗi kỳ tuyển sinh Đại học, Cao đẳng, bên cạnh điểm thi thực tế, điểm ưu tiên khu vực 2 luôn là mối quan tâm hàng đầu của các thí sinh. Chỉ cần chênh lệch 0,25 điểm cũng có thể thay đổi hoàn toàn kết quả đỗ hay trượt. Trong bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-2/</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
+          <t>Điểm ưu tiên khu vực 1 năm 2026: Cập nhật mới nhất theo Thông tư 06-BGDĐT</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:22</t>
+          <t>09/06/2026 09:23</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -2319,12 +2319,12 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
+          <t>Trong kỳ tuyển sinh Đại học, Cao đẳng năm 2026, các quy định về điểm ưu tiên đã có những điều chỉnh quan trọng nhằm đảm bảo tính công bằng. Đặc biệt, mức điểm ưu tiên khu vực 1 và cách tính điểm đối với thí sinh đạt điểm cao đang là vấn đề được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/diem-uu-tien-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
+          <t>Bản đồ Trường Đại học FPT: Toàn cảnh 5 Campus hiện đại trên toàn quốc</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2352,12 +2352,12 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
+          <t>Bước chân vào ngưỡng cửa đại học, chắc hẳn các tân sinh viên và gia đình sẽ không khỏi choáng ngợp trước không gian hiện đại của trường. Tại một môi trường năng động như FPTU, việc nằm lòng &amp;#8220;tấm bản đồ&amp;#8221; học đường là bí kíp để bạn không bỏ lỡ bất kỳ tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/ban-do-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
+          <t>Bằng 6.0 IELTS quy đổi điểm đại học 2026 được bao nhiêu?</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:19</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -2385,12 +2385,12 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
+          <t>Sở hữu chứng chỉ IELTS 6.0 là một lợi thế lớn trong kỳ tuyển sinh đại học năm 2026. Không chỉ giúp miễn thi tốt nghiệp môn Tiếng Anh, mức điểm này còn mở ra cánh cửa vào các trường đại học danh tiếng qua phương thức xét tuyển kết hợp. Vậy cụ thể 6.0 IELTS [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/6-0-ielts-quy-doi-diem-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
+          <t>Ngành Logistics xét khối nào? Tổ hợp môn và khối thi</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:22</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -2418,12 +2418,12 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
+          <t>Bạn đang tìm hiểu ngành Logistics xét khối nào để chuẩn bị cho kỳ thi tuyển sinh sắp tới? Hiện nay, ngành Logistics và Quản lý chuỗi cung ứng được xét tuyển ở nhiều tổ hợp môn đa dạng, phổ biến nhất là A00, A01, D01 và D07. Bài viết này, FPTU sẽ cung cấp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-logistics-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
+          <t>Lương ngành Thương mại điện tử 2026: Chi tiết theo vị trí, kinh nghiệm, khu vực</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026 09:18</t>
+          <t>09/06/2026 09:19</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -2451,12 +2451,12 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
+          <t>Lương ngành Thương mại điện tử tại Việt Nam dao động từ 8 đến 45 triệu VNĐ/tháng. Mức lương cụ thể sẽ phụ thuộc vào vị trí, năng lực thực tế và số năm kinh nghiệm. Trong bối cảnh số hóa bùng nổ, Thương mại điện tử (TMĐT) tiếp tục là ngành &amp;#8220;khát&amp;#8221; nhân lực [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/luong-nganh-thuong-mai-dien-tu/</t>
         </is>
       </c>
     </row>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
+          <t>Ngành Thương mại điện tử xét khối nào? Tổ hợp môn xét tuyển</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026 14:55</t>
+          <t>09/06/2026 09:18</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -2484,12 +2484,12 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
+          <t>&amp;#160; Bạn đang thắc mắc ngành Thương mại điện tử xét khối nào để chuẩn bị cho kỳ tuyển sinh đại học sắp tới? Bài viết này FPTU sẽ giúp bạn giải đáp chi tiết tất cả các tổ hợp môn xét tuyển, các phương thức tuyển sinh mới nhất năm 2026 và danh sách [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thuong-mai-dien-tu-xet-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
+          <t>Có nên học Thiết kế đồ họa ở FPTU? Giải đáp chi tiết cho sĩ tử</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2509,24 +2509,20 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 22:25</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>09/06/2026 09:18</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
+          <t>Mỗi mùa tuyển sinh đến, câu hỏi &amp;#8220;Có nên học Thiết kế đồ họa ở FPTU?&amp;#8221; luôn là tâm điểm chú ý trên các diễn đàn lựa chọn ngành nghề. Nếu bạn đang băn khoăn liệu Trường Đại học FPT (FPTU) có phải là bệ phóng hoàn hảo cho đam mê sáng tạo của mình hay [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/co-nen-hoc-thiet-ke-do-hoa-o-fptu/</t>
         </is>
       </c>
     </row>
@@ -2536,17 +2532,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026 07:22</t>
+          <t>08/06/2026 14:55</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -2554,12 +2550,12 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
+          <t>Trường Đại học FPT chính thức mở cổng đăng ký thông tin xét tuyển hệ đại học chính quy năm 2026 trên toàn quốc. Thí sinh đăng ký tại đây. Thông qua hệ thống đăng ký, thí sinh có thể cập nhật sớm các thông tin về phương thức tuyển sinh, ngành đào tạo, học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-cong-dang-ky-thong-tin-xet-tuyen-dai-hoc-chinh-quy-nam-2026/</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2565,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
+          <t>Trường Đại học FPT tổ chức hội nghị về tương lai việc làm: Khi AI thay đổi luật chơi, thế hệ trẻ cần chuẩn bị những gì?</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2579,20 +2575,24 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 18:09</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
+          <t>06/06/2026 22:25</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
+          <t>Ngày 06/06/2026, FPTU Career Summit 2026 do Trường Đại học FPT tổ chức đã diễn ra tại Hà Nội với sự tham gia của hơn 1.200 sinh viên, cùng các chuyên gia, diễn giả và lãnh đạo doanh nghiệp đến từ nhiều tập đoàn, tổ chức hàng đầu. Hội nghị đã mang đến không gian [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-career-summit-2026-dinh-hinh-nang-luc-cho-the-he-tre-viet-nam-truoc-lan-song-ai-va-fdi-ky-luc/</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
+          <t>Thông báo về nhu cầu bổ nhiệm chức danh Phó Giáo sư năm 2026 đợt 1</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2612,24 +2612,20 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 13:00</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>06/06/2026 07:22</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
+          <t>Căn cứ Quyết định số 37/2018/QĐ-TTg ngày 31 tháng 8 năm 2018 của Thủ tướng Chính phủ ban hành quy định tiêu chuẩn, thủ tục xét công nhận đạt tiêu chuẩn và bổ nhiệm chức danh Giáo sư, Phó Giáo sư; thủ tục xét hủy bỏ công nhận chức danh và miễn nhiệm chức danh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/thong-bao-ve-nhu-cau-bo-nhiem-chuc-danh-pho-giao-su-nam-2026-dot-1/</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2635,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
+          <t>[Đầy đủ] Tổ hợp môn thi tốt nghiệp và tổ hợp môn thi đại học 2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -2649,24 +2645,20 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026 12:25</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>05/06/2026 18:09</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
+          <t>Tổ hợp môn là danh sách 3 môn học được học sinh lựa chọn để xét công nhận tốt nghiệp và xét tuyển vào trường đại học. Việc nắm rõ danh sách các tổ hợp phổ biến và cách chọn phù hợp với năng lực sẽ giúp học sinh tăng cơ hội trúng tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/to-hop-mon/</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2668,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
+          <t>Khai trương phòng thi IELTS trên máy tính tại Trường Đại học FPT cơ sở Quy Nhơn</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -2686,20 +2678,24 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 14:02</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>05/06/2026 13:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
+          <t>Sáng 5/6, Trường Đại học FPT đã chính thức khai trương Phòng thi IELTS trên máy tính tại cơ sở Quy Nhơn (Gia Lai), đánh dấu bước tiến quan trọng trong việc chuẩn hóa hoạt động khảo thí quốc tế tại khu vực miền Trung &amp;#8211; Tây Nguyên. Đến dự lễ khai trương có các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khai-truong-phong-thi-ielts-tren-may-tinh-tai-truong-dai-hoc-fpt-co-so-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2705,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
+          <t>Trường Đại học FPT Quy Nhơn khai trương Phòng thi IELTS trên máy tính, mở rộng cơ hội khảo thí quốc tế tại miền Trung – Tây Nguyên</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -2719,20 +2715,24 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:30</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr"/>
+          <t>05/06/2026 12:25</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
+          <t>Trường Đại học FPT cơ sở Quy Nhơn vừa tổ chức lễ khai trương Phòng thi IELTS trên máy tính, đánh dấu bước tiến mới trong việc phát triển hệ sinh thái khảo thí và đào tạo quốc tế, đồng thời tạo điều kiện thuận lợi để học sinh, sinh viên và người học tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/gia-tri-cot-loi/quoc-te-hoa/truong-dai-hoc-fpt-quy-nhon-khai-truong-phong-thi-ielts-tren-may-tinh-mo-rong-co-hoi-khao-thi-quoc-te-tai-mien-trung-tay-nguyen/</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
+          <t>Sinh viên FPTU trở thành Chủ tọa trẻ tuổi nhất tại Hội thảo quốc tế ICTechED13</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -2752,24 +2752,20 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026 09:11</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>04/06/2026 14:02</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
+          <t>Nguyễn Thành Trương &amp;#8211; sinh viên K18 chuyên ngành Kỹ thuật Phần mềm Trường Đại học FPT đã trở thành Chủ tọa điều phối phiên báo cáo khoa học tại Hội thảo quốc tế ICTechED13, diễn ra tại Đại học Công nghệ King Mongkut (Thái Lan). Diễn ra ngày 28-29/5, Hội thảo khoa học quốc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-tro-thanh-chu-toa-tre-tuoi-nhat-tai-hoi-thao-quoc-te-icteched13/</t>
         </is>
       </c>
     </row>
@@ -2779,17 +2775,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
+          <t>Giải HSG tỉnh có được cộng điểm ưu tiên không? Cập nhật quy định mới nhất 2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:29</t>
+          <t>04/06/2026 09:30</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -2797,12 +2793,12 @@
       <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
+          <t>Kỳ thi chọn học sinh giỏi (HSG) cấp tỉnh là một thử thách lớn, đòi hỏi sự đầu tư công phu về thời gian và trí tuệ. Chính vì thế, câu hỏi &amp;#8220;giải HSG tỉnh có được cộng điểm ưu tiên không&amp;#8221; luôn là thắc mắc hàng đầu của các bạn thí sinh khi chuẩn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/giai-hsg-tinh-co-duoc-cong-diem-uu-tien-khong/</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2808,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
+          <t>FPTU tổ chức hội nghị chuyên sâu giúp sinh viên định hình sự nghiệp trong thời đại AI</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -2822,24 +2818,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026 14:21</t>
+          <t>04/06/2026 09:11</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Cần Thơ</t>
+          <t>Hà Nội</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
+          <t>Sáng ngày 6/6, sự kiện FPTU Career Summit 2026 do Trường Đại học FPT tổ chức với sự đồng hành của NIC &amp;#8211; Trung tâm Đổi mới sáng tạo Quốc gia sẽ diễn ra tại Khu Công nghệ cao Hòa Lạc, Hà Nội. Hội nghị chuyên sâu về định hướng nghề nghiệp và thị trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-to-chuc-hoi-nghi-chuyen-sau-giup-sinh-vien-dinh-hinh-su-nghiep-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2849,17 +2845,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
+          <t>Mega Livestream FPTU: Gen Z làm chủ công nghệ – Học gì để không bị bỏ lại trong thời đại AI?</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:53</t>
+          <t>03/06/2026 14:29</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -2867,12 +2863,12 @@
       <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
+          <t>Trước sự phát triển nhanh chóng của trí tuệ nhân tạo và công nghệ, việc lựa chọn ngành học, định hướng nghề nghiệp đang trở thành mối quan tâm lớn của nhiều học sinh THPT và phụ huynh. Những câu hỏi như “AI có thay thế con người không?”, “Ngành nào còn nhiều cơ hội [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/event/mega-livestream-fptu-gen-z-lam-chu-cong-nghe-hoc-gi-de-khong-bi-bo-lai-trong-thoi-dai-ai/</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2878,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
+          <t>Học sinh tại các trường THPT sau được nhận học bổng khu vực 1 tại Campus Cần Thơ</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -2892,20 +2888,24 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:51</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr"/>
+          <t>03/06/2026 14:21</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
+          <t>Bước vào kỳ tuyển sinh đại học năm 2026, nỗi lo về học phí và các khoản chi phí sinh hoạt luôn là bài toán khiến nhiều gia đình trăn trở. Thấu hiểu những khó khăn đó, Trường Đại học FPT liên tục triển khai nhiều chính sách hỗ trợ thiết thực nhằm đồng hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/hoc-bong-khu-vuc-1/</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
+          <t>Học ngôn ngữ Anh có khó không? Giải đáp từ A-Z và lộ trình chinh phục</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 19:22</t>
+          <t>02/06/2026 19:53</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -2933,12 +2933,12 @@
       <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
+          <t>Trong bối cảnh toàn cầu hóa, Ngôn ngữ Anh vẫn luôn là ngành học &amp;#8220;quốc dân&amp;#8221; với cơ hội việc làm rộng mở. Tuy nhiên, trước khi quyết định theo đuổi, hầu hết các bạn học sinh đều băn khoăn: &amp;#8220;Học ngôn ngữ Anh có khó không?&amp;#8221;. Thực tế, ngôn ngữ Anh không chỉ là [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-kho-khong/</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
+          <t>Bảng quy đổi điểm IELTS sang điểm thi Đại học 2026 [50++ trường]</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:55</t>
+          <t>02/06/2026 19:51</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -2966,12 +2966,12 @@
       <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, chứng chỉ IELTS không chỉ là &amp;#8220;tấm vé&amp;#8221; du học mà còn là lợi thế cực lớn trong kỳ thi tốt nghiệp THPT và xét tuyển Đại học. Vậy cách quy đổi điểm IELTS sang điểm thi Đại học hiện nay như thế nào? Trường nào ưu tiên chứng chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/quy-doi-diem-ielts-sang-diem-thi-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
+          <t>TS Lê Trường Tùng – Chủ tịch hội đồng trường FPTU được giao phụ trách điều hành Hiệp hội Các trường đại học, cao đẳng Việt Nam</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 16:52</t>
+          <t>02/06/2026 19:22</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -2999,12 +2999,12 @@
       <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
+          <t>Sáng ngày 2/6, tại Văn phòng Hiệp hội các trường đại học, cao đẳng Việt Nam, Hiệp hội công bố Quyết định chuẩn y phân công Tiến sĩ Lê Trường Tùng – Chủ tịch Hội đồng trường Trường Đại học FPT, phụ trách điều hành hoạt động của Hiệp hội. Cụ thể, theo Quyết định [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ts-le-truong-tung-chu-tich-hoi-dong-truong-fptu-duoc-giao-phu-trach-dieu-hanh-hiep-hoi-cac-truong-dai-hoc-cao-dang-viet-nam/</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
+          <t>Ngành học tạo ra “bộ não số”: Khoa học máy tính tại FPTU có gì khác biệt?</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:21</t>
+          <t>02/06/2026 16:55</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -3032,12 +3032,12 @@
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
+          <t>Tuyển sinh từ 2026, ngành Khoa học máy tính của Trường Đại học FPT cùng 2 chuyên ngành đón đầu xu hướng: Trí tuệ nhân tạo và Khoa học dữ liệu; An ninh mạng và An toàn số sẽ là cánh cửa cho các nhân tài yêu thích công nghệ trên khắp cả nước. 200.000 [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nganh-hoc-tao-ra-bo-nao-so-khoa-hoc-may-tinh-tai-fptu-co-gi-khac-biet/</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
+          <t>FPTU đào tạo ngành Khoa học máy tính theo mô hình cử nhân tài năng</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 16:52</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -3065,12 +3065,12 @@
       <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
+          <t>Chương trình Khoa học máy tính tại trường Đại học FPT (FPTU) chú trọng thực hành, đào tạo chuyên sâu về AI, dữ liệu và an ninh mạng, đáp ứng nhu cầu nhân lực công nghệ. Trường triển khai ngành Khoa học máy tính theo mô hình Cử nhân tài năng, hướng tới nhóm sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/fptu-dao-tao-nganh-khoa-hoc-may-tinh-theo-mo-hinh-cu-nhan-tai-nang/</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế đồ họa tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:01</t>
+          <t>02/06/2026 10:21</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -3098,12 +3098,12 @@
       <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
+          <t>Việc lựa chọn đúng môi trường đào tạo giúp sinh viên nắm vững kiến thức thiết kế, tư duy thẩm mỹ và kỹ năng sử dụng công cụ chuyên ngành, đồng thời mở ra nhiều cơ hội thực tập và việc làm tại các agency, studio và doanh nghiệp truyền thông lớn. Trong bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-thiet-ke-do-hoa-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
+          <t>Nên học Ngôn ngữ Anh hay Marketing? Lựa chọn nào cho tương lai bền vững?</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -3131,12 +3131,12 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
+          <t>Trước ngưỡng cửa đại học, việc chọn ngành luôn là bài toán cân não. Hai cái tên thường xuyên được đặt lên bàn cân là Ngôn ngữ Anh và Marketing. Một bên là công cụ giao tiếp toàn cầu, một bên là &amp;#8220;nghề hái ra tiền&amp;#8221; trong thời đại số. Vậy bạn nên học Ngôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nen-hoc-ngon-ngu-anh-hay-marketing/</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
+          <t>Có nên học ngôn ngữ Hàn? Cơ hội nghề nghiệp và những sự thật cần biết</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 10:00</t>
+          <t>02/06/2026 10:01</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -3164,12 +3164,12 @@
       <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
+          <t>Sự bùng nổ của làn sóng Hallyu (K-Pop, K-Drama) cùng với làn sóng đầu tư mạnh mẽ từ các tập đoàn lớn như Samsung, LG, Hyundai vào Việt Nam đã khiến tiếng Hàn trở thành một trong những ngoại ngữ &amp;#8220;quyền lực&amp;#8221; nhất. Tuy nhiên, đứng trước quyết định chọn ngành, nhiều bạn trẻ vẫn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-han/</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
+          <t>Có nên học ngôn ngữ Trung không? Cơ hội và thách thức năm 2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
+          <t>Trong bối cảnh giao thương Việt &amp;#8211; Trung ngày càng phát triển mạnh mẽ, tiếng Trung đã vươn lên trở thành một trong những ngoại ngữ quyền lực nhất. Tuy nhiên, với một ngôn ngữ tượng hình phức tạp, nhiều bạn vẫn băn khoăn: Có nên học ngôn ngữ Trung không? Bài viết này, FPTU [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-ngon-ngu-trung-khong/</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
+          <t>Học Ngôn ngữ Trung có cần học tiếng Anh không? Câu trả lời từ chuyên gia</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:57</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -3230,12 +3230,12 @@
       <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
+          <t>Khi bắt đầu theo đuổi tiếng Trung, nhiều bạn trẻ đặt ra câu hỏi: &amp;#8220;Học Ngôn ngữ Trung có cần học tiếng Anh không?&amp;#8221;. Liệu việc tập trung vào một ngôn ngữ tỷ dân đã là đủ, hay việc sở hữu cả hai mới là &amp;#8220;chìa khóa vàng&amp;#8221; cho sự nghiệp? Trong bài viết này, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-can-hoc-tieng-anh-khong/</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
+          <t>Học Ngôn ngữ Trung có dễ xin việc không? Cơ hội và mức lương năm 2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:55</t>
+          <t>02/06/2026 10:00</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -3263,12 +3263,12 @@
       <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
+          <t>Trong xu thế hội nhập kinh tế hiện nay, tiếng Trung đã trở thành một công cụ giao tiếp và kinh doanh toàn cầu. Nhiều bạn trẻ đang đứng trước quyết định chọn ngành thường thắc mắc: &amp;#8220;Học Ngôn ngữ Trung có dễ xin việc không?&amp;#8221; hay &amp;#8220;Liệu thị trường có đang bão hòa?&amp;#8221;. Bài [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-trung-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
+          <t>Chương trình học ngành Công nghệ thông tin gồm những gì? Khám phá ngay</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:54</t>
+          <t>02/06/2026 09:57</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -3296,12 +3296,12 @@
       <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
+          <t>Trong cuộc cách mạng công nghiệp 4.0, Công nghệ thông tin (CNTT) vẫn giữ vững ngôi vương là ngành học dẫn đầu xu hướng. Tuy nhiên, không ít bạn trẻ còn mơ hồ về việc mình sẽ học những gì trong suốt 4 năm đại học. Bài viết này sẽ cùng bạn khám phá chi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/chuong-trinh-hoc-nganh-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không? Lộ trình chi tiết 2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026 09:41</t>
+          <t>02/06/2026 09:55</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -3329,12 +3329,12 @@
       <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
+          <t>Học Ngôn ngữ Anh có làm giáo viên được không là câu hỏi phổ biến của các bạn yêu thích tiếng Anh nhưng không theo học ngành Sư phạm ngay từ đầu. Câu trả lời ngắn gọn là: CÓ. Tuy nhiên, để đứng trên bục giảng tại các trường công lập hay quốc tế, bạn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-ngon-ngu-anh-co-lam-giao-vien-duoc-khong/</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
+          <t>Cập nhật học phí ngành Quan hệ công chúng mới nhất 2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 13:31</t>
+          <t>02/06/2026 09:54</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -3362,12 +3362,12 @@
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Quan hệ công chúng (PR) đang trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút các bạn trẻ năng động. Tuy nhiên, bên cạnh chương trình đào tạo và cơ hội việc làm, học phí ngành Quan hệ công chúng luôn là mối quan tâm hàng đầu của các bậc phụ huynh và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
+          <t>Ngành Truyền thông thi khối nào? Tổ hợp xét tuyển 2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:38</t>
+          <t>02/06/2026 09:41</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -3395,12 +3395,12 @@
       <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, nhạy bén với xu hướng thị trường và muốn theo đuổi lĩnh vực cốt lõi của thời đại số nhưng chưa biết ngành Truyền thông thi khối nào dễ trúng tuyển nhất? Từ các khối kinh điển như A00, A01, D01, C00 đến các tổ hợp hệ X thế hệ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -3410,17 +3410,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
+          <t>Phía sau những concert cháy vé là cả một ngành học mà Gen Z có thể chưa nghĩ tới</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:28</t>
+          <t>01/06/2026 13:31</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -3428,12 +3428,12 @@
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
+          <t>Không chỉ là &amp;#8220;làm event&amp;#8221;, Quản trị giải trí và sự kiện đang trở thành một trong những hướng đi được chú ý nhất trong bối cảnh công nghiệp giải trí Việt Nam tăng tốc. Một concert kéo dài ba tiếng. Nhưng để ba tiếng đó xảy ra, cỗ máy phía sau đã vận hành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/phia-sau-nhung-concert-chay-ve-la-ca-mot-nganh-hoc-ma-gen-z-co-the-chua-nghi-toi/</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Tri Thức, Công Nghệ Và Trách Nhiệm Toàn Diện Đến Cộng Đồng</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:19</t>
+          <t>01/06/2026 00:38</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -3461,12 +3461,12 @@
       <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
+          <t>Trách nhiệm toàn diện được sinh viên Trường Đại học FPT lan tỏa qua các hoạt động công nghệ, văn hóa, môi trường và dự án cộng đồng ý nghĩa. Trách nhiệm toàn diện không chỉ là một giá trị cốt lõi trong định hướng giáo dục của Trường Đại học FPT mà còn được [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/trach-nhiem-toan-dien/</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
+          <t>Sinh Viên Trường Đại Học FPT Mang Giải Pháp Y Tế Ứng Dụng Công Nghệ Vươn Ra Quốc Tế</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:09</t>
+          <t>01/06/2026 00:28</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -3494,12 +3494,12 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
+          <t>Giải pháp y tế ứng dụng công nghệ OrcaX của sinh viên Trường Đại học FPT góp phần hỗ trợ chăm sóc sức khỏe mắt và ghi dấu ấn tại Campuchia. Giải pháp y tế ứng dụng công nghệ đang trở thành xu hướng quan trọng trong quá trình chuyển đổi số ngành y tế [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/giai-phap-y-te-ung-dung-cong-nghe/</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
+          <t>Trường Đại Học FPT Tổ Chức Workshop Tập Huấn Khai Thác Thông Tin Sáng Chế Trong Lĩnh Vực Công Nghệ Thông Tin</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -3519,24 +3519,20 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026 00:01</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>01/06/2026 00:19</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
+          <t>Thông tin sáng chế là nội dung trọng tâm của workshop tại Trường Đại học FPT, giúp nâng cao năng lực nghiên cứu và phát triển công nghệ. Thông tin sáng chế đang trở thành nguồn tài nguyên quan trọng trong hoạt động nghiên cứu, đổi mới sáng tạo và phát triển công nghệ. Nhằm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/khai-thac-thong-tin-sang-che/</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3542,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
+          <t>Dự Án Môn Học Đầy Tính Nhân Văn “Legacy Portraits” – Kết Nối Thế Hệ, Lan Tỏa Yêu Thương</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -3556,7 +3552,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:52</t>
+          <t>01/06/2026 00:09</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -3564,12 +3560,12 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
+          <t>Legacy Portraits là dự án nhân văn của sinh viên Đại học FPT, kết nối thế hệ, lưu giữ ký ức và lan tỏa yêu thương đến người cao tuổi neo đơn. Giữa nhịp sống hiện đại ngày càng hối hả, vẫn còn nhiều người cao tuổi đang sống trong hoàn cảnh neo đơn, thiếu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/legacy-portraits-ket-noi-the-he/</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3575,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
+          <t>Sinh Viên Ngành Ngôn Ngữ Hàn Trải Nghiệm Thông Dịch Thực Tế Tại Bảo Tàng TP Cần Thơ</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -3589,20 +3585,24 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:43</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr"/>
+          <t>01/06/2026 00:01</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
+          <t>Thông dịch thực tế tại Bảo tàng TP Cần Thơ giúp sinh viên ngành Ngôn ngữ Hàn Trường Đại học FPT nâng cao kỹ năng nghề nghiệp và hội nhập quốc tế. Thông dịch thực tế là một trong những hoạt động quan trọng giúp sinh viên ngành ngôn ngữ phát triển kỹ năng nghề [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thong-dich-thuc-te/</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
+          <t>Cóc Vàng Khối Ngành Kinh Tế Trường Đại Học FPT: Nguyễn Vân Long Và Hành Trình “Phá Kén”</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -3622,24 +3622,20 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 23:33</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>31/05/2026 23:52</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
+          <t>Cóc Vàng khối ngành Kinh tế là cột mốc đáng nhớ trên hành trình “phá kén” của Nguyễn Vân Long, sinh viên Digital Marketing tại Đại học FPT. Danh hiệu Cóc Vàng khối ngành Kinh tế không chỉ là sự ghi nhận cho thành tích học tập xuất sắc mà còn phản ánh hành trình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-khoi-nganh-kinh-te/</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3645,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
+          <t>Cóc Vàng Công Nghệ Thông Tin Trường Đại Học FPT – Hành Trình Biến Áp Lực Thành Động Lực Trong Kỷ Nguyên Công Nghệ</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -3659,7 +3655,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026 21:33</t>
+          <t>31/05/2026 23:43</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -3667,12 +3663,12 @@
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
+          <t>Cóc Vàng Công nghệ Thông tin là dấu mốc ấn tượng của Bùi Đức Anh, sinh viên Trí tuệ nhân tạo Trường Đại học FPT với GPA 9.44 đầy thuyết phục. Danh hiệu Cóc Vàng Công nghệ Thông tin luôn là mục tiêu mà nhiều sinh viên Trường Đại học FPT hướng tới. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/coc-vang-cong-nghe-thong-tin/</t>
         </is>
       </c>
     </row>
@@ -3682,34 +3678,34 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
+          <t>CLB F-AI Của Trường Đại Học FPT Campus Cần Thơ Ghi Dấu Ấn Công Nghệ Tại Cuộc Thi Data For Life</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 20:49</t>
+          <t>31/05/2026 23:33</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>TP.HCM</t>
+          <t>Cần Thơ</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
+          <t>Data for Life 2025 ghi nhận dấu ấn của CLB F-AI Trường Đại học FPT Cần Thơ với dự án ứng dụng AI xác thực văn bằng, phục vụ cộng đồng. Data for Life 2025 là một trong những cuộc thi công nghệ nổi bật nhất năm, quy tụ hàng nghìn thí sinh và các [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/data-for-life-2025/</t>
         </is>
       </c>
     </row>
@@ -3719,17 +3715,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
+          <t>Nữ Sinh Ngành Ngôn Ngữ Trung Quốc Và Câu Chuyện Nỗ Lực Vượt Qua Giới Hạn Để Chinh Phục Danh Hiệu Cóc Vàng</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026 13:42</t>
+          <t>31/05/2026 21:33</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -3737,12 +3733,12 @@
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
+          <t>Cóc Vàng là thành quả xứng đáng cho hành trình nỗ lực không ngừng của nữ sinh ngành Ngôn ngữ Trung Quốc Đặng Nguyễn Ngọc Trân tại Đại học FPT. Tại Trường Đại học FPT, danh hiệu Cóc Vàng không chỉ là sự ghi nhận dành cho những sinh viên có thành tích học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/humans-of-fptu/coc-vang-nganh-ngon-ngu/</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3748,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
+          <t>Phụ huynh, học sinh tìm lời giải cho bài toán chọn ngành, chọn nghề, chọn trường tại hội thảo hướng nghiệp của Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -3762,20 +3758,24 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 20:31</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>30/05/2026 20:49</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
+          <t>Trong bối cảnh chỉ còn chưa đầy hai tuần trước Kỳ thi Tốt nghiệp THPT 2026, hàng trăm phụ huynh và học sinh đã tham dự hội thảo “Cùng Trường Đại học FPT kiến tạo tương lai” diễn ra sáng 30/5 tại Trường Đại học FPT cơ sở TP.HCM, để trực tiếp tìm hiểu chương [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/phu-huynh-hoc-sinh-tim-loi-giai-cho-bai-toan-chon-nganh-chon-nghe-chon-truong-tai-hoi-thao-huong-nghiep-cua-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -3785,17 +3785,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
+          <t>Từ lớp học 20 người đến chuẩn kiểm định châu Âu: Hành trình khác biệt của sinh viên Ngôn ngữ FPTU</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:51</t>
+          <t>30/05/2026 13:42</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -3803,12 +3803,12 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
+          <t>Hình dung một ngày học của sinh viên Ngôn ngữ tại &amp;#8220;trường F&amp;#8221;: sáng luyện phản xạ ngoại ngữ cùng giảng viên bản xứ, chiều lên võ đường tập Vovinam, tối ngồi nghiên cứu xem học kỳ này đăng ký &amp;#8220;du học trải nghiệm&amp;#8221; tại Hàn Quốc, Trung Quốc hay Philippines. Nghe có vẻ khó [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tu-lop-hoc-20-nguoi-den-chuan-kiem-dinh-chau-au-hanh-trinh-khac-biet-cua-sinh-vien-ngon-ngu-fptu/</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
+          <t>Giá trị của ngành ngôn ngữ khi ‘AI dịch trong vài giây’</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:34</t>
+          <t>29/05/2026 20:31</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -3836,12 +3836,12 @@
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
+          <t>Trong thời đại AI phát triển mạnh, giá trị của ngành ngôn ngữ được mở rộng nhờ năng lực liên văn hóa, tư duy công nghệ và trải nghiệm quốc tế. Theo đại diện trường Đại học FPT, môi trường đào tạo ngành Ngôn ngữ tại đây được xây dựng theo hướng tăng trải nghiệm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/gia-tri-cua-nganh-ngon-ngu-khi-ai-dich-trong-vai-giay/</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
+          <t>Khép lại tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026: Sinh viên FPT sẵn sàng bước vào thị trường lao động toàn cầu</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -3861,24 +3861,20 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026 08:30</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Quy Nhơn</t>
-        </is>
-      </c>
+          <t>29/05/2026 08:51</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
       <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
+          <t>Tuần lễ bảo vệ khóa luận tốt nghiệp kỳ Spring 2026 của sinh viên Trường Đại học FPT đã chính thức khép lại, đánh dấu cột mốc trưởng thành sau hành trình học tập, nghiên cứu và phát triển năng lực nghề nghiệp của sinh viên ở nhiều lĩnh vực. Khép lại tuần lễ bảo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-camus-quy-nhon/khep-lai-tuan-le-bao-ve-khoa-luan-tot-nghiep-ky-spring-2026-sinh-vien-fpt-san-sang-buoc-vao-thi-truong-lao-dong-toan-cau/</t>
         </is>
       </c>
     </row>
@@ -3888,17 +3884,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION”</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026 10:33</t>
+          <t>29/05/2026 08:34</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -3906,12 +3902,12 @@
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
+          <t>WORKSHOP “END-TO-END RESEARCH: FROM QUESTION TO PUBLICATION” ĐÃ DIỄN RA THÀNH CÔNG!  Ngày 16/05/2026 vừa qua, Phòng Công tác sinh viên phối hợp cùng Bộ môn CF tổ chức Workshop “End-to-End Research: From Question to Publication” với sự tham gia 200 sinh viên quan tâm đến nghiên cứu khoa học, năng lực AI cần thiết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
+          <t>https://daihoc.fpt.edu.vn/trai-nghiem-sinh-vien/workshop-end-to-end-research-from-question-to-publication/</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3917,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
+          <t>Kỳ thi IELTS chính thức được tổ chức lần đầu tiên tại Trường Đại học FPT Quy Nhơn</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -3931,20 +3927,24 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 11:02</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr"/>
+          <t>29/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Quy Nhơn</t>
+        </is>
+      </c>
       <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
+          <t>Tin vui dành cho các bạn sinh viên và học viên tại Quy Nhơn — nay đã có IDP tại Trường Đại học FPT Quy Nhơn, không cần phải đi đâu xa vẫn có thể đăng ký và tham gia kỳ thi IELTS chính thức thuận tiện hơn bao giờ hết Cơ hội nhận ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
+          <t>https://daihoc.fpt.edu.vn/chua-phan-loai/ky-thi-ielts-chinh-thuc-duoc-to-chuc-lan-dau-tien-tai-truong-dai-hoc-fpt-quy-nhon/</t>
         </is>
       </c>
     </row>
@@ -3954,34 +3954,30 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
+          <t>Kỷ nguyên “kinh tế cảm xúc”: Khi trải nghiệm khách hàng trở thành nghề nghiệp quyền lực của thời đại số</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:38</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>28/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
+          <t>Trong cuộc đua sinh tồn của kinh tế số, doanh nghiệp không còn cạnh tranh bằng giá hay sản phẩm. Họ cạnh tranh bằng cảm xúc. Và người biến cảm xúc thành chiến lược &amp;#8211; đó chính là chuyên gia Quản trị Trải nghiệm Khách hàng. Cuộc chiến mới của kinh doanh hiện đại Hãy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/ky-nguyen-kinh-te-cam-xuc-khi-trai-nghiem-khach-hang-tro-thanh-nghe-nghiep-quyen-luc-cua-thoi-dai-so/</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3987,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Sinh viên FPTU dùng AI “đánh thức” di sản Việt bằng mô hình tương tác</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4001,24 +3997,20 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:32</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>27/05/2026 11:02</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
       <c r="F103" s="2" t="inlineStr"/>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
+          <t>Từ những làn điệu quan họ, hát Xoan hay Xòe Thái, nhóm sinh viên Digital Marketing Trường Đại học FPT đã tạo nên “Dáng hình di sản”, dự án kết hợp mô hình 3D, AI và trải nghiệm tương tác để đưa văn hoá truyền thống đến gần hơn với thế hệ trẻ. “Dáng hình [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-dung-ai-danh-thuc-di-san-viet-bang-mo-hinh-tuong-tac/</t>
         </is>
       </c>
     </row>
@@ -4028,30 +4020,34 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
+          <t>FPTU Chess Club: Nơi sinh viên Trường Đại học FPT rèn luyện tư duy chiến lược và phát triển toàn diện qua từng hoạt động</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026 09:09</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>27/05/2026 09:38</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
+          <t>FPTU Chess Club được thành lập năm 2012, trực thuộc Trường Đại học FPT Hà Nội, với mục tiêu xây dựng môi trường sinh hoạt dành cho sinh viên yêu thích cờ vua, cờ tướng, cờ caro và các hình thức tư duy chiến thuật liên quan. Tại đây, sinh viên có cơ hội giao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-chess-club-noi-sinh-vien-truong-dai-hoc-fpt-ren-luyen-tu-duy-chien-luoc-va-phat-trien-toan-dien-qua-tung-hoat-dong/</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4057,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>FPTU English Club: Không gian rèn luyện tiếng Anh cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4071,7 +4067,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 16:11</t>
+          <t>27/05/2026 09:32</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -4083,12 +4079,12 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
+          <t>Tiếng Anh là kỹ năng cần được luyện tập thường xuyên, không chỉ qua giáo trình mà còn qua giao tiếp, làm việc nhóm và các tình huống thực tế. Với sinh viên đại học, một môi trường đủ cởi mở để thực hành mỗi ngày sẽ giúp việc học ngôn ngữ trở nên tự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-english-club-khong-gian-ren-luyen-tieng-anh-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4094,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
+          <t>Khi dữ liệu trở thành quyền lực: Thế hệ chuyên gia mới đang được đào tạo như thế nào?</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:52</t>
+          <t>27/05/2026 09:09</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -4116,12 +4112,12 @@
       <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
+          <t>Hơn một thập kỷ trước, khi nhắc đến nghề phân tích dữ liệu, không ít người vẫn hình dung đó là công việc quanh quẩn với những bảng Excel và những con số có phần khô cứng. Ngày nay, cách nhìn đó đã thay đổi đáng kể khi dữ liệu dần trở thành nền tảng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-du-lieu-tro-thanh-quyen-luc-the-he-chuyen-gia-moi-dang-duoc-dao-tao-nhu-the-nao/</t>
         </is>
       </c>
     </row>
@@ -4131,30 +4127,34 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
+          <t>FPTU Data Science Club: Không gian học thuật và thực hành AI, Data Science cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 10:10</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr"/>
+          <t>26/05/2026 16:11</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F107" s="2" t="inlineStr"/>
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
+          <t>Được thành lập năm 2020, FPTU Data Science Club — FDS — là câu lạc bộ chuyên môn trực thuộc Trường Đại học FPT cơ sở Hà Nội, quy tụ những sinh viên có niềm yêu thích với Trí tuệ nhân tạo — AI — và Khoa học Dữ liệu — Data Science. Không chỉ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-data-science-club-khong-gian-hoc-thuat-va-thuc-hanh-ai-data-science-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
+          <t>Đại học FPT vừa mở chuyên ngành ‘chưa tốt nghiệp đã được doanh nghiệp săn đón’, tân binh cũng nhận lương 18-30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4174,24 +4174,20 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026 09:22</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>26/05/2026 10:52</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
+          <t>Đây được xem là bước đi nhằm đón đầu nhu cầu nhân lực công nghệ cao trong kỷ nguyên công nghiệp số. Trong bối cảnh trí tuệ nhân tạo (AI), robot và tự động hóa trở thành những lĩnh vực tăng trưởng nhanh trên toàn cầu, Đại học FPT vừa công bố mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-vua-mo-chuyen-nganh-chua-tot-nghiep-da-duoc-doanh-nghiep-san-don-tan-binh-cung-nhan-luong-18-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4201,17 +4197,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
+          <t>Cuộc đua nhân lực thời AI: Những chuyên ngành công nghệ đang được săn đón nhất</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 19:40</t>
+          <t>26/05/2026 10:10</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -4219,12 +4215,12 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
+          <t>AI đã biết code, biết vẽ, biết viết, thậm chí có thể thay con người xử lý hàng loạt tác vụ chỉ trong vài giây. Vậy học Công nghệ thông tin bây giờ để làm gì? Câu trả lời không nằm ở việc &amp;#8220;cạnh tranh với AI&amp;#8221;, mà ở việc trở thành những người tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuoc-dua-nhan-luc-thoi-ai-nhung-chuyen-nganh-cong-nghe-dang-duoc-san-don-nhat/</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4230,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
+          <t>FPTU Pickleball Club: Khi đam mê thể thao tạo nên môi trường phát triển toàn diện cho sinh viên Trường Đại học FPT cơ sở Hà Nội</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -4244,20 +4240,24 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:18</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+          <t>26/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
+          <t>Được thành lập năm 2024, FPTU Pickleball Club là câu lạc bộ thể thao trực thuộc Trường Đại học FPT cơ sở Hà Nội. CLB xây dựng môi trường để sinh viên yêu thích pickleball không chỉ được luyện tập và thi đấu, mà còn có cơ hội tham gia vận hành sự kiện, phối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/doi-song-sinh-vien-fptuhn/fptu-pickleball-club-khi-dam-me-the-thao-tao-nen-moi-truong-phat-trien-toan-dien-cho-sinh-vien-truong-dai-hoc-fpt-co-so-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
+          <t>Hàng trăm phụ huynh tham dự hội thảo về chọn đại học cho hành trình trưởng thành của người trẻ của FPTU</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -4277,24 +4277,20 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:17</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>25/05/2026 19:40</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
       <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
+          <t>Tại hội thảo “Hiểu đúng &amp;#8211; Quyết định đúng” do Trường Đại học FPT tổ chức, hàng trăm phụ huynh và học sinh lớp 12 cùng thảo luận về một câu hỏi mới của kỷ nguyên AI: cần trang bị cho người trẻ những kỹ năng gì để “bất biến” trước mọi thời đại. Ngày [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-phu-huynh-tham-du-hoi-thao-ve-chon-dai-hoc-cho-hanh-trinh-truong-thanh-cua-nguoi-tre-cua-fptu/</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4300,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
+          <t>TOP 10+ trường đào tạo ngành Thiết kế vi mạch bán dẫn tốt nhất Việt Nam</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -4314,7 +4310,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
+          <t>25/05/2026 17:18</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -4322,12 +4318,12 @@
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
+          <t>Ngành công nghiệp bán dẫn đang bước vào kỷ nguyên vàng tại Việt Nam. Với mục tiêu đào tạo 50.000 kỹ sư chất lượng cao phục vụ thị trường trong nước và quốc tế, ngành Thiết kế vi mạch bán dẫn trở thành &amp;#8220;thỏi nam châm&amp;#8221; thu hút Gen Z trong các mùa tuyển sinh. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-vi-mach-ban-dan-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4333,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
+          <t>TOP 3 trường Đại học Công nghệ thông tin hàng đầu tại Cần Thơ</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -4347,20 +4343,24 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:15</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr"/>
+          <t>25/05/2026 17:17</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
+          <t>Trong bối cảnh chuyển đổi số phát triển mạnh mẽ, nhu cầu theo học các ngành công nghệ thông tin ngày càng gia tăng, đặc biệt tại khu vực Đồng bằng sông Cửu Long. Nếu bạn đang tìm kiếm Trường Đại học Công nghệ thông tin tại Cần Thơ có chất lượng đào tạo tốt, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dai-hoc-cong-nghe-thong-tin-can-tho/</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
+          <t>Nữ học Logistics ra làm gì? TOP 5 vị trí “hái ra tiền” và cơ hội nghề nghiệp 2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:14</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -4388,12 +4388,12 @@
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
+          <t>Nhiều bạn nữ yêu thích sự năng động của chuỗi cung ứng nhưng vẫn lo ngại: &amp;#8220;Nữ học Logistics ra làm gì? Có phải làm việc nặng nhọc không?&amp;#8221;. Sự thật là trong kỷ nguyên Logistics 4.0, sự tỉ mỉ, kỹ năng đàm phán và tư duy quản lý của phái đẹp chính là &amp;#8220;vũ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nu-hoc-logistics-ra-lam-gi/</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
+          <t>Logistics cần học những môn gì? Lộ trình đào tạo chi tiết từ A – Z (Cập nhật 2026)</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:13</t>
+          <t>25/05/2026 17:15</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -4421,12 +4421,12 @@
       <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
+          <t>Trong bối cảnh thương mại điện tử bùng nổ, các chuỗi cung ứng thông minh dịch chuyển mạnh mẽ về Việt Nam vào năm 2026, ngành học Logistics ngày càng chứng minh được sức hút &amp;#8220;khủng&amp;#8221; đối với thế hệ trẻ. Để thành công, sinh viên Logistics cần học những môn gì? Đâu là lộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/logistics-can-hoc-nhung-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
+          <t>Marketing khối C00 học trường nào? TOP 10+ trường đào tạo uy tín nhất 2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026 17:12</t>
+          <t>25/05/2026 17:14</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -4454,12 +4454,12 @@
       <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
+          <t>Trong những năm gần đây, xu hướng xét tuyển đại học bằng các tổ hợp môn xã hội đang tăng mạnh. Trong đó, câu hỏi &amp;#8220;Marketing khối C00 học trường nào?&amp;#8221; trở thành chủ đề thảo luận sôi nổi trên các diễn đàn giáo dục. Việc các trường kinh tế mở rộng xét tuyển khối [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/marketing-khoi-c00-hoc-truong-nao/</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
+          <t>Ngành Truyền thông đa phương tiện có dễ xin việc không? Bức tranh toàn cảnh 2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:54</t>
+          <t>25/05/2026 17:13</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -4487,12 +4487,12 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
+          <t>Giữa thời điểm thị trường lao động có nhiều biến động, liệu cơ hội việc làm của ngành Truyền thông đa phương tiện có thực sự rộng mở cho các cử nhân tương lai? Hãy cùng FPTU phân tích thực trạng thị trường và giải mã sức hút của lĩnh vực đầy tiềm năng này. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-da-phuong-tien-co-de-xin-viec-khong/</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
+          <t>Ngành Công nghệ truyền thông thi khối nào? Cập nhật xu hướng tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 14:52</t>
+          <t>25/05/2026 17:12</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -4520,12 +4520,12 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, Công nghệ truyền thông đã trở thành một trong những ngành học dẫn dắt xu hướng nghề nghiệp. Sự kết hợp giữa năng lực công nghệ và tư duy sáng tạo mở ra không gian phát triển không giới hạn cho người học. Tuy nhiên, trước các đổi mới trong quy [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-cong-nghe-truyen-thong-thi-khoi-nao/</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
+          <t>Khi AI viết lại bản đồ ngành kinh tế: Trường đại học FPTU đào tạo gì cho thế hệ nhân lực số mới?</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 13:38</t>
+          <t>22/05/2026 14:54</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -4553,12 +4553,12 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
+          <t>Trong kỷ nguyên số, AI có thể viết content, phân tích hành vi khách hàng hay dự báo tài chính chỉ trong vài giây. Khi công nghệ đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/khi-ai-viet-lai-ban-do-nganh-kinh-te-truong-dai-hoc-fptu-dao-tao-gi-cho-the-he-nhan-luc-so-moi/</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
+          <t>Thi Tốt nghiệp THPT 2026: Cách đánh giá năng lực cá nhân trong giai đoạn nước rút</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 10:33</t>
+          <t>22/05/2026 14:52</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -4586,12 +4586,12 @@
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
+          <t>Chỉ còn chưa đầy 20 ngày trước kỳ thi Tốt nghiệp THPT 2026, áp lực ôn tập đang tăng dần khi thời gian ngày càng rút ngắn. Tuy nhiên, ở giai đoạn này, việc học nhiều chưa chắc đã hiệu quả bằng việc hiểu rõ năng lực hiện tại của bản thân và xây dựng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-da-nang/thi-tot-nghiep-thpt-2026-cach-danh-gia-nang-luc-ca-nhan-trong-giai-doan-nuoc-rut/</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
+          <t>Đại học FPT mở ngành Robot và AI đón đầu thị trường lương trăm triệu</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:29</t>
+          <t>22/05/2026 13:38</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -4619,12 +4619,12 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
+          <t>Trường Đại học FPT vừa mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid), lĩnh vực đang có nhu cầu nhân lực cao với mức thu nhập hấp dẫn. Chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) được xây dựng được thiết kế theo mô [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dai-hoc-fpt-mo-nganh-robot-va-ai-don-dau-thi-truong-luong-tram-trieu/</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Khối ngành Ngôn ngữ FPTU đạt chuẩn kiểm định quốc tế châu Âu AQAS</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:23</t>
+          <t>22/05/2026 10:33</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -4652,12 +4652,12 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
+          <t>3 chương trình đào tạo thuộc khối ngành Ngôn ngữ của Trường Đại học FPT vừa chính thức đạt kiểm định quốc tế AQAS &amp;#8211; tổ chức kiểm định chất lượng giáo dục uy tín của Đức, được công nhận trên toàn châu Âu.  Ngày 18/5, theo quyết định của Ủy ban Thường trực AQAS, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/khoi-nganh-ngon-ngu-fptu-dat-chuan-kiem-dinh-quoc-te-chau-au-aqas/</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo: Đón đầu cuộc đua UAV và Robot hình người</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026 09:20</t>
+          <t>22/05/2026 09:29</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -4685,12 +4685,12 @@
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT (FPTU) chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-don-dau-cuoc-dua-uav-va-robot-hinh-nguoi/</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 16:08</t>
+          <t>22/05/2026 09:23</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -4718,12 +4718,12 @@
       <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
+          <t>Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng đến đào tạo nguồn nhân lực chất lượng cao, có kiến thức chuyên sâu về robot và trí tuệ nhân tạo, đồng thời, có khả năng vận dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>Cử nhân ngành Robot và AI có thể nhận mức lương từ 18 đến 30 triệu đồng/tháng</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:46</t>
+          <t>22/05/2026 09:20</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -4751,12 +4751,12 @@
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chuyên ngành Robot và Trí tuệ nhân tạo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cu-nhan-nganh-robot-va-ai-co-the-nhan-muc-luong-tu-18-den-30-trieu-dong-thang/</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
+          <t>AI đang định nghĩa lại ngành kinh tế: Những chuyên ngành hút Gen Z mùa tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:34</t>
+          <t>21/05/2026 16:08</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -4784,12 +4784,12 @@
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
+          <t>Khi AI đang tái định hình cách doanh nghiệp vận hành, bản đồ ngành nghề của lĩnh vực kinh tế cũng đang được vẽ lại và thế hệ tuyển sinh 2026 đang đứng trước những lựa chọn hoàn toàn khác trước. Dưới đây là 5 chuyên ngành kinh tế của Trường Đại học FPT đang được thị [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ai-dang-dinh-nghia-lai-nganh-kinh-te-nhung-chuyen-nganh-hut-gen-z-mua-tuyen-sinh-2026/</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:26</t>
+          <t>21/05/2026 15:46</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
@@ -4817,12 +4817,12 @@
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Ngày 21-5, Trường ĐH FPT cho biết vừa chính thức mở chuyên ngành robot và trí tuệ nhân tạo (AI) thuộc ngành công nghệ thông tin. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot-2/</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
+          <t>Trường ĐH FPT mở chuyên ngành mới, hướng đến UAV và robot</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -4842,24 +4842,20 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:21</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>21/05/2026 15:34</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
+          <t>Điểm nổi bật của chuyên ngành này là định hướng đào tạo theo công nghệ tiên tiến, trong đó có máy bay không người lái và robot hình người. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dh-fpt-mo-chuyen-nganh-moi-huong-den-uav-va-robot/</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4865,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
+          <t>Mở chuyên ngành mới đón đầu làn sóng Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -4879,7 +4875,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:07</t>
+          <t>21/05/2026 15:26</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr"/>
@@ -4887,12 +4883,12 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
+          <t>VTV.vn &amp;#8211; Nhu cầu nhân lực chất lượng cao trong lĩnh vực trí tuệ nhân tạo (AI) và robotics đang tăng trưởng đột biến. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, nhu cầu nhân lực chất lượng cao trong lĩnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/mo-chuyen-nganh-moi-don-dau-lan-song-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4898,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
+          <t>Sinh viên FPTU ra quân hỗ trợ chuyển đổi số tại xã Vân Đình (Hà Nội)</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -4912,20 +4908,24 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 15:01</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr"/>
+          <t>21/05/2026 15:21</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
+          <t>Sáng 21/5, 43 sinh viên Trường Đại học FPT chính thức ra quân hỗ trợ chuyển đổi số tại xã Vân Đình, tham gia các hoạt động hỗ trợ người dân, trường học và các cơ quan hành chính tại địa phương tiếp cận công nghệ số, dịch vụ công trực tuyến và ứng dụng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/sinh-vien-fptu-ra-quan-ho-tro-chuyen-doi-so-tai-xa-van-dinh-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
+          <t>Tuyển sinh 2026: Trường Đại học FPT mở thêm chuyên ngành gắn với robot</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 14:33</t>
+          <t>21/05/2026 15:07</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr"/>
@@ -4953,12 +4953,12 @@
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
+          <t>Mùa tuyển sinh 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid). Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/tuyen-sinh-2026-truong-dai-hoc-fpt-mo-them-chuyen-nganh-gan-voi-robot/</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng đặc biệt</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 11:00</t>
+          <t>21/05/2026 15:01</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr"/>
@@ -4986,12 +4986,12 @@
       <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
+          <t>Trường đại học FPT mở chuyên ngành robot và trí tuệ nhân tạo theo định hướng UAV, humanoid, tập trung đào tạo drone, robot hình người và các hệ thống tự động. Năm 2026, Trường đại học FPT chính thức mở chuyên ngành robot và trí tuệ nhân tạo (định hướng UAV và humanoid) thuộc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/truong-dai-hoc-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-theo-dinh-huong-dac-biet/</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
+          <t>Đón sóng UAV, đại học của Chủ tịch FPT Trương Gia Bình lập tức có quyết định mới, thực hiện ngay năm nay</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026 09:36</t>
+          <t>21/05/2026 14:33</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr"/>
@@ -5019,12 +5019,12 @@
       <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
+          <t>Quyết định này thể hiện định hướng đón đầu xu thế công nghệ và nhu cầu nhân lực của thị trường. Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, trường Đại học FPT &amp;#8211; thuộc Tập đoàn FPT của [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/don-song-uav-dai-hoc-cua-chu-tich-fpt-truong-gia-binh-lap-tuc-co-quyet-dinh-moi-thuc-hien-ngay-nam-nay/</t>
         </is>
       </c>
     </row>
@@ -5034,17 +5034,17 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>ĐH FPT mở chuyên ngành Robot và Trí tuệ nhân tạo</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 19:08</t>
+          <t>21/05/2026 11:00</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dh-fpt-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
+          <t>Toàn cầu không bắt đầu từ sân bay: Câu chuyện về một thế hệ trẻ Việt Nam mang theo tiếng đàn bầu ra thế giới</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 17:08</t>
+          <t>21/05/2026 09:36</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
@@ -5085,12 +5085,12 @@
       <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
+          <t>Trong một phòng thí nghiệm tại Đại học Tokyo, vị Tiến sĩ trẻ người Việt Tạ Đức Tùng ngồi lặng thinh hàng giờ trước màn hình. Đề án anh kỳ công xây dựng vừa bị từ chối tài trợ. Hướng nghiên cứu tưởng đã đúng, bất ngờ rẽ vào ngõ cụt. Anh quay lại từ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/toan-cau-khong-bat-dau-tu-san-bay/</t>
         </is>
       </c>
     </row>
@@ -5100,34 +5100,30 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
+          <t>Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:57</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Cần Thơ</t>
-        </is>
-      </c>
+          <t>20/05/2026 19:08</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, năm 2026, Trường Đại học FPT chính thức mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin. Chương trình hướng tới việc [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-chinh-thuc-mo-chuyen-nganh-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5133,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
+          <t>2k8 còn bao nhiêu ngày thi THPT quốc gia 2026? Đếm ngược ngày thi</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -5147,7 +5143,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 16:41</t>
+          <t>20/05/2026 17:08</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
@@ -5155,12 +5151,12 @@
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT 2026 đang đến gần, câu hỏi &amp;#8220;2k8 còn bao nhiêu ngày thi THPT Quốc gia 2026&amp;#8221; đang trở thành tâm điểm chú ý trên các diễn đàn giáo dục. Việc nắm bắt chính xác thời gian đếm ngược không chỉ giúp các sĩ tử chủ động trong lộ trình ôn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/2k8-con-bao-nhieu-ngay-thi-thpt-quoc-gia-2026/</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5166,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
+          <t>Học phí các trường đại học ở Cần Thơ cập nhật mới nhất 2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -5180,20 +5176,24 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:37</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr"/>
+          <t>20/05/2026 16:57</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
       <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
+          <t>Học phí các trường đại học ở Cần Thơ dao động khoảng 10 &amp;#8211; 60 triệu đồng/kỳ (tương đương 20 &amp;#8211; 120 triệu/năm), trung bình 80 &amp;#8211; 480 triệu cho 4 năm học. Mức phí có sự khác biệt rõ giữa các nhóm ngành và chương trình đào tạo. Bên cạnh đó, mỗi trường còn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-phi-cac-truong-dai-hoc-o-can-tho/</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
+          <t>C19 là tổ hợp môn gì? Môn thi và các nhóm ngành phổ biến</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026 09:02</t>
+          <t>20/05/2026 16:41</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr"/>
@@ -5221,12 +5221,12 @@
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
+          <t>Trong bối cảnh đa dạng hóa thi tuyển đại học, tổ hợp C19 ngày càng được nhiều thí sinh quan tâm nhờ phù hợp với thế mạnh khoa học xã hội. Vậy C19 là tổ hợp môn gì? gồm những môn nào, có ưu điểm gì và phù hợp với ngành học nào? Bài viết [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/c19-la-to-hop-mon-gi/</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
+          <t>Học lực khá nên chọn ngành nào khối A, B, C, D?</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:46</t>
+          <t>20/05/2026 09:37</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr"/>
@@ -5254,12 +5254,12 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
+          <t>Thành công tại giảng đường đại học không chỉ dựa trên bảng điểm trung bình ở bậc phổ thông mà còn phụ thuộc vào sự nỗ lực và khả năng thích nghi của mỗi cá nhân. Thí sinh cần hiểu rằng thành tích học tập cấp 3 ở mức khá là một nền tảng tốt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/hoc-luc-kha-nen-chon-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
+          <t>Làm sao để biết mình phù hợp với ngành nào?</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:33</t>
+          <t>20/05/2026 09:02</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr"/>
@@ -5287,12 +5287,12 @@
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
+          <t>Việc xác định làm sao để biết mình phù hợp với ngành nào không chỉ đơn thuần là chọn một môi trường học tập, mà là đặt viên gạch đầu tiên cho sự nghiệp lâu dài. Trong bối cảnh thị trường lao động đầy biến động, thí sinh cần có cái nhìn thấu đáo để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/lam-sao-de-biet-minh-phu-hop-voi-nganh-nao/</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
+          <t>Nhóm Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Với 2 Bài Báo Quốc Tế Về Ứng Dụng Trí Tuệ Nhân Tạo Trong Y Khoa</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 23:10</t>
+          <t>19/05/2026 23:46</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr"/>
@@ -5320,12 +5320,12 @@
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
+          <t>Nhóm sinh viên Trường Đại học FPT ghi dấu ấn với 2 bài báo quốc tế về ứng dụng trí tuệ nhân tạo trong y khoa hỗ trợ chẩn đoán ung thư vú. Sở hữu một bài báo khoa học quốc tế đã là cột mốc đáng tự hào với nhiều sinh viên, nhưng tại [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/ung-dung-tri-tue-nhan-tao/</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
+          <t>Sinh Viên Trường Đại Học FPT Ghi Dấu Ấn Ở Diễn Đàn Học Thuật Quốc Tế Tại Malaysia</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 22:33</t>
+          <t>19/05/2026 23:33</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr"/>
@@ -5353,12 +5353,12 @@
       <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT tự tin tham gia diễn đàn học thuật quốc tế tại Malaysia với nhiều đề tài nghiên cứu ứng dụng AI và công nghệ hiện đại. Vừa qua, từ ngày 10/04/2026 đến ngày 12/04/2026 tại Kuala Lumpur, Malaysia, sinh viên Trường Đại học FPT đã tham gia báo cáo [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/dien-dan-hoc-thuat-quoc-te/</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
+          <t>Trường Đại Học FPT Ký Kết Hợp Tác Với Đại Học Đài Cương (Đài Loan), Mở Rộng Cơ Hội Trải Nghiệm Quốc Tế Cho Sinh Viên</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -5378,24 +5378,20 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 17:19</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>19/05/2026 23:10</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác với TSUST (Đài Loan), mở rộng cơ hội trải nghiệm quốc tế cho sinh viên thông qua nhiều chương trình học tập hấp dẫn. Ngày 14/04/2026, Trường Đại học FPT chính thức ký kết Biên bản ghi nhớ hợp tác (MOU) với Đại học Khoa học và [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
+          <t>https://daihoc.fpt.edu.vn/doanh-nghiep-hop-tac-co-so-ha-noi/trai-nghiem-quoc-te-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5401,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
+          <t>Sinh Viên Trường Đại Học FPT Xuất Sắc Giành Trọn Bộ Huy Chương Tại Cúp Thế Giới Kickboxing 2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -5415,24 +5411,20 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
+          <t>19/05/2026 22:33</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
+          <t>Sinh viên Trường Đại học FPT Trương Tấn Lộc xuất sắc giành HCV, HCB và HCĐ tại Cúp thế giới Kickboxing 2026 diễn ra ở Thái Lan. Trương Tấn Lộc – sinh viên Trường Đại học FPT – đã ghi dấu ấn mạnh mẽ trên đấu trường quốc tế khi cùng đội tuyển Kickboxing Việt [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/cup-the-gioi-kickboxing-2026/</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5434,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng 3 hiệp hội công nghệ tại TP.HCM, thúc đẩy đào tạo nguồn nhân lực chất lượng cao</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -5452,24 +5444,24 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:15</t>
+          <t>19/05/2026 17:19</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Hà Nội</t>
+          <t>TP.HCM</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
+          <t>Ngày 19/5, tại TP.HCM đã diễn ra lễ ký kết Biên bản ghi nhớ hợp tác (MOU) giữa Trường Đại học FPT với ba hiệp hội công nghệ trên địa bàn gồm Hội Tin học TP.HCM (HCA), Hội Truyền thông &amp;#8211; Điện tử TP.HCM (EIC) và Hội Công nghệ Vi mạch Bán dẫn TP.HCM (HSIA). [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-noi-bat-muc-tin-tuc/truong-dai-hoc-fpt-ky-ket-hop-tac-cung-3-hiep-hoi-cong-nghe-tai-tp-hcm-thuc-day-dao-tao-nguon-nhan-luc-chat-luong-cao/</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5471,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
+          <t>TOP 4 trường đào tạo Truyền thông đa phương tiện Đà Nẵng</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -5492,17 +5484,21 @@
           <t>19/05/2026 15:15</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
+          <t>Học Truyền thông đa phương tiện Đà Nẵng ở đâu để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp sau tốt nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc, phát triển kỹ năng thực hành và tạo lợi thế cạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-da-phuong-tien-da-nang/</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5508,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
+          <t>TOP 5 trường đào tạo Truyền thông đa phương tiện Hà Nội</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -5522,20 +5518,24 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:14</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
+          <t>Bạn đam mê sáng tạo, thích làm chủ công nghệ và muốn dấn thân vào thế giới nội dung số đầy biến động? Truyền thông đa phương tiện chính là cánh cửa mở ra những cơ hội việc làm &amp;#8220;nghìn đô&amp;#8221; dành cho bạn. Để giúp bạn dễ dàng lựa chọn điểm đến học tập [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/dao-tao-truyen-thong-da-phuong-tien-ha-noi/</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
+          <t>Có nên học ngành Quan hệ công chúng? Cơ hội và thách thức trong kỷ nguyên số 2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
+          <t>19/05/2026 15:15</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr"/>
@@ -5563,12 +5563,12 @@
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học năng động và có sức ảnh hưởng lớn nhất hiện nay, Quan hệ công chúng (PR) luôn chiếm vị trí ưu tiên. Tuy nhiên, trước sự thay đổi chóng mặt của công nghệ và trí tuệ nhân tạo, nhiều bạn trẻ vẫn thắc mắc: &amp;#8220;Có nên học ngành Quan [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/co-nen-hoc-nganh-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
+          <t>Nên chọn ngành Truyền thông hay Quan hệ công chúng? Cẩm nang định hướng 2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5588,24 +5588,20 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 15:04</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>19/05/2026 15:14</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
+          <t>Trong danh sách các ngành học &amp;#8220;quyền lực&amp;#8221; nhất kỷ nguyên số, Truyền thông và Quan hệ công chúng (PR) luôn là hai cái tên khiến nhiều bạn trẻ phải cân não. Dù có mối liên hệ mật thiết, nhưng lộ trình phát triển và bản chất công việc của hai ngành này lại có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/truyen-thong-va-quan-he-cong-chung/</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5611,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
+          <t>Ngành truyền thông học trường gì? TOP 11 trường đào tạo uy tín hàng đầu 2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -5625,7 +5621,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 13:55</t>
+          <t>19/05/2026 15:04</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
@@ -5633,12 +5629,12 @@
       <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
+          <t>Ngành truyền thông học trường gì để vừa có môi trường đào tạo chất lượng, vừa mở rộng cơ hội nghề nghiệp? Việc chọn đúng trường sẽ giúp bạn xây dựng nền tảng kiến thức vững chắc và lợi thế cạnh tranh sớm. Hiện nay, nhiều trường đại học tại Việt Nam có thế mạnh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-truyen-thong-hoc-truong-gi/</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5644,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
+          <t>TOP 8 trường đào tạo ngành An toàn thông tin uy tín tại TP.HCM</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -5658,20 +5654,24 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 11:40</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr"/>
+          <t>19/05/2026 15:04</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
+          <t>Trong bối cảnh an ninh mạng ngày càng trở thành vấn đề then chốt, ngành An toàn thông tin đang thu hút sự quan tâm mạnh mẽ từ học sinh &amp;#8211; sinh viên tại TP.HCM. Tuy vậy, nhiều bạn vẫn còn băn khoăn ngành An toàn thông tin học trường nào ở TP.HCM để có [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/nganh-an-toan-thong-tin-hoc-truong-nao-o-tphcm/</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
+          <t>THÚC ĐẨY HỆ SINH THÁI KHỞI NGHIỆP SÁNG TẠO: Trường Đại học FPT ký kết hợp tác cùng Sở Khoa học và công nghệ tỉnh Gia Lai</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026 09:04</t>
+          <t>19/05/2026 13:55</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr"/>
@@ -5699,12 +5699,12 @@
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
+          <t>Trường Đại học FPT ký kết hợp tác cùng Sở KH&amp;#38;CN tỉnh Gia Lai nhằm thúc đẩy hệ sinh thái khởi nghiệp sáng tạo, đổi mới sáng tạo và phát triển nguồn nhân lực thời AI. Trường Đại học FPT ký kết hợp tác thúc đẩy hệ sinh thái khởi nghiệp sáng tạo tại Gia [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/hop-tac-doanh-nghiep-va-ojt/thuc-day-he-sinh-thai-khoi-nghiep-sang-tao-truong-dai-hoc-fpt-ky-ket-hop-tac-cung-so-khoa-hoc-va-cong-nghe-tinh-gia-lai/</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
+          <t>Được doanh nghiệp đặt hàng từ khi chưa tốt nghiệp, nhóm sinh viên FPTU xây hệ thống “AI kiểm soát AI”</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 16:11</t>
+          <t>19/05/2026 11:40</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
@@ -5732,12 +5732,12 @@
       <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
+          <t>Dù chưa tốt nghiệp đại học, nhóm 5 sinh viên K18 chuyên ngành Kỹ thuật phần mềm Trường Đại học FPT đã được doanh nghiệp công nghệ giao bài toán xây dựng hệ thống AI Agent có khả năng tự động phát hiện sai lệch giữa tài liệu và mã nguồn. Dự án mang tên [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/duoc-doanh-nghiep-dat-hang-tu-khi-chua-tot-nghiep-nhom-sinh-vien-fptu-xay-he-thong-ai-kiem-soat-ai/</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
+          <t>Hướng dẫn chọn trường đại học phù hợp [4 bước chi tiết]</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 15:17</t>
+          <t>19/05/2026 09:04</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr"/>
@@ -5765,12 +5765,12 @@
       <c r="G155" s="2" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
+          <t>Trong hành trình tìm kiếm môi trường học tập lý tưởng, quá trình chọn trường đại học là một trong những bước quan trọng. Thông qua bài viết này, Trường Đại học FPT sẽ cung cấp hướng dẫn chi tiết, giúp thí sinh đưa ra quyết định thông minh và phù hợp với ước mơ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/chon-truong-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -5780,17 +5780,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
+          <t>Mức lương ngành Quản trị thu mua 2026 theo từng cấp bậc, vị trí</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 14:51</t>
+          <t>18/05/2026 16:11</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
@@ -5798,12 +5798,12 @@
       <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
+          <t>Trong bối cảnh dịch chuyển chuỗi cung ứng toàn cầu và làn sóng đầu tư FDI đổ mạnh vào Việt Nam, Quản trị thu mua (Procurement/Purchasing Management) đã trở thành một trong những khối ngành &amp;#8220;xương sống&amp;#8221; của các doanh nghiệp sản xuất, thương mại và logistics. Không còn bó hẹp trong khái niệm &amp;#8220;đi [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
+          <t>https://daihoc.fpt.edu.vn/huong-nghiep/muc-luong-nganh-quan-tri-thu-mua/</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
+          <t>Cựu sinh viên Digital Marketing đạt học bổng Thạc sĩ Đại học Bắc Kinh: “Tôi có được hôm nay nhờ FPTU”</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 10:32</t>
+          <t>18/05/2026 15:17</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr"/>
@@ -5831,12 +5831,12 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
+          <t>Từng tận dụng phòng học tại FPTU để tuyển sinh lớp tiếng Trung đầu tiên mà không tốn chi phí thuê mặt bằng, Hoàng Đức Bình &amp;#8211; cựu sinh viên K17 chuyên ngành Digital Marketing &amp;#8211; vừa giành học bổng chương trình Thạc sĩ Giáo dục Hán ngữ Quốc tế tại Đại học Bắc Kinh, [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/alumni/cuu-sinh-vien-digital-marketing-dat-hoc-bong-thac-si-dai-hoc-bac-kinh-toi-co-duoc-hom-nay-nho-fptu/</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
+          <t>Hàng trăm gương mặt Gen Z gây ấn tượng tại vòng phỏng vấn chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam – Học bổng Giáo sư Nguyễn Văn Đạo”</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026 09:07</t>
+          <t>18/05/2026 14:51</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr"/>
@@ -5864,12 +5864,12 @@
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
+          <t>Trong hai ngày 16 và 17/5, vòng phỏng vấn Đợt 1 chương trình “Tìm kiếm Nhân tài Kỷ nguyên số Việt Nam &amp;#8211; Học bổng Giáo sư Nguyễn Văn Đạo” đã diễn ra đồng loạt tại 5 cơ sở của Trường Đại học FPT trên toàn quốc, thu hút đông đảo thí sinh 2K8 tham [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/hang-tram-guong-mat-gen-z-gay-an-tuong-tai-vong-phong-van-chuong-trinh-tim-kiem-nhan-tai-ky-nguyen-so-viet-nam-hoc-bong-giao-su-nguyen-van-dao/</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
+          <t>Giới thiệu Trường Đại học FPT chi tiết, mới nhất 2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:30</t>
+          <t>18/05/2026 10:32</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr"/>
@@ -5897,12 +5897,12 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
+          <t>Kiên trì với sứ mệnh “Học thật &amp;#8211; Làm thật &amp;#8211; Thành công thật”, Trường Đại học FPT không chỉ là nơi truyền thụ kiến thức mà còn là cầu nối đưa sinh viên trực tiếp tham gia vào các dự án thực tế của doanh nghiệp để sẵn sàng vươn tầm thế giới. Để [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/gioi-thieu-ve-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
+          <t>Sinh viên kể chuyện tuổi trẻ bằng âm nhạc</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026 09:22</t>
+          <t>18/05/2026 09:07</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr"/>
@@ -5930,12 +5930,12 @@
       <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
+          <t>Từ trải nghiệm học tập trong môi trường đại học, sinh viên và cựu sinh viên Trường Đại học FPT đã đưa câu chuyện tuổi trẻ vào âm nhạc qua một dự án album. Nhân dịp kỷ niệm 20 năm thành lập, sinh viên và cựu sinh viên Trường Đại học FPT thực hiện dự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-ke-chuyen-tuoi-tre-bang-am-nhac/</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
+          <t>Điều đặc biệt trong album ca nhạc của 50 sinh viên, cựu sinh viên FPT</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 20:09</t>
+          <t>16/05/2026 09:30</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
@@ -5963,12 +5963,12 @@
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
+          <t>&amp;#8220;Thay vì thuê các ca sĩ, nhạc sĩ&amp;#8230; bên ngoài để làm một sản phẩm kỷ niệm hoành tráng nhưng mang tính một chiều, chúng tôi chọn cách trao toàn bộ sân khấu này cho chính sinh viên và cựu sinh viên&amp;#8221;, Hữu Phát nói. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/dieu-dac-biet-trong-album-ca-nhac-cua-50-sinh-vien-cuu-sinh-vien-fpt/</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
+          <t>50 sinh viên gây bất ngờ với album nhạc đậm tinh thần tuổi trẻ Việt</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5988,24 +5988,20 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 17:30</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
+          <t>16/05/2026 09:22</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” gây chú ý khi quy tụ 50 sinh viên và cựu sinh viên tham gia từ khâu sáng tác, hòa âm đến thể hiện. Sáu ca khúc mang màu sắc trẻ trung, lồng ghép nhiều chất liệu văn hóa Việt và tinh thần của thế hệ trẻ hôm nay. [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/50-sinh-vien-gay-bat-ngo-voi-album-nhac-dam-tinh-than-tuoi-tre-viet/</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6011,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
+          <t>Sinh viên Trường đại học FPT tự sáng tác, thu âm album ca nhạc mừng sinh nhật trường</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -6025,7 +6021,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:11</t>
+          <t>15/05/2026 20:09</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
@@ -6033,12 +6029,12 @@
       <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
+          <t>Album “Vươn mình cùng đất nước” do 50 sinh viên, cựu sinh viên Trường đại học FPT thực hiện từ sáng tác, phối khí, thu âm đến truyền thông, phát hành. Nhân dịp kỷ niệm 20 năm thành lập (2006 &amp;#8211; 2026), Trường đại học FPT ra mắt music album Vươn mình cùng đất nước với sự [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/sinh-vien-truong-dai-hoc-fpt-tu-sang-tac-thu-am-album-ca-nhac-mung-sinh-nhat-truong/</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6044,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
+          <t>FPTU đồng hành HITC Hub, tăng cơ hội thương mại hóa ý tưởng cho sinh viên</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -6058,20 +6054,24 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:08</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr"/>
+          <t>15/05/2026 17:30</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
+          <t>Sáng 15/5 tại Hà Nội, Trung tâm Ươm tạo và Đào tạo Công nghệ cao (HITC) tổ chức “Lễ kết nối mạng lưới và khởi động Không gian Đổi mới sáng tạo HITC Hub”. Tại đây, sinh viên FPTU &amp;#8211; các “nhà sáng lập trẻ” cũng trực tiếp mang các dự án startup đến trưng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/fptu-dong-hanh-hitc-hub-tang-co-hoi-thuong-mai-hoa-y-tuong-cho-sinh-vien/</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
+          <t>Trường Đại học FPT ở đâu? Danh sách các cơ sở trên toàn quốc</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:11</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr"/>
@@ -6099,12 +6099,12 @@
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
+          <t>Trường Đại học FPT là một trong những cơ sở đào tạo Đại học uy tín tại Việt Nam, nổi bật với mô hình giáo dục hiện đại, định hướng thực tiễn và môi trường học tập chuẩn quốc tế. Hiện nay, Trường Đại học FPT có 5 campus trải dài trên cả nước, tọa [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
+          <t>https://daihoc.fpt.edu.vn/tat-tan-tat-ve-fptu/dai-hoc-fpt-o-dau/</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
+          <t>5.0 IELTS quy đổi điểm tốt nghiệp THPT được bao nhiêu?</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 11:07</t>
+          <t>15/05/2026 11:08</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
@@ -6132,12 +6132,12 @@
       <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
+          <t>“5.0 IELTS quy đổi điểm tốt nghiệp được bao nhiêu?” đây là câu hỏi đang được rất nhiều học sinh và phụ huynh quan tâm trong bối cảnh kỳ thi THPT ngày càng cạnh tranh. Với mức điểm 5.0 IELTS, liệu thí sinh có được miễn thi môn tiếng Anh hay được cộng điểm ưu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/5-ielts-quy-doi-diem-tot-nghiep/</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
+          <t>40 Đề thi thử tốt nghiệp THPT 2026 môn Tiếng Anh có đáp án</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
+          <t>Việc tìm kiếm và rèn luyện các bộ đề thi thử tốt nghiệp THPT 2026 môn tiếng Anh từ sớm là bước chuẩn bị chiến lược để các sĩ tử 2008 bứt phá điểm số. Cùng FPTU điểm qua những thay đổi quan trọng và tải về bộ tài liệu ôn thi sát sườn nhất [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I167" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-tieng-anh/</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
+          <t>30 Đề thi thử tốt nghiệp THPT 2026 môn Địa Lý kèm ĐÁP ÁN, file PDF</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
+          <t>Việc luyện tập với các bộ đề thi thử tốt nghiệp THPT 2026 môn Địa từ sớm là cách tốt nhất để bạn làm quen với tư duy phân tích số liệu và kỹ năng quản lý thời gian làm bài hiệu quả. Cùng FPTU điểm qua những thay đổi trọng tâm và luyện bộ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-dia/</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
+          <t>15+ Đề thi thử tốt nghiệp THPT 2026 môn Sử và bí quyết ôn tập</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:54</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr"/>
@@ -6231,12 +6231,12 @@
       <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
+          <t>Lịch sử là môn học đòi hỏi khả năng tổng hợp và ghi nhớ cao. Việc tiếp cận sớm với các dạng đề thi thử tốt nghiệp THPT 2026 môn Sử sẽ giúp bạn nắm vững kiến thức và kỹ năng làm bài cần thiết. Tổng hợp đề thi thử tốt nghiệp THPT 2026 môn [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/e-thi-thu-tot-nghiep-thpt-2026-mon-su/</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
+          <t>40+ đề thi thử tốt nghiệp THPT môn Văn 2026 kèm đáp án</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:42</t>
+          <t>15/05/2026 11:07</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr"/>
@@ -6264,12 +6264,12 @@
       <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
+          <t>Môn Ngữ văn với sự thay đổi về ngữ liệu ngoài sách giáo khoa đang là nỗi băn khoăn lớn của nhiều sĩ tử. Việc tìm kiếm và luyện tập đề thi thử tốt nghiệp THPT 2026 môn Văn sớm sẽ giúp bạn làm lên chiến lược phân bổ thời gian hợp lý. Cùng Trường [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tuyen-sinh/de-thi-thu-tot-nghiep-thpt-2026-mon-van/</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
+          <t>Thi tốt nghiệp THPT gồm những môn nào? Cập nhật năm 2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 09:12</t>
+          <t>15/05/2026 09:54</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr"/>
@@ -6297,12 +6297,12 @@
       <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
+          <t>Thi tốt nghiệp THPT &amp;#8211; dấu mốc quan trọng đánh giá kết quả học tập của học sinh phổ thông và là bước đệm cho những lựa chọn định hướng tương lai. Tuy nhiên, cấu trúc và nội dung thi cử luôn có sự thay đổi theo từng năm học, khiến nhiều bạn thí sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thi-tot-nghiep-thpt-gom-nhung-mon-nao/</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
+          <t>Điểm khuyến khích là gì? Khái niệm và cách tính điểm 2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026 08:55</t>
+          <t>15/05/2026 09:42</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr"/>
@@ -6330,12 +6330,12 @@
       <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
+          <t>Trong kỳ thi tốt nghiệp THPT và xét tuyển đại học, bên cạnh điểm thi thực tế, thí sinh còn có cơ hội gia tăng tổng điểm thông qua các loại điểm cộng. Một trong những thắc mắc phổ biến nhất của các sĩ tử hiện nay là điểm khuyến khích là gì và làm [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-khuyen-khich-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6345,17 +6345,17 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
+          <t>Ra mắt Music Album “Vươn Mình Cùng Đất Nước”: Dấu ấn âm nhạc đặc biệt kỷ niệm 20 năm thành lập Trường Đại học FPT</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 19:35</t>
+          <t>15/05/2026 09:12</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr"/>
@@ -6363,12 +6363,12 @@
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
+          <t>Nhân dịp kỷ niệm 20 năm thành lập Trường Đại học FPT (2006 &amp;#8211; 2026), Music Album “Vươn Mình Cùng Đất Nước” chính thức được giới thiệu với sự tham gia thực hiện của 50 sinh viên và cựu sinh viên đến từ cả 5 cơ sở trên toàn quốc. Gồm 6 bài mang màu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/ra-mat-music-album-vuon-minh-cung-dat-nuoc-dau-an-am-nhac-dac-biet-ky-niem-20-nam-thanh-lap-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Điểm ưu tiên là gì? Cách tính điểm ưu tiên 2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026 13:42</t>
+          <t>15/05/2026 08:55</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr"/>
@@ -6396,12 +6396,12 @@
       <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
+          <t>Kỳ thi tốt nghiệp THPT đang đến gần, và điểm ưu tiên là một chủ đề quan trọng mà nhiều thí sinh thắc mắc. Vậy điểm ưu tiên là gì? Ai được hưởng điểm ưu tiên? Và cách tính điểm ưu tiên như thế nào? Trong bài viết này, Trường Đại học FPT sẽ cung [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6411,17 +6411,17 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
+          <t>HỘI THẢO PHỤ HUYNH HỌC SINH NĂM 2026 “CHỌN ĐẠI HỌC THẬT ĐẠI”</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:01</t>
+          <t>14/05/2026 19:35</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
+          <t>https://daihoc.fpt.edu.vn/event/hoi-thao-phu-huynh-hoc-sinh-nam-2026-chon-dai-hoc-that-dai/</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
+          <t>Nam sinh vùng cao giành học bổng tiến sĩ toàn phần hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 17:00</t>
+          <t>14/05/2026 13:42</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr"/>
@@ -6462,12 +6462,12 @@
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
+          <t>Từ học sinh vùng cao rụt rè, Nguyễn Hồng Anh theo đuổi ngành Trí tuệ nhân tạo và xuất sắc giành học bổng tiến sĩ toàn phần Mỹ trị giá 300.000 USD. Sinh ra và lớn lên tại tỉnh vùng cao Tuyên Quang (Hà Giang cũ), nơi điều kiện tiếp cận tri thức và công [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/nam-sinh-vung-cao-gianh-hoc-bong-tien-si-toan-phan-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6477,17 +6477,17 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
+          <t>Trường Đại học FPT tổ chức hội thảo phụ huynh quy tụ chuyên gia đa lĩnh vực, cùng giải bài toán nghề nghiệp trong kỷ nguyên AI</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 16:35</t>
+          <t>13/05/2026 17:01</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr"/>
@@ -6495,12 +6495,12 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
+          <t>Khi trí tuệ nhân tạo (AI) đang thay đổi cách con người học tập, làm việc và phát triển sự nghiệp, nhiều phụ huynh và học sinh đứng trước không ít băn khoăn: Ngành nghề nào sẽ phát triển mạnh trong tương lai? Những công việc nào có nguy cơ bị AI thay thế? Học [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-to-chuc-hoi-thao-phu-huynh-quy-tu-chuyen-gia-da-linh-vuc-cung-giai-bai-toan-nghe-nghiep-trong-ky-nguyen-ai/</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
+          <t>Cựu sinh viên FPTU giành học bổng Tiến sĩ hơn 7,5 tỷ đồng tại Mỹ</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 14:34</t>
+          <t>13/05/2026 17:00</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr"/>
@@ -6528,12 +6528,12 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
+          <t>Nguyễn Hồng Anh, sinh năm 2002, cựu sinh viên trường Đại học FPT (FPTU), nhận học bổng Tiến sĩ toàn phần trị giá khoảng 300.000 USD tại Đại học công nghệ Texas (Mỹ). Từ một học sinh vùng cao Hà Giang từng tự ti trước đám đông, Hồng Anh trở thành một trong những sinh [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
+          <t>https://daihoc.fpt.edu.vn/bao-chi-noi-ve-fptu/cuu-sinh-vien-fptu-gianh-hoc-bong-tien-si-hon-75-ty-dong-tai-my/</t>
         </is>
       </c>
     </row>
@@ -6543,17 +6543,17 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
+          <t>FPTU FUTURE READY TALK 2026: Đồng hành cùng phụ huynh và học sinh trước kỳ tuyển sinh đại học</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Tin tuc</t>
+          <t>Su kien</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 13:24</t>
+          <t>13/05/2026 16:35</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr"/>
@@ -6561,12 +6561,12 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
+          <t>Trong bối cảnh AI và công nghệ đang tạo ra nhiều thay đổi mạnh mẽ đối với thị trường lao động và xu hướng nghề nghiệp, việc lựa chọn ngành học và môi trường đào tạo phù hợp trở thành mối quan tâm lớn của nhiều phụ huynh và học sinh lớp 12 trước kỳ [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
+          <t>https://daihoc.fpt.edu.vn/event/fptu-future-ready-talk-2026-dong-hanh-cung-phu-huynh-va-hoc-sinh-truoc-ky-tuyen-sinh-dai-hoc/</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
+          <t>Đồ án khởi nghiệp của sinh viên FPTU đạt doanh thu gần 1 tỷ đồng sau 1 năm</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:59</t>
+          <t>13/05/2026 14:34</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr"/>
@@ -6594,12 +6594,12 @@
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
+          <t>Từ một dự án trong học phần khởi nghiệp tại FPTU, FTES đã phát triển thành nền tảng AI Learning thu hút hơn 4.000 học viên và đạt doanh thu gần 1 tỷ đồng chỉ sau hơn một năm vận hành. Được triển khai từ tháng 3/2025 đến nay, FTES (First Technology Education Solution) &amp;#8211; [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/do-an-khoi-nghiep-cua-sinh-vien-fptu-dat-doanh-thu-gan-1-ty-dong-sau-1-nam/</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
+          <t>Cựu sinh viên Trường Đại học FPT kể chuyện làm truyền thông tại DHG Pharma</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:33</t>
+          <t>13/05/2026 13:24</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr"/>
@@ -6627,12 +6627,12 @@
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
+          <t>Cựu sinh viên Trường Đại học FPT &amp;#8211; Phan Khương Hoan chia sẻ hành trình làm truyền thông tại DHG Pharma với nhiều hoạt động ý nghĩa vì cộng đồng. Không phải ánh đèn sân khấu hay những chiến dịch truyền thông hào nhoáng, hành trình làm nghề của Phan Khương Hoan lại bắt đầu [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/cuu-sinh-vien-truong-dai-hoc-fpt-2/</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
+          <t>Nguyện vọng là gì? Cách đăng ký nguyện vọng trực tuyến 2025</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:23</t>
+          <t>13/05/2026 09:59</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr"/>
@@ -6660,12 +6660,12 @@
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
+          <t>Sau khi kỳ thi tốt nghiệp THPT kết thúc, thí sinh bước vào giai đoạn quan trọng nhất: đăng ký nguyện vọng xét tuyển đại học. Đây là thời điểm quyết định lộ trình tương lai của học sinh. Tuy nhiên, việc hiểu rõ bản chất nguyện vọng là gì và thao tác chính xác [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
+          <t>Điểm sàn là gì? Điểm sàn với điểm chuẩn khác nhau như thế nào?</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026 09:12</t>
+          <t>13/05/2026 09:33</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr"/>
@@ -6693,12 +6693,12 @@
       <c r="G183" s="2" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
+          <t>Thời điểm hiện tại các sĩ tử chắc hẳn đang phải chạy đua nước rút để chuẩn bị cho kì thi tốt nghiệp trung học phổ thông quốc gia sắp tới. Cùng thời điểm này, các trường đại học sẽ công bố điểm sàn đến với các sĩ tử có nguyện vọng xét tuyển vào [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/diem-san-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
+          <t>Đối tượng ưu tiên là gì? Chi tiết về đối tượng ưu tiên tuyển sinh 2026</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -6718,24 +6718,20 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026 11:29</t>
-        </is>
-      </c>
-      <c r="E184" s="2" t="inlineStr">
-        <is>
-          <t>TP.HCM</t>
-        </is>
-      </c>
+          <t>13/05/2026 09:23</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
+          <t>Trong lộ trình xét tuyển đại học, việc nắm rõ đối tượng ưu tiên là gì đóng vai trò cực kỳ quan trọng, giúp học sinh không bỏ lỡ những quyền lợi chính đáng về điểm số. Đây là yếu tố có thể thay đổi cục diện, giúp học sinh gia tăng cơ hội trúng [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/doi-tuong-uu-tien-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6745,17 +6741,17 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
+          <t>Thứ tự nguyện vọng là gì? Những lưu ý khi đăng ký nguyện vọng</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026 19:37</t>
+          <t>13/05/2026 09:12</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr"/>
@@ -6763,12 +6759,12 @@
       <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
+          <t>Thứ tự nguyện vọng là gì? Đây là câu hỏi mà hầu hết học sinh lớp 12 đều quan tâm khi bước vào giai đoạn nước rút của kỳ thi tốt nghiệp THPT và xét tuyển đại học. Việc hiểu đúng bản chất và quy tắc sắp xếp nguyện vọng không chỉ giúp các em [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-campus/tin-campus-can-tho/thu-tu-nguyen-vong-la-gi/</t>
         </is>
       </c>
     </row>
@@ -6778,30 +6774,34 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
+          <t>Trường ĐH FPT tổ chức Hội nghị quốc tế EAI FISAT 2026</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Tuyen sinh</t>
+          <t>Tin tuc</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026 10:31</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr"/>
+          <t>12/05/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>TP.HCM</t>
+        </is>
+      </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
+          <t>Trường ĐH FPT sẽ tổ chức Hội nghị khoa học quốc tế EAI FISAT tại phân hiệu TP. Hồ Chí Minh từ ngày 25-27/11. Sự kiện dự kiến quy tụ hơn 150 chuyên gia trong và ngoài nước, các sinh viên, nghiên cứu sinh về hệ thống thông minh và các kỹ thuật nâng cao [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dh-fpt-to-chuc-hoi-nghi-quoc-te-eai-fisat-2026/</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
+          <t>Cập nhật mã Trường Đại học FPT và danh sách mã ngành xét tuyển Đại học 2026</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026 01:28</t>
+          <t>06/05/2026 19:37</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr"/>
@@ -6829,12 +6829,12 @@
       <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT trân trọng thông báo tuyển sinh hệ đại học chính quy năm 2026. Theo đó, phương thức tuyển sinh của Trường được thực hiện theo hình thức xét tuyển kết hợp giữa kết quả kỳ thi tốt nghiệp THPT và kết quả học tập THPT, nhằm đánh giá toàn diện năng [&amp;#8230;]</t>
+          <t>Trước thềm tuyển sinh Đại học 2026, việc nắm vững thông tin để đăng ký nguyện vọng chính xác trên hệ thống của Bộ Giáo dục và Đào tạo (Bộ GDĐT) là vô cùng cần thiết. Bài viết này sẽ cập nhật chi tiết về mã trường FPT và mã các ngành học 2026, giúp [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/thong-bao-tuyen-sinh-truong-dai-hoc-fpt-he-dai-hoc-chinh-quy-nam-2026/</t>
+          <t>https://daihoc.fpt.edu.vn/thong-bao-tuyen-sinh/ma-truong-dai-hoc-fpt/</t>
         </is>
       </c>
     </row>
@@ -6844,17 +6844,17 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>FPTU Open Day tại Nghệ An: Ngày hội trải nghiệm giáo dục đại học và định hướng tương lai dành cho học sinh THPT</t>
+          <t>Trường Đại học FPT dự kiến mở chuyên ngành mới Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid)</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Su kien</t>
+          <t>Tuyen sinh</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>16/03/2026 11:15</t>
+          <t>05/05/2026 10:31</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr"/>
@@ -6862,12 +6862,12 @@
       <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Trong bối cảnh lựa chọn ngành học và trường đại học trở thành một trong những quyết định quan trọng nhất của học sinh THPT, nhiều bạn trẻ và phụ huynh mong muốn được tìm hiểu thực tế về chương trình đào tạo, môi trường học tập và cơ hội nghề nghiệp trước khi đưa [&amp;#8230;]</t>
+          <t>Trong bối cảnh trí tuệ nhân tạo (AI) và robotics đang trở thành trụ cột của cuộc cách mạng công nghiệp mới, Trường Đại học FPT dự kiến mở chuyên ngành Robot và Trí tuệ nhân tạo (Định hướng UAV và Humanoid) thuộc ngành Công nghệ thông tin, tiếp tục mở rộng hệ sinh thái [&amp;#8230;]</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>https://daihoc.fpt.edu.vn/event/fptu-open-day-tai-nghe-an-co-hoi-kham-pha-nganh-hoc-va-trai-nghiem-moi-truong-dai-hoc-truoc-khi-quyet-dinh-tuong-lai/</t>
+          <t>https://daihoc.fpt.edu.vn/tin-tuc/truong-dai-hoc-fpt-du-kien-mo-chuyen-nganh-moi-robot-va-tri-tue-nhan-tao-dinh-huong-uav-va-humanoid/</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Trường Đại học FPT hỗ trợ 30% học phí toàn khóa cho học sinh vùng khó khăn</t>
+          <t>Thông báo tuyển sinh Trường Đại học FPT hệ đại học chính quy năm 2026</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
 